--- a/DC OPF/GridInputs.xlsx
+++ b/DC OPF/GridInputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/76f4b4c107b736ef/Programación/Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="308" documentId="14_{D584702F-B3CD-3F47-A25C-44363057DD2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A78AD236-6353-9E46-8104-27F600A4110F}"/>
+  <xr:revisionPtr revIDLastSave="399" documentId="14_{D584702F-B3CD-3F47-A25C-44363057DD2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D13FC94-C881-3542-A4C6-C198D2992F50}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" tabRatio="714" activeTab="5" xr2:uid="{36617186-47CB-F249-899F-182F2423F0BD}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" tabRatio="714" activeTab="3" xr2:uid="{36617186-47CB-F249-899F-182F2423F0BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Net_Buses" sheetId="5" r:id="rId1"/>
@@ -19,6 +19,9 @@
     <sheet name="Gen_Dispatchable" sheetId="7" r:id="rId4"/>
     <sheet name="Gen_PV_and_Wind" sheetId="8" r:id="rId5"/>
     <sheet name="StorageUnit" sheetId="13" r:id="rId6"/>
+    <sheet name="Tareas" sheetId="21" r:id="rId7"/>
+    <sheet name="Sheet4" sheetId="22" r:id="rId8"/>
+    <sheet name="Sheet1" sheetId="24" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="PV_Day">#REF!</definedName>
@@ -166,7 +169,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{1F2A03E5-7F7C-D940-AE1A-C1A8D7D1BB4B}">
+    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{1F2A03E5-7F7C-D940-AE1A-C1A8D7D1BB4B}">
       <text>
         <r>
           <rPr>
@@ -190,7 +193,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{DD0C3B7E-7816-A845-B8ED-5FA91332C753}">
+    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{DD0C3B7E-7816-A845-B8ED-5FA91332C753}">
       <text>
         <r>
           <rPr>
@@ -212,7 +215,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{D6D9CED7-0794-814D-B5B8-49D8CDAB5CFE}">
+    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{D6D9CED7-0794-814D-B5B8-49D8CDAB5CFE}">
       <text>
         <r>
           <rPr>
@@ -234,7 +237,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{E7C62203-8455-7F46-B593-D88B5F63BC43}">
+    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{E7C62203-8455-7F46-B593-D88B5F63BC43}">
       <text>
         <r>
           <rPr>
@@ -258,7 +261,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{484A55CF-B28F-9547-945F-5BA45CDECD2D}">
+    <comment ref="M3" authorId="0" shapeId="0" xr:uid="{484A55CF-B28F-9547-945F-5BA45CDECD2D}">
       <text>
         <r>
           <rPr>
@@ -280,7 +283,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M3" authorId="0" shapeId="0" xr:uid="{B87A6114-D140-124B-BDC5-CF3E26959C22}">
+    <comment ref="N3" authorId="0" shapeId="0" xr:uid="{B87A6114-D140-124B-BDC5-CF3E26959C22}">
       <text>
         <r>
           <rPr>
@@ -302,7 +305,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N3" authorId="0" shapeId="0" xr:uid="{3347CBF7-46F1-DC4B-839C-2BE23CEEBFB0}">
+    <comment ref="O3" authorId="0" shapeId="0" xr:uid="{3347CBF7-46F1-DC4B-839C-2BE23CEEBFB0}">
       <text>
         <r>
           <rPr>
@@ -324,7 +327,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O3" authorId="0" shapeId="0" xr:uid="{C16FE675-E26A-4F4F-A7AF-3C3D052898FF}">
+    <comment ref="P3" authorId="0" shapeId="0" xr:uid="{C16FE675-E26A-4F4F-A7AF-3C3D052898FF}">
       <text>
         <r>
           <rPr>
@@ -561,7 +564,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1362" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="189">
   <si>
     <t>From</t>
   </si>
@@ -1031,7 +1034,124 @@
     </r>
   </si>
   <si>
-    <t>BatteryStore</t>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Objetivo</t>
+  </si>
+  <si>
+    <t>Restricciones</t>
+  </si>
+  <si>
+    <t>Variables</t>
+  </si>
+  <si>
+    <t>LP</t>
+  </si>
+  <si>
+    <t>Lineal</t>
+  </si>
+  <si>
+    <t>Lineales</t>
+  </si>
+  <si>
+    <t>Continuas</t>
+  </si>
+  <si>
+    <t>QP</t>
+  </si>
+  <si>
+    <t>Cuadrático</t>
+  </si>
+  <si>
+    <t>NLP</t>
+  </si>
+  <si>
+    <t>No lineal</t>
+  </si>
+  <si>
+    <t>Lineales/no lineales</t>
+  </si>
+  <si>
+    <t>ILP</t>
+  </si>
+  <si>
+    <t>Enteras</t>
+  </si>
+  <si>
+    <t>MILP</t>
+  </si>
+  <si>
+    <t>Continuas + enteras</t>
+  </si>
+  <si>
+    <t>MIQP</t>
+  </si>
+  <si>
+    <t>MIQCP</t>
+  </si>
+  <si>
+    <t>Lineal/cuadrático</t>
+  </si>
+  <si>
+    <t>Cuadráticas</t>
+  </si>
+  <si>
+    <t>MINLP</t>
+  </si>
+  <si>
+    <t>No lineales</t>
+  </si>
+  <si>
+    <t>SOCP</t>
+  </si>
+  <si>
+    <t>Cónicas de segundo orden</t>
+  </si>
+  <si>
+    <t>SDP</t>
+  </si>
+  <si>
+    <t>Matriciales semidefinidas</t>
+  </si>
+  <si>
+    <t>Continuas/matriciales</t>
+  </si>
+  <si>
+    <t>Estocástica</t>
+  </si>
+  <si>
+    <t>Depende</t>
+  </si>
+  <si>
+    <t>Con escenarios</t>
+  </si>
+  <si>
+    <t>Robusta</t>
+  </si>
+  <si>
+    <t>Incertidumbre acotada</t>
+  </si>
+  <si>
+    <t>Dinámica</t>
+  </si>
+  <si>
+    <t>Secuenciales</t>
+  </si>
+  <si>
+    <t>DC OPF</t>
+  </si>
+  <si>
+    <t>PF</t>
+  </si>
+  <si>
+    <t>ED</t>
+  </si>
+  <si>
+    <t>AC OPF</t>
+  </si>
+  <si>
+    <t>Committable</t>
   </si>
 </sst>
 </file>
@@ -1042,7 +1162,7 @@
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1167,6 +1287,14 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1259,7 +1387,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1374,6 +1502,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1388,6 +1517,12 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2615,12 +2750,12 @@
       <c r="E1"/>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B3" s="6" t="s">
@@ -4053,11 +4188,11 @@
       <c r="D1"/>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
       <c r="F2" s="7"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
@@ -4256,7 +4391,7 @@
   <sheetPr codeName="Sheet5">
     <tabColor theme="6" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="B1:S65"/>
+  <dimension ref="B1:T65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5" customWidth="1"/>
@@ -4265,22 +4400,23 @@
     <col min="4" max="4" width="12.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="26.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="25.5" style="2" customWidth="1"/>
+    <col min="10" max="10" width="26.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.83203125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:20" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1"/>
       <c r="C1"/>
       <c r="D1"/>
@@ -4299,44 +4435,46 @@
       <c r="Q1"/>
       <c r="R1"/>
       <c r="S1"/>
-    </row>
-    <row r="2" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T1"/>
+    </row>
+    <row r="2" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="48"/>
-      <c r="F2" s="50" t="s">
+      <c r="E2" s="49"/>
+      <c r="F2" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="49" t="s">
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="P2" s="49"/>
-      <c r="Q2" s="49"/>
-      <c r="R2" s="49"/>
-      <c r="S2" s="49"/>
-    </row>
-    <row r="3" spans="2:19" ht="21" x14ac:dyDescent="0.2">
-      <c r="B3" s="30" t="s">
+      <c r="Q2" s="50"/>
+      <c r="R2" s="50"/>
+      <c r="S2" s="50"/>
+      <c r="T2" s="50"/>
+    </row>
+    <row r="3" spans="2:20" ht="21" x14ac:dyDescent="0.2">
+      <c r="B3" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="53" t="s">
         <v>138</v>
       </c>
       <c r="D3" s="30" t="s">
         <v>148</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="53" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="30" t="s">
@@ -4345,44 +4483,47 @@
       <c r="G3" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="30" t="s">
+      <c r="H3" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="I3" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="I3" s="30" t="s">
+      <c r="J3" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="30" t="s">
+      <c r="K3" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="K3" s="30" t="s">
+      <c r="L3" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="L3" s="30" t="s">
+      <c r="M3" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="M3" s="30" t="s">
+      <c r="N3" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="N3" s="30" t="s">
+      <c r="O3" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="O3" s="30" t="s">
+      <c r="P3" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="P3" s="32" t="s">
+      <c r="Q3" s="32" t="s">
         <v>141</v>
       </c>
-      <c r="Q3" s="30" t="s">
+      <c r="R3" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="R3" s="30" t="s">
+      <c r="S3" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="S3" s="30" t="s">
+      <c r="T3" s="30" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B4" s="29" t="s">
         <v>72</v>
       </c>
@@ -4401,45 +4542,48 @@
       <c r="G4" s="29">
         <v>0.05</v>
       </c>
-      <c r="H4" s="29">
-        <v>0.05</v>
+      <c r="H4" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I4" s="29">
         <v>0.05</v>
       </c>
       <c r="J4" s="29">
+        <v>0.05</v>
+      </c>
+      <c r="K4" s="29">
         <v>168</v>
       </c>
-      <c r="K4" s="29">
+      <c r="L4" s="29">
         <v>48</v>
       </c>
-      <c r="L4" s="29">
+      <c r="M4" s="29">
         <v>168</v>
       </c>
-      <c r="M4" s="34">
-        <v>0</v>
-      </c>
-      <c r="N4" s="29">
+      <c r="N4" s="34">
+        <v>0</v>
+      </c>
+      <c r="O4" s="29">
         <v>2659.2149999999997</v>
       </c>
-      <c r="O4" s="35">
+      <c r="P4" s="35">
         <v>27.32280368098159</v>
       </c>
-      <c r="P4" s="36">
+      <c r="Q4" s="36">
         <v>1</v>
       </c>
-      <c r="Q4" s="37">
+      <c r="R4" s="37">
         <f>E4*95</f>
         <v>252625.42499999996</v>
       </c>
-      <c r="R4" s="36">
-        <v>0</v>
-      </c>
       <c r="S4" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T4" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B5" s="29" t="s">
         <v>80</v>
       </c>
@@ -4458,45 +4602,48 @@
       <c r="G5" s="29">
         <v>0.05</v>
       </c>
-      <c r="H5" s="29">
-        <v>0.05</v>
+      <c r="H5" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I5" s="29">
         <v>0.05</v>
       </c>
       <c r="J5" s="29">
+        <v>0.05</v>
+      </c>
+      <c r="K5" s="29">
         <v>168</v>
       </c>
-      <c r="K5" s="29">
+      <c r="L5" s="29">
         <v>48</v>
       </c>
-      <c r="L5" s="29">
+      <c r="M5" s="29">
         <v>168</v>
       </c>
-      <c r="M5" s="34">
-        <v>0</v>
-      </c>
-      <c r="N5" s="29">
+      <c r="N5" s="34">
+        <v>0</v>
+      </c>
+      <c r="O5" s="29">
         <v>900.77</v>
       </c>
-      <c r="O5" s="35">
+      <c r="P5" s="35">
         <v>27.32280368098159</v>
       </c>
-      <c r="P5" s="36">
+      <c r="Q5" s="36">
         <v>1</v>
       </c>
-      <c r="Q5" s="37">
-        <f t="shared" ref="Q5:Q7" si="0">E5*95</f>
+      <c r="R5" s="37">
+        <f t="shared" ref="R5:R7" si="0">E5*95</f>
         <v>85573.15</v>
       </c>
-      <c r="R5" s="36">
-        <v>0</v>
-      </c>
       <c r="S5" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T5" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B6" s="29" t="s">
         <v>87</v>
       </c>
@@ -4515,45 +4662,48 @@
       <c r="G6" s="29">
         <v>0.05</v>
       </c>
-      <c r="H6" s="29">
-        <v>0.05</v>
+      <c r="H6" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I6" s="29">
         <v>0.05</v>
       </c>
       <c r="J6" s="29">
+        <v>0.05</v>
+      </c>
+      <c r="K6" s="29">
         <v>168</v>
       </c>
-      <c r="K6" s="29">
+      <c r="L6" s="29">
         <v>48</v>
       </c>
-      <c r="L6" s="29">
+      <c r="M6" s="29">
         <v>168</v>
       </c>
-      <c r="M6" s="34">
-        <v>0</v>
-      </c>
-      <c r="N6" s="29">
+      <c r="N6" s="34">
+        <v>0</v>
+      </c>
+      <c r="O6" s="29">
         <v>931.18999999999994</v>
       </c>
-      <c r="O6" s="35">
+      <c r="P6" s="35">
         <v>27.32280368098159</v>
       </c>
-      <c r="P6" s="36">
+      <c r="Q6" s="36">
         <v>1</v>
       </c>
-      <c r="Q6" s="37">
+      <c r="R6" s="37">
         <f t="shared" si="0"/>
         <v>88463.049999999988</v>
       </c>
-      <c r="R6" s="36">
-        <v>0</v>
-      </c>
       <c r="S6" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T6" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B7" s="29" t="s">
         <v>94</v>
       </c>
@@ -4572,45 +4722,48 @@
       <c r="G7" s="29">
         <v>0.05</v>
       </c>
-      <c r="H7" s="29">
-        <v>0.05</v>
+      <c r="H7" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I7" s="29">
         <v>0.05</v>
       </c>
       <c r="J7" s="29">
+        <v>0.05</v>
+      </c>
+      <c r="K7" s="29">
         <v>168</v>
       </c>
-      <c r="K7" s="29">
+      <c r="L7" s="29">
         <v>48</v>
       </c>
-      <c r="L7" s="29">
+      <c r="M7" s="29">
         <v>168</v>
       </c>
-      <c r="M7" s="34">
-        <v>0</v>
-      </c>
-      <c r="N7" s="29">
+      <c r="N7" s="34">
+        <v>0</v>
+      </c>
+      <c r="O7" s="29">
         <v>1768.585</v>
       </c>
-      <c r="O7" s="35">
+      <c r="P7" s="35">
         <v>27.32280368098159</v>
       </c>
-      <c r="P7" s="38">
+      <c r="Q7" s="38">
         <v>1</v>
       </c>
-      <c r="Q7" s="37">
+      <c r="R7" s="37">
         <f t="shared" si="0"/>
         <v>168015.57500000001</v>
       </c>
-      <c r="R7" s="36">
-        <v>0</v>
-      </c>
       <c r="S7" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T7" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B8" s="29" t="s">
         <v>65</v>
       </c>
@@ -4630,45 +4783,48 @@
       <c r="G8" s="36">
         <v>0.5</v>
       </c>
-      <c r="H8" s="36">
-        <v>0.5</v>
+      <c r="H8" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I8" s="36">
         <v>0.5</v>
       </c>
       <c r="J8" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="K8" s="36">
         <v>3</v>
       </c>
-      <c r="K8" s="36">
+      <c r="L8" s="36">
         <v>2</v>
       </c>
-      <c r="L8" s="34">
-        <v>0</v>
-      </c>
-      <c r="M8" s="36">
+      <c r="M8" s="34">
+        <v>0</v>
+      </c>
+      <c r="N8" s="36">
         <v>2</v>
       </c>
-      <c r="N8" s="34">
-        <v>0</v>
-      </c>
-      <c r="O8" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="P8" s="39">
+      <c r="O8" s="34">
+        <v>0</v>
+      </c>
+      <c r="P8" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q8" s="39">
         <v>0.6</v>
       </c>
-      <c r="Q8" s="36">
+      <c r="R8" s="36">
         <f>E8*40</f>
         <v>33440</v>
       </c>
-      <c r="R8" s="36">
-        <v>0</v>
-      </c>
       <c r="S8" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T8" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B9" s="29" t="s">
         <v>66</v>
       </c>
@@ -4688,45 +4844,48 @@
       <c r="G9" s="36">
         <v>0.5</v>
       </c>
-      <c r="H9" s="36">
-        <v>0.5</v>
+      <c r="H9" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I9" s="36">
         <v>0.5</v>
       </c>
       <c r="J9" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="K9" s="36">
         <v>3</v>
       </c>
-      <c r="K9" s="36">
+      <c r="L9" s="36">
         <v>2</v>
       </c>
-      <c r="L9" s="34">
-        <v>0</v>
-      </c>
-      <c r="M9" s="36">
+      <c r="M9" s="34">
+        <v>0</v>
+      </c>
+      <c r="N9" s="36">
         <v>2</v>
       </c>
-      <c r="N9" s="34">
-        <v>0</v>
-      </c>
-      <c r="O9" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="P9" s="39">
+      <c r="O9" s="34">
+        <v>0</v>
+      </c>
+      <c r="P9" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q9" s="39">
         <v>0.58718656544743497</v>
       </c>
-      <c r="Q9" s="36">
-        <f t="shared" ref="Q9:Q38" si="2">E9*40</f>
+      <c r="R9" s="36">
+        <f t="shared" ref="R9:R38" si="2">E9*40</f>
         <v>104328</v>
       </c>
-      <c r="R9" s="36">
-        <v>0</v>
-      </c>
       <c r="S9" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T9" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B10" s="29" t="s">
         <v>67</v>
       </c>
@@ -4746,45 +4905,48 @@
       <c r="G10" s="36">
         <v>0.5</v>
       </c>
-      <c r="H10" s="36">
-        <v>0.5</v>
+      <c r="H10" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I10" s="36">
         <v>0.5</v>
       </c>
       <c r="J10" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="K10" s="36">
         <v>3</v>
       </c>
-      <c r="K10" s="36">
+      <c r="L10" s="36">
         <v>2</v>
       </c>
-      <c r="L10" s="34">
-        <v>0</v>
-      </c>
-      <c r="M10" s="36">
+      <c r="M10" s="34">
+        <v>0</v>
+      </c>
+      <c r="N10" s="36">
         <v>2</v>
       </c>
-      <c r="N10" s="34">
-        <v>0</v>
-      </c>
-      <c r="O10" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="P10" s="39">
+      <c r="O10" s="34">
+        <v>0</v>
+      </c>
+      <c r="P10" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q10" s="39">
         <v>0.58809606293778693</v>
       </c>
-      <c r="Q10" s="36">
+      <c r="R10" s="36">
         <f t="shared" si="2"/>
         <v>115924</v>
       </c>
-      <c r="R10" s="36">
-        <v>0</v>
-      </c>
       <c r="S10" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T10" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B11" s="29" t="s">
         <v>68</v>
       </c>
@@ -4804,45 +4966,48 @@
       <c r="G11" s="36">
         <v>0.5</v>
       </c>
-      <c r="H11" s="36">
-        <v>0.5</v>
+      <c r="H11" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I11" s="36">
         <v>0.5</v>
       </c>
       <c r="J11" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="K11" s="36">
         <v>3</v>
       </c>
-      <c r="K11" s="36">
+      <c r="L11" s="36">
         <v>2</v>
       </c>
-      <c r="L11" s="34">
-        <v>0</v>
-      </c>
-      <c r="M11" s="36">
+      <c r="M11" s="34">
+        <v>0</v>
+      </c>
+      <c r="N11" s="36">
         <v>2</v>
       </c>
-      <c r="N11" s="34">
-        <v>0</v>
-      </c>
-      <c r="O11" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="P11" s="39">
+      <c r="O11" s="34">
+        <v>0</v>
+      </c>
+      <c r="P11" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q11" s="39">
         <v>0.6</v>
       </c>
-      <c r="Q11" s="36">
+      <c r="R11" s="36">
         <f t="shared" si="2"/>
         <v>3040</v>
       </c>
-      <c r="R11" s="36">
-        <v>0</v>
-      </c>
       <c r="S11" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T11" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B12" s="29" t="s">
         <v>69</v>
       </c>
@@ -4862,45 +5027,48 @@
       <c r="G12" s="36">
         <v>0.5</v>
       </c>
-      <c r="H12" s="36">
-        <v>0.5</v>
+      <c r="H12" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I12" s="36">
         <v>0.5</v>
       </c>
       <c r="J12" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="K12" s="36">
         <v>3</v>
       </c>
-      <c r="K12" s="36">
+      <c r="L12" s="36">
         <v>2</v>
       </c>
-      <c r="L12" s="34">
-        <v>0</v>
-      </c>
-      <c r="M12" s="36">
+      <c r="M12" s="34">
+        <v>0</v>
+      </c>
+      <c r="N12" s="36">
         <v>2</v>
       </c>
-      <c r="N12" s="34">
-        <v>0</v>
-      </c>
-      <c r="O12" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="P12" s="39">
+      <c r="O12" s="34">
+        <v>0</v>
+      </c>
+      <c r="P12" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q12" s="39">
         <v>0.6</v>
       </c>
-      <c r="Q12" s="36">
+      <c r="R12" s="36">
         <f t="shared" si="2"/>
         <v>3840</v>
       </c>
-      <c r="R12" s="36">
-        <v>0</v>
-      </c>
       <c r="S12" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T12" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B13" s="29" t="s">
         <v>72</v>
       </c>
@@ -4920,45 +5088,48 @@
       <c r="G13" s="36">
         <v>0.5</v>
       </c>
-      <c r="H13" s="36">
-        <v>0.5</v>
+      <c r="H13" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I13" s="36">
         <v>0.5</v>
       </c>
       <c r="J13" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="K13" s="36">
         <v>3</v>
       </c>
-      <c r="K13" s="36">
+      <c r="L13" s="36">
         <v>2</v>
       </c>
-      <c r="L13" s="34">
-        <v>0</v>
-      </c>
-      <c r="M13" s="36">
+      <c r="M13" s="34">
+        <v>0</v>
+      </c>
+      <c r="N13" s="36">
         <v>2</v>
       </c>
-      <c r="N13" s="34">
-        <v>0</v>
-      </c>
-      <c r="O13" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="P13" s="39">
+      <c r="O13" s="34">
+        <v>0</v>
+      </c>
+      <c r="P13" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q13" s="39">
         <v>0.6</v>
       </c>
-      <c r="Q13" s="36">
+      <c r="R13" s="36">
         <f t="shared" si="2"/>
         <v>35884</v>
       </c>
-      <c r="R13" s="36">
-        <v>0</v>
-      </c>
       <c r="S13" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T13" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B14" s="29" t="s">
         <v>75</v>
       </c>
@@ -4978,45 +5149,48 @@
       <c r="G14" s="36">
         <v>0.5</v>
       </c>
-      <c r="H14" s="36">
-        <v>0.5</v>
+      <c r="H14" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I14" s="36">
         <v>0.5</v>
       </c>
       <c r="J14" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="K14" s="36">
         <v>3</v>
       </c>
-      <c r="K14" s="36">
+      <c r="L14" s="36">
         <v>2</v>
       </c>
-      <c r="L14" s="34">
-        <v>0</v>
-      </c>
-      <c r="M14" s="36">
+      <c r="M14" s="34">
+        <v>0</v>
+      </c>
+      <c r="N14" s="36">
         <v>2</v>
       </c>
-      <c r="N14" s="34">
-        <v>0</v>
-      </c>
-      <c r="O14" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="P14" s="39">
+      <c r="O14" s="34">
+        <v>0</v>
+      </c>
+      <c r="P14" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q14" s="39">
         <v>0.60000000000000009</v>
       </c>
-      <c r="Q14" s="36">
+      <c r="R14" s="36">
         <f t="shared" si="2"/>
         <v>2992</v>
       </c>
-      <c r="R14" s="36">
-        <v>0</v>
-      </c>
       <c r="S14" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T14" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B15" s="29" t="s">
         <v>76</v>
       </c>
@@ -5036,45 +5210,48 @@
       <c r="G15" s="36">
         <v>0.5</v>
       </c>
-      <c r="H15" s="36">
-        <v>0.5</v>
+      <c r="H15" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I15" s="36">
         <v>0.5</v>
       </c>
       <c r="J15" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="K15" s="36">
         <v>3</v>
       </c>
-      <c r="K15" s="36">
+      <c r="L15" s="36">
         <v>2</v>
       </c>
-      <c r="L15" s="34">
-        <v>0</v>
-      </c>
-      <c r="M15" s="36">
+      <c r="M15" s="34">
+        <v>0</v>
+      </c>
+      <c r="N15" s="36">
         <v>2</v>
       </c>
-      <c r="N15" s="34">
-        <v>0</v>
-      </c>
-      <c r="O15" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="P15" s="39">
+      <c r="O15" s="34">
+        <v>0</v>
+      </c>
+      <c r="P15" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q15" s="39">
         <v>0.6</v>
       </c>
-      <c r="Q15" s="36">
+      <c r="R15" s="36">
         <f t="shared" si="2"/>
         <v>54880</v>
       </c>
-      <c r="R15" s="36">
-        <v>0</v>
-      </c>
       <c r="S15" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T15" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B16" s="29" t="s">
         <v>77</v>
       </c>
@@ -5094,45 +5271,48 @@
       <c r="G16" s="36">
         <v>0.5</v>
       </c>
-      <c r="H16" s="36">
-        <v>0.5</v>
+      <c r="H16" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I16" s="36">
         <v>0.5</v>
       </c>
       <c r="J16" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="K16" s="36">
         <v>3</v>
       </c>
-      <c r="K16" s="36">
+      <c r="L16" s="36">
         <v>2</v>
       </c>
-      <c r="L16" s="34">
-        <v>0</v>
-      </c>
-      <c r="M16" s="36">
+      <c r="M16" s="34">
+        <v>0</v>
+      </c>
+      <c r="N16" s="36">
         <v>2</v>
       </c>
-      <c r="N16" s="34">
-        <v>0</v>
-      </c>
-      <c r="O16" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="P16" s="39">
+      <c r="O16" s="34">
+        <v>0</v>
+      </c>
+      <c r="P16" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q16" s="39">
         <v>0.6</v>
       </c>
-      <c r="Q16" s="36">
+      <c r="R16" s="36">
         <f t="shared" si="2"/>
         <v>34240</v>
       </c>
-      <c r="R16" s="36">
-        <v>0</v>
-      </c>
       <c r="S16" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T16" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B17" s="29" t="s">
         <v>78</v>
       </c>
@@ -5152,45 +5332,48 @@
       <c r="G17" s="36">
         <v>0.5</v>
       </c>
-      <c r="H17" s="36">
-        <v>0.5</v>
+      <c r="H17" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I17" s="36">
         <v>0.5</v>
       </c>
       <c r="J17" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="K17" s="36">
         <v>3</v>
       </c>
-      <c r="K17" s="36">
+      <c r="L17" s="36">
         <v>2</v>
       </c>
-      <c r="L17" s="34">
-        <v>0</v>
-      </c>
-      <c r="M17" s="36">
+      <c r="M17" s="34">
+        <v>0</v>
+      </c>
+      <c r="N17" s="36">
         <v>2</v>
       </c>
-      <c r="N17" s="34">
-        <v>0</v>
-      </c>
-      <c r="O17" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="P17" s="39">
+      <c r="O17" s="34">
+        <v>0</v>
+      </c>
+      <c r="P17" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q17" s="39">
         <v>0.6</v>
       </c>
-      <c r="Q17" s="36">
+      <c r="R17" s="36">
         <f t="shared" si="2"/>
         <v>920</v>
       </c>
-      <c r="R17" s="36">
-        <v>0</v>
-      </c>
       <c r="S17" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T17" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B18" s="29" t="s">
         <v>79</v>
       </c>
@@ -5210,45 +5393,48 @@
       <c r="G18" s="36">
         <v>0.5</v>
       </c>
-      <c r="H18" s="36">
-        <v>0.5</v>
+      <c r="H18" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I18" s="36">
         <v>0.5</v>
       </c>
       <c r="J18" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="K18" s="36">
         <v>3</v>
       </c>
-      <c r="K18" s="36">
+      <c r="L18" s="36">
         <v>2</v>
       </c>
-      <c r="L18" s="34">
-        <v>0</v>
-      </c>
-      <c r="M18" s="36">
+      <c r="M18" s="34">
+        <v>0</v>
+      </c>
+      <c r="N18" s="36">
         <v>2</v>
       </c>
-      <c r="N18" s="34">
-        <v>0</v>
-      </c>
-      <c r="O18" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="P18" s="39">
+      <c r="O18" s="34">
+        <v>0</v>
+      </c>
+      <c r="P18" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q18" s="39">
         <v>0.6</v>
       </c>
-      <c r="Q18" s="36">
+      <c r="R18" s="36">
         <f t="shared" si="2"/>
         <v>138708</v>
       </c>
-      <c r="R18" s="36">
-        <v>0</v>
-      </c>
       <c r="S18" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T18" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B19" s="29" t="s">
         <v>80</v>
       </c>
@@ -5268,45 +5454,48 @@
       <c r="G19" s="36">
         <v>0.5</v>
       </c>
-      <c r="H19" s="36">
-        <v>0.5</v>
+      <c r="H19" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I19" s="36">
         <v>0.5</v>
       </c>
       <c r="J19" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="K19" s="36">
         <v>3</v>
       </c>
-      <c r="K19" s="36">
+      <c r="L19" s="36">
         <v>2</v>
       </c>
-      <c r="L19" s="34">
-        <v>0</v>
-      </c>
-      <c r="M19" s="36">
+      <c r="M19" s="34">
+        <v>0</v>
+      </c>
+      <c r="N19" s="36">
         <v>2</v>
       </c>
-      <c r="N19" s="34">
-        <v>0</v>
-      </c>
-      <c r="O19" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="P19" s="39">
+      <c r="O19" s="34">
+        <v>0</v>
+      </c>
+      <c r="P19" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q19" s="39">
         <v>0.6</v>
       </c>
-      <c r="Q19" s="36">
+      <c r="R19" s="36">
         <f t="shared" si="2"/>
         <v>1000</v>
       </c>
-      <c r="R19" s="36">
-        <v>0</v>
-      </c>
       <c r="S19" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T19" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B20" s="29" t="s">
         <v>81</v>
       </c>
@@ -5326,45 +5515,48 @@
       <c r="G20" s="36">
         <v>0.5</v>
       </c>
-      <c r="H20" s="36">
-        <v>0.5</v>
+      <c r="H20" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I20" s="36">
         <v>0.5</v>
       </c>
       <c r="J20" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="K20" s="36">
         <v>3</v>
       </c>
-      <c r="K20" s="36">
+      <c r="L20" s="36">
         <v>2</v>
       </c>
-      <c r="L20" s="34">
-        <v>0</v>
-      </c>
-      <c r="M20" s="36">
+      <c r="M20" s="34">
+        <v>0</v>
+      </c>
+      <c r="N20" s="36">
         <v>2</v>
       </c>
-      <c r="N20" s="34">
-        <v>0</v>
-      </c>
-      <c r="O20" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="P20" s="39">
+      <c r="O20" s="34">
+        <v>0</v>
+      </c>
+      <c r="P20" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q20" s="39">
         <v>0.59017014020996272</v>
       </c>
-      <c r="Q20" s="36">
+      <c r="R20" s="36">
         <f t="shared" si="2"/>
         <v>170316</v>
       </c>
-      <c r="R20" s="36">
-        <v>0</v>
-      </c>
       <c r="S20" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T20" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B21" s="29" t="s">
         <v>85</v>
       </c>
@@ -5384,45 +5576,48 @@
       <c r="G21" s="36">
         <v>0.5</v>
       </c>
-      <c r="H21" s="36">
-        <v>0.5</v>
+      <c r="H21" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I21" s="36">
         <v>0.5</v>
       </c>
       <c r="J21" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="K21" s="36">
         <v>3</v>
       </c>
-      <c r="K21" s="36">
+      <c r="L21" s="36">
         <v>2</v>
       </c>
-      <c r="L21" s="34">
-        <v>0</v>
-      </c>
-      <c r="M21" s="36">
+      <c r="M21" s="34">
+        <v>0</v>
+      </c>
+      <c r="N21" s="36">
         <v>2</v>
       </c>
-      <c r="N21" s="34">
-        <v>0</v>
-      </c>
-      <c r="O21" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="P21" s="39">
+      <c r="O21" s="34">
+        <v>0</v>
+      </c>
+      <c r="P21" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q21" s="39">
         <v>0.6</v>
       </c>
-      <c r="Q21" s="36">
+      <c r="R21" s="36">
         <f t="shared" si="2"/>
         <v>1000</v>
       </c>
-      <c r="R21" s="36">
-        <v>0</v>
-      </c>
       <c r="S21" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T21" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B22" s="29" t="s">
         <v>86</v>
       </c>
@@ -5442,45 +5637,48 @@
       <c r="G22" s="36">
         <v>0.5</v>
       </c>
-      <c r="H22" s="36">
-        <v>0.5</v>
+      <c r="H22" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I22" s="36">
         <v>0.5</v>
       </c>
       <c r="J22" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="K22" s="36">
         <v>3</v>
       </c>
-      <c r="K22" s="36">
+      <c r="L22" s="36">
         <v>2</v>
       </c>
-      <c r="L22" s="34">
-        <v>0</v>
-      </c>
-      <c r="M22" s="36">
+      <c r="M22" s="34">
+        <v>0</v>
+      </c>
+      <c r="N22" s="36">
         <v>2</v>
       </c>
-      <c r="N22" s="34">
-        <v>0</v>
-      </c>
-      <c r="O22" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="P22" s="39">
+      <c r="O22" s="34">
+        <v>0</v>
+      </c>
+      <c r="P22" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q22" s="39">
         <v>0.6</v>
       </c>
-      <c r="Q22" s="36">
+      <c r="R22" s="36">
         <f t="shared" si="2"/>
         <v>34104</v>
       </c>
-      <c r="R22" s="36">
-        <v>0</v>
-      </c>
       <c r="S22" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T22" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B23" s="29" t="s">
         <v>88</v>
       </c>
@@ -5500,45 +5698,48 @@
       <c r="G23" s="36">
         <v>0.5</v>
       </c>
-      <c r="H23" s="36">
-        <v>0.5</v>
+      <c r="H23" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I23" s="36">
         <v>0.5</v>
       </c>
       <c r="J23" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="K23" s="36">
         <v>3</v>
       </c>
-      <c r="K23" s="36">
+      <c r="L23" s="36">
         <v>2</v>
       </c>
-      <c r="L23" s="34">
-        <v>0</v>
-      </c>
-      <c r="M23" s="36">
+      <c r="M23" s="34">
+        <v>0</v>
+      </c>
+      <c r="N23" s="36">
         <v>2</v>
       </c>
-      <c r="N23" s="34">
-        <v>0</v>
-      </c>
-      <c r="O23" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="P23" s="39">
+      <c r="O23" s="34">
+        <v>0</v>
+      </c>
+      <c r="P23" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q23" s="39">
         <v>0.6</v>
       </c>
-      <c r="Q23" s="36">
+      <c r="R23" s="36">
         <f t="shared" si="2"/>
         <v>2000</v>
       </c>
-      <c r="R23" s="36">
-        <v>0</v>
-      </c>
       <c r="S23" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T23" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B24" s="29" t="s">
         <v>89</v>
       </c>
@@ -5558,45 +5759,48 @@
       <c r="G24" s="36">
         <v>0.5</v>
       </c>
-      <c r="H24" s="36">
-        <v>0.5</v>
+      <c r="H24" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I24" s="36">
         <v>0.5</v>
       </c>
       <c r="J24" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="K24" s="36">
         <v>3</v>
       </c>
-      <c r="K24" s="36">
+      <c r="L24" s="36">
         <v>2</v>
       </c>
-      <c r="L24" s="34">
-        <v>0</v>
-      </c>
-      <c r="M24" s="36">
+      <c r="M24" s="34">
+        <v>0</v>
+      </c>
+      <c r="N24" s="36">
         <v>2</v>
       </c>
-      <c r="N24" s="34">
-        <v>0</v>
-      </c>
-      <c r="O24" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="P24" s="39">
+      <c r="O24" s="34">
+        <v>0</v>
+      </c>
+      <c r="P24" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q24" s="39">
         <v>0.6</v>
       </c>
-      <c r="Q24" s="36">
+      <c r="R24" s="36">
         <f t="shared" si="2"/>
         <v>18000</v>
       </c>
-      <c r="R24" s="36">
-        <v>0</v>
-      </c>
       <c r="S24" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T24" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B25" s="29" t="s">
         <v>90</v>
       </c>
@@ -5616,45 +5820,48 @@
       <c r="G25" s="36">
         <v>0.5</v>
       </c>
-      <c r="H25" s="36">
-        <v>0.5</v>
+      <c r="H25" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I25" s="36">
         <v>0.5</v>
       </c>
       <c r="J25" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="K25" s="36">
         <v>3</v>
       </c>
-      <c r="K25" s="36">
+      <c r="L25" s="36">
         <v>2</v>
       </c>
-      <c r="L25" s="34">
-        <v>0</v>
-      </c>
-      <c r="M25" s="36">
+      <c r="M25" s="34">
+        <v>0</v>
+      </c>
+      <c r="N25" s="36">
         <v>2</v>
       </c>
-      <c r="N25" s="34">
-        <v>0</v>
-      </c>
-      <c r="O25" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="P25" s="39">
+      <c r="O25" s="34">
+        <v>0</v>
+      </c>
+      <c r="P25" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q25" s="39">
         <v>0.6</v>
       </c>
-      <c r="Q25" s="36">
+      <c r="R25" s="36">
         <f t="shared" si="2"/>
         <v>19840</v>
       </c>
-      <c r="R25" s="36">
-        <v>0</v>
-      </c>
       <c r="S25" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T25" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B26" s="29" t="s">
         <v>96</v>
       </c>
@@ -5674,45 +5881,48 @@
       <c r="G26" s="36">
         <v>0.5</v>
       </c>
-      <c r="H26" s="36">
-        <v>0.5</v>
+      <c r="H26" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I26" s="36">
         <v>0.5</v>
       </c>
       <c r="J26" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="K26" s="36">
         <v>3</v>
       </c>
-      <c r="K26" s="36">
+      <c r="L26" s="36">
         <v>2</v>
       </c>
-      <c r="L26" s="34">
-        <v>0</v>
-      </c>
-      <c r="M26" s="36">
+      <c r="M26" s="34">
+        <v>0</v>
+      </c>
+      <c r="N26" s="36">
         <v>2</v>
       </c>
-      <c r="N26" s="34">
-        <v>0</v>
-      </c>
-      <c r="O26" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="P26" s="39">
+      <c r="O26" s="34">
+        <v>0</v>
+      </c>
+      <c r="P26" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q26" s="39">
         <v>0.6</v>
       </c>
-      <c r="Q26" s="36">
+      <c r="R26" s="36">
         <f t="shared" si="2"/>
         <v>78680</v>
       </c>
-      <c r="R26" s="36">
-        <v>0</v>
-      </c>
       <c r="S26" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T26" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B27" s="29" t="s">
         <v>97</v>
       </c>
@@ -5732,45 +5942,48 @@
       <c r="G27" s="36">
         <v>0.5</v>
       </c>
-      <c r="H27" s="36">
-        <v>0.5</v>
+      <c r="H27" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I27" s="36">
         <v>0.5</v>
       </c>
       <c r="J27" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="K27" s="36">
         <v>3</v>
       </c>
-      <c r="K27" s="36">
+      <c r="L27" s="36">
         <v>2</v>
       </c>
-      <c r="L27" s="34">
-        <v>0</v>
-      </c>
-      <c r="M27" s="36">
+      <c r="M27" s="34">
+        <v>0</v>
+      </c>
+      <c r="N27" s="36">
         <v>2</v>
       </c>
-      <c r="N27" s="34">
-        <v>0</v>
-      </c>
-      <c r="O27" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="P27" s="39">
+      <c r="O27" s="34">
+        <v>0</v>
+      </c>
+      <c r="P27" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q27" s="39">
         <v>0.6</v>
       </c>
-      <c r="Q27" s="36">
+      <c r="R27" s="36">
         <f t="shared" si="2"/>
         <v>2800</v>
       </c>
-      <c r="R27" s="36">
-        <v>0</v>
-      </c>
       <c r="S27" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T27" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B28" s="29" t="s">
         <v>98</v>
       </c>
@@ -5790,45 +6003,48 @@
       <c r="G28" s="36">
         <v>0.5</v>
       </c>
-      <c r="H28" s="36">
-        <v>0.5</v>
+      <c r="H28" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I28" s="36">
         <v>0.5</v>
       </c>
       <c r="J28" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="K28" s="36">
         <v>3</v>
       </c>
-      <c r="K28" s="36">
+      <c r="L28" s="36">
         <v>2</v>
       </c>
-      <c r="L28" s="34">
-        <v>0</v>
-      </c>
-      <c r="M28" s="36">
+      <c r="M28" s="34">
+        <v>0</v>
+      </c>
+      <c r="N28" s="36">
         <v>2</v>
       </c>
-      <c r="N28" s="34">
-        <v>0</v>
-      </c>
-      <c r="O28" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="P28" s="39">
+      <c r="O28" s="34">
+        <v>0</v>
+      </c>
+      <c r="P28" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q28" s="39">
         <v>0.30130258346394029</v>
       </c>
-      <c r="Q28" s="36">
+      <c r="R28" s="36">
         <f t="shared" si="2"/>
         <v>50648</v>
       </c>
-      <c r="R28" s="36">
-        <v>0</v>
-      </c>
       <c r="S28" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T28" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B29" s="29" t="s">
         <v>100</v>
       </c>
@@ -5848,45 +6064,48 @@
       <c r="G29" s="36">
         <v>0.5</v>
       </c>
-      <c r="H29" s="36">
-        <v>0.5</v>
+      <c r="H29" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I29" s="36">
         <v>0.5</v>
       </c>
       <c r="J29" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="K29" s="36">
         <v>3</v>
       </c>
-      <c r="K29" s="36">
+      <c r="L29" s="36">
         <v>2</v>
       </c>
-      <c r="L29" s="34">
-        <v>0</v>
-      </c>
-      <c r="M29" s="36">
+      <c r="M29" s="34">
+        <v>0</v>
+      </c>
+      <c r="N29" s="36">
         <v>2</v>
       </c>
-      <c r="N29" s="34">
-        <v>0</v>
-      </c>
-      <c r="O29" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="P29" s="39">
+      <c r="O29" s="34">
+        <v>0</v>
+      </c>
+      <c r="P29" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q29" s="39">
         <v>0.6</v>
       </c>
-      <c r="Q29" s="36">
+      <c r="R29" s="36">
         <f t="shared" si="2"/>
         <v>1280</v>
       </c>
-      <c r="R29" s="36">
-        <v>0</v>
-      </c>
       <c r="S29" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T29" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B30" s="29" t="s">
         <v>101</v>
       </c>
@@ -5906,45 +6125,48 @@
       <c r="G30" s="36">
         <v>0.5</v>
       </c>
-      <c r="H30" s="36">
-        <v>0.5</v>
+      <c r="H30" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I30" s="36">
         <v>0.5</v>
       </c>
       <c r="J30" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="K30" s="36">
         <v>3</v>
       </c>
-      <c r="K30" s="36">
+      <c r="L30" s="36">
         <v>2</v>
       </c>
-      <c r="L30" s="34">
-        <v>0</v>
-      </c>
-      <c r="M30" s="36">
+      <c r="M30" s="34">
+        <v>0</v>
+      </c>
+      <c r="N30" s="36">
         <v>2</v>
       </c>
-      <c r="N30" s="34">
-        <v>0</v>
-      </c>
-      <c r="O30" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="P30" s="39">
+      <c r="O30" s="34">
+        <v>0</v>
+      </c>
+      <c r="P30" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q30" s="39">
         <v>0.3899999999999999</v>
       </c>
-      <c r="Q30" s="36">
+      <c r="R30" s="36">
         <f t="shared" si="2"/>
         <v>16640</v>
       </c>
-      <c r="R30" s="36">
-        <v>0</v>
-      </c>
       <c r="S30" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T30" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B31" s="29" t="s">
         <v>102</v>
       </c>
@@ -5964,45 +6186,48 @@
       <c r="G31" s="36">
         <v>0.5</v>
       </c>
-      <c r="H31" s="36">
-        <v>0.5</v>
+      <c r="H31" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I31" s="36">
         <v>0.5</v>
       </c>
       <c r="J31" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="K31" s="36">
         <v>3</v>
       </c>
-      <c r="K31" s="36">
+      <c r="L31" s="36">
         <v>2</v>
       </c>
-      <c r="L31" s="34">
-        <v>0</v>
-      </c>
-      <c r="M31" s="36">
+      <c r="M31" s="34">
+        <v>0</v>
+      </c>
+      <c r="N31" s="36">
         <v>2</v>
       </c>
-      <c r="N31" s="34">
-        <v>0</v>
-      </c>
-      <c r="O31" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="P31" s="39">
+      <c r="O31" s="34">
+        <v>0</v>
+      </c>
+      <c r="P31" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q31" s="39">
         <v>0.6</v>
       </c>
-      <c r="Q31" s="36">
+      <c r="R31" s="36">
         <f t="shared" si="2"/>
         <v>83880</v>
       </c>
-      <c r="R31" s="36">
-        <v>0</v>
-      </c>
       <c r="S31" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T31" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B32" s="29" t="s">
         <v>104</v>
       </c>
@@ -6022,45 +6247,48 @@
       <c r="G32" s="36">
         <v>0.5</v>
       </c>
-      <c r="H32" s="36">
-        <v>0.5</v>
+      <c r="H32" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I32" s="36">
         <v>0.5</v>
       </c>
       <c r="J32" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="K32" s="36">
         <v>3</v>
       </c>
-      <c r="K32" s="36">
+      <c r="L32" s="36">
         <v>2</v>
       </c>
-      <c r="L32" s="34">
-        <v>0</v>
-      </c>
-      <c r="M32" s="36">
+      <c r="M32" s="34">
+        <v>0</v>
+      </c>
+      <c r="N32" s="36">
         <v>2</v>
       </c>
-      <c r="N32" s="34">
-        <v>0</v>
-      </c>
-      <c r="O32" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="P32" s="39">
+      <c r="O32" s="34">
+        <v>0</v>
+      </c>
+      <c r="P32" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q32" s="39">
         <v>0.60000000000000009</v>
       </c>
-      <c r="Q32" s="36">
+      <c r="R32" s="36">
         <f t="shared" si="2"/>
         <v>66752</v>
       </c>
-      <c r="R32" s="36">
-        <v>0</v>
-      </c>
       <c r="S32" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T32" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B33" s="29" t="s">
         <v>105</v>
       </c>
@@ -6080,45 +6308,48 @@
       <c r="G33" s="36">
         <v>0.5</v>
       </c>
-      <c r="H33" s="36">
-        <v>0.5</v>
+      <c r="H33" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I33" s="36">
         <v>0.5</v>
       </c>
       <c r="J33" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="K33" s="36">
         <v>3</v>
       </c>
-      <c r="K33" s="36">
+      <c r="L33" s="36">
         <v>2</v>
       </c>
-      <c r="L33" s="34">
-        <v>0</v>
-      </c>
-      <c r="M33" s="36">
+      <c r="M33" s="34">
+        <v>0</v>
+      </c>
+      <c r="N33" s="36">
         <v>2</v>
       </c>
-      <c r="N33" s="34">
-        <v>0</v>
-      </c>
-      <c r="O33" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="P33" s="39">
+      <c r="O33" s="34">
+        <v>0</v>
+      </c>
+      <c r="P33" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q33" s="39">
         <v>0.6</v>
       </c>
-      <c r="Q33" s="36">
+      <c r="R33" s="36">
         <f t="shared" si="2"/>
         <v>1400</v>
       </c>
-      <c r="R33" s="36">
-        <v>0</v>
-      </c>
       <c r="S33" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T33" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B34" s="29" t="s">
         <v>106</v>
       </c>
@@ -6138,45 +6369,48 @@
       <c r="G34" s="36">
         <v>0.5</v>
       </c>
-      <c r="H34" s="36">
-        <v>0.5</v>
+      <c r="H34" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I34" s="36">
         <v>0.5</v>
       </c>
       <c r="J34" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="K34" s="36">
         <v>3</v>
       </c>
-      <c r="K34" s="36">
+      <c r="L34" s="36">
         <v>2</v>
       </c>
-      <c r="L34" s="34">
-        <v>0</v>
-      </c>
-      <c r="M34" s="36">
+      <c r="M34" s="34">
+        <v>0</v>
+      </c>
+      <c r="N34" s="36">
         <v>2</v>
       </c>
-      <c r="N34" s="34">
-        <v>0</v>
-      </c>
-      <c r="O34" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="P34" s="39">
+      <c r="O34" s="34">
+        <v>0</v>
+      </c>
+      <c r="P34" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q34" s="39">
         <v>0.57499999999999996</v>
       </c>
-      <c r="Q34" s="36">
+      <c r="R34" s="36">
         <f t="shared" si="2"/>
         <v>47040</v>
       </c>
-      <c r="R34" s="36">
-        <v>0</v>
-      </c>
       <c r="S34" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T34" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B35" s="29" t="s">
         <v>107</v>
       </c>
@@ -6196,45 +6430,48 @@
       <c r="G35" s="36">
         <v>0.5</v>
       </c>
-      <c r="H35" s="36">
-        <v>0.5</v>
+      <c r="H35" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I35" s="36">
         <v>0.5</v>
       </c>
       <c r="J35" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="K35" s="36">
         <v>3</v>
       </c>
-      <c r="K35" s="36">
+      <c r="L35" s="36">
         <v>2</v>
       </c>
-      <c r="L35" s="34">
-        <v>0</v>
-      </c>
-      <c r="M35" s="36">
+      <c r="M35" s="34">
+        <v>0</v>
+      </c>
+      <c r="N35" s="36">
         <v>2</v>
       </c>
-      <c r="N35" s="34">
-        <v>0</v>
-      </c>
-      <c r="O35" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="P35" s="39">
+      <c r="O35" s="34">
+        <v>0</v>
+      </c>
+      <c r="P35" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q35" s="39">
         <v>0.59999999999999987</v>
       </c>
-      <c r="Q35" s="36">
+      <c r="R35" s="36">
         <f t="shared" si="2"/>
         <v>42440</v>
       </c>
-      <c r="R35" s="36">
-        <v>0</v>
-      </c>
       <c r="S35" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T35" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B36" s="29" t="s">
         <v>109</v>
       </c>
@@ -6254,45 +6491,48 @@
       <c r="G36" s="36">
         <v>0.5</v>
       </c>
-      <c r="H36" s="36">
-        <v>0.5</v>
+      <c r="H36" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I36" s="36">
         <v>0.5</v>
       </c>
       <c r="J36" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="K36" s="36">
         <v>3</v>
       </c>
-      <c r="K36" s="36">
+      <c r="L36" s="36">
         <v>2</v>
       </c>
-      <c r="L36" s="34">
-        <v>0</v>
-      </c>
-      <c r="M36" s="36">
+      <c r="M36" s="34">
+        <v>0</v>
+      </c>
+      <c r="N36" s="36">
         <v>2</v>
       </c>
-      <c r="N36" s="34">
-        <v>0</v>
-      </c>
-      <c r="O36" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="P36" s="39">
+      <c r="O36" s="34">
+        <v>0</v>
+      </c>
+      <c r="P36" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q36" s="39">
         <v>0.59999999999999987</v>
       </c>
-      <c r="Q36" s="36">
+      <c r="R36" s="36">
         <f t="shared" si="2"/>
         <v>3360</v>
       </c>
-      <c r="R36" s="36">
-        <v>0</v>
-      </c>
       <c r="S36" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T36" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B37" s="29" t="s">
         <v>110</v>
       </c>
@@ -6312,45 +6552,48 @@
       <c r="G37" s="36">
         <v>0.5</v>
       </c>
-      <c r="H37" s="36">
-        <v>0.5</v>
+      <c r="H37" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I37" s="36">
         <v>0.5</v>
       </c>
       <c r="J37" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="K37" s="36">
         <v>3</v>
       </c>
-      <c r="K37" s="36">
+      <c r="L37" s="36">
         <v>2</v>
       </c>
-      <c r="L37" s="34">
-        <v>0</v>
-      </c>
-      <c r="M37" s="36">
+      <c r="M37" s="34">
+        <v>0</v>
+      </c>
+      <c r="N37" s="36">
         <v>2</v>
       </c>
-      <c r="N37" s="34">
-        <v>0</v>
-      </c>
-      <c r="O37" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="P37" s="39">
+      <c r="O37" s="34">
+        <v>0</v>
+      </c>
+      <c r="P37" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q37" s="39">
         <v>0.58211764705882352</v>
       </c>
-      <c r="Q37" s="36">
+      <c r="R37" s="36">
         <f t="shared" si="2"/>
         <v>37400</v>
       </c>
-      <c r="R37" s="36">
-        <v>0</v>
-      </c>
       <c r="S37" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T37" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B38" s="29" t="s">
         <v>112</v>
       </c>
@@ -6370,45 +6613,48 @@
       <c r="G38" s="36">
         <v>0.5</v>
       </c>
-      <c r="H38" s="36">
-        <v>0.5</v>
+      <c r="H38" s="52" t="b">
+        <v>1</v>
       </c>
       <c r="I38" s="36">
         <v>0.5</v>
       </c>
       <c r="J38" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="K38" s="36">
         <v>3</v>
       </c>
-      <c r="K38" s="36">
+      <c r="L38" s="36">
         <v>2</v>
       </c>
-      <c r="L38" s="34">
-        <v>0</v>
-      </c>
-      <c r="M38" s="36">
+      <c r="M38" s="34">
+        <v>0</v>
+      </c>
+      <c r="N38" s="36">
         <v>2</v>
       </c>
-      <c r="N38" s="34">
-        <v>0</v>
-      </c>
-      <c r="O38" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="P38" s="39">
+      <c r="O38" s="34">
+        <v>0</v>
+      </c>
+      <c r="P38" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q38" s="39">
         <v>0.6</v>
       </c>
-      <c r="Q38" s="36">
+      <c r="R38" s="36">
         <f t="shared" si="2"/>
         <v>37200</v>
       </c>
-      <c r="R38" s="36">
-        <v>0</v>
-      </c>
       <c r="S38" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T38" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B39" s="26" t="s">
         <v>66</v>
       </c>
@@ -6427,8 +6673,8 @@
       <c r="G39" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="H39" s="35" t="s">
-        <v>142</v>
+      <c r="H39" s="52" t="b">
+        <v>0</v>
       </c>
       <c r="I39" s="35" t="s">
         <v>142</v>
@@ -6448,23 +6694,26 @@
       <c r="N39" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="O39" s="26">
-        <v>0</v>
+      <c r="O39" s="35" t="s">
+        <v>142</v>
       </c>
       <c r="P39" s="26">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="26">
         <v>0.9</v>
       </c>
-      <c r="Q39" s="35" t="s">
-        <v>142</v>
-      </c>
       <c r="R39" s="35" t="s">
         <v>142</v>
       </c>
       <c r="S39" s="35" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="40" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T39" s="35" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="40" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B40" s="26" t="s">
         <v>72</v>
       </c>
@@ -6483,8 +6732,8 @@
       <c r="G40" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="H40" s="35" t="s">
-        <v>142</v>
+      <c r="H40" s="52" t="b">
+        <v>0</v>
       </c>
       <c r="I40" s="35" t="s">
         <v>142</v>
@@ -6504,23 +6753,26 @@
       <c r="N40" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="O40" s="26">
-        <v>0</v>
+      <c r="O40" s="35" t="s">
+        <v>142</v>
       </c>
       <c r="P40" s="26">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="26">
         <v>0.9</v>
       </c>
-      <c r="Q40" s="35" t="s">
-        <v>142</v>
-      </c>
       <c r="R40" s="35" t="s">
         <v>142</v>
       </c>
       <c r="S40" s="35" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="41" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T40" s="35" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="41" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B41" s="26" t="s">
         <v>76</v>
       </c>
@@ -6539,8 +6791,8 @@
       <c r="G41" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="H41" s="35" t="s">
-        <v>142</v>
+      <c r="H41" s="52" t="b">
+        <v>0</v>
       </c>
       <c r="I41" s="35" t="s">
         <v>142</v>
@@ -6560,23 +6812,26 @@
       <c r="N41" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="O41" s="26">
-        <v>0</v>
+      <c r="O41" s="35" t="s">
+        <v>142</v>
       </c>
       <c r="P41" s="26">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="26">
         <v>0.9</v>
       </c>
-      <c r="Q41" s="35" t="s">
-        <v>142</v>
-      </c>
       <c r="R41" s="35" t="s">
         <v>142</v>
       </c>
       <c r="S41" s="35" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T41" s="35" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B42" s="26" t="s">
         <v>78</v>
       </c>
@@ -6595,8 +6850,8 @@
       <c r="G42" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="H42" s="35" t="s">
-        <v>142</v>
+      <c r="H42" s="52" t="b">
+        <v>0</v>
       </c>
       <c r="I42" s="35" t="s">
         <v>142</v>
@@ -6616,23 +6871,26 @@
       <c r="N42" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="O42" s="26">
-        <v>0</v>
+      <c r="O42" s="35" t="s">
+        <v>142</v>
       </c>
       <c r="P42" s="26">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="26">
         <v>0.9</v>
       </c>
-      <c r="Q42" s="35" t="s">
-        <v>142</v>
-      </c>
       <c r="R42" s="35" t="s">
         <v>142</v>
       </c>
       <c r="S42" s="35" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T42" s="35" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B43" s="26" t="s">
         <v>83</v>
       </c>
@@ -6651,8 +6909,8 @@
       <c r="G43" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="H43" s="35" t="s">
-        <v>142</v>
+      <c r="H43" s="52" t="b">
+        <v>0</v>
       </c>
       <c r="I43" s="35" t="s">
         <v>142</v>
@@ -6672,23 +6930,26 @@
       <c r="N43" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="O43" s="26">
-        <v>0</v>
+      <c r="O43" s="35" t="s">
+        <v>142</v>
       </c>
       <c r="P43" s="26">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="26">
         <v>0.9</v>
       </c>
-      <c r="Q43" s="35" t="s">
-        <v>142</v>
-      </c>
       <c r="R43" s="35" t="s">
         <v>142</v>
       </c>
       <c r="S43" s="35" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T43" s="35" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B44" s="26" t="s">
         <v>85</v>
       </c>
@@ -6707,8 +6968,8 @@
       <c r="G44" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="H44" s="35" t="s">
-        <v>142</v>
+      <c r="H44" s="52" t="b">
+        <v>0</v>
       </c>
       <c r="I44" s="35" t="s">
         <v>142</v>
@@ -6728,23 +6989,26 @@
       <c r="N44" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="O44" s="26">
-        <v>0</v>
+      <c r="O44" s="35" t="s">
+        <v>142</v>
       </c>
       <c r="P44" s="26">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="26">
         <v>0.9</v>
       </c>
-      <c r="Q44" s="35" t="s">
-        <v>142</v>
-      </c>
       <c r="R44" s="35" t="s">
         <v>142</v>
       </c>
       <c r="S44" s="35" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T44" s="35" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B45" s="26" t="s">
         <v>91</v>
       </c>
@@ -6763,8 +7027,8 @@
       <c r="G45" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="H45" s="35" t="s">
-        <v>142</v>
+      <c r="H45" s="52" t="b">
+        <v>0</v>
       </c>
       <c r="I45" s="35" t="s">
         <v>142</v>
@@ -6784,23 +7048,26 @@
       <c r="N45" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="O45" s="26">
-        <v>0</v>
+      <c r="O45" s="35" t="s">
+        <v>142</v>
       </c>
       <c r="P45" s="26">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="26">
         <v>0.9</v>
       </c>
-      <c r="Q45" s="35" t="s">
-        <v>142</v>
-      </c>
       <c r="R45" s="35" t="s">
         <v>142</v>
       </c>
       <c r="S45" s="35" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T45" s="35" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B46" s="26" t="s">
         <v>95</v>
       </c>
@@ -6819,8 +7086,8 @@
       <c r="G46" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="H46" s="35" t="s">
-        <v>142</v>
+      <c r="H46" s="52" t="b">
+        <v>0</v>
       </c>
       <c r="I46" s="35" t="s">
         <v>142</v>
@@ -6840,23 +7107,26 @@
       <c r="N46" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="O46" s="26">
-        <v>0</v>
+      <c r="O46" s="35" t="s">
+        <v>142</v>
       </c>
       <c r="P46" s="26">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="26">
         <v>0.9</v>
       </c>
-      <c r="Q46" s="35" t="s">
-        <v>142</v>
-      </c>
       <c r="R46" s="35" t="s">
         <v>142</v>
       </c>
       <c r="S46" s="35" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T46" s="35" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B47" s="26" t="s">
         <v>107</v>
       </c>
@@ -6875,8 +7145,8 @@
       <c r="G47" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="H47" s="35" t="s">
-        <v>142</v>
+      <c r="H47" s="52" t="b">
+        <v>0</v>
       </c>
       <c r="I47" s="35" t="s">
         <v>142</v>
@@ -6896,23 +7166,26 @@
       <c r="N47" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="O47" s="26">
-        <v>0</v>
+      <c r="O47" s="35" t="s">
+        <v>142</v>
       </c>
       <c r="P47" s="26">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="26">
         <v>0.9</v>
       </c>
-      <c r="Q47" s="35" t="s">
-        <v>142</v>
-      </c>
       <c r="R47" s="35" t="s">
         <v>142</v>
       </c>
       <c r="S47" s="35" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T47" s="35" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B48" s="26" t="s">
         <v>108</v>
       </c>
@@ -6931,8 +7204,8 @@
       <c r="G48" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="H48" s="35" t="s">
-        <v>142</v>
+      <c r="H48" s="52" t="b">
+        <v>0</v>
       </c>
       <c r="I48" s="35" t="s">
         <v>142</v>
@@ -6952,23 +7225,26 @@
       <c r="N48" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="O48" s="26">
-        <v>0</v>
+      <c r="O48" s="35" t="s">
+        <v>142</v>
       </c>
       <c r="P48" s="26">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="26">
         <v>0.9</v>
       </c>
-      <c r="Q48" s="35" t="s">
-        <v>142</v>
-      </c>
       <c r="R48" s="35" t="s">
         <v>142</v>
       </c>
       <c r="S48" s="35" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="49" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T48" s="35" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="49" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B49" s="26" t="s">
         <v>111</v>
       </c>
@@ -6987,8 +7263,8 @@
       <c r="G49" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H49" s="28" t="s">
-        <v>142</v>
+      <c r="H49" s="52" t="b">
+        <v>0</v>
       </c>
       <c r="I49" s="28" t="s">
         <v>142</v>
@@ -7008,23 +7284,26 @@
       <c r="N49" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="O49" s="26">
-        <v>0</v>
+      <c r="O49" s="28" t="s">
+        <v>142</v>
       </c>
       <c r="P49" s="26">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="26">
         <v>0.9</v>
       </c>
-      <c r="Q49" s="28" t="s">
-        <v>142</v>
-      </c>
       <c r="R49" s="28" t="s">
         <v>142</v>
       </c>
       <c r="S49" s="28" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="50" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T49" s="28" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="50" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B50" s="26" t="s">
         <v>113</v>
       </c>
@@ -7043,8 +7322,8 @@
       <c r="G50" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H50" s="28" t="s">
-        <v>142</v>
+      <c r="H50" s="52" t="b">
+        <v>0</v>
       </c>
       <c r="I50" s="28" t="s">
         <v>142</v>
@@ -7064,23 +7343,26 @@
       <c r="N50" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="O50" s="26">
-        <v>0</v>
+      <c r="O50" s="28" t="s">
+        <v>142</v>
       </c>
       <c r="P50" s="26">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="26">
         <v>0.9</v>
       </c>
-      <c r="Q50" s="28" t="s">
-        <v>142</v>
-      </c>
       <c r="R50" s="28" t="s">
         <v>142</v>
       </c>
       <c r="S50" s="28" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="51" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T50" s="28" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="51" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B51" s="29" t="s">
         <v>72</v>
       </c>
@@ -7099,8 +7381,8 @@
       <c r="G51" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H51" s="28" t="s">
-        <v>142</v>
+      <c r="H51" s="52" t="b">
+        <v>0</v>
       </c>
       <c r="I51" s="28" t="s">
         <v>142</v>
@@ -7120,23 +7402,26 @@
       <c r="N51" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="O51" s="26">
+      <c r="O51" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="P51" s="26">
         <v>20</v>
       </c>
-      <c r="P51" s="29">
+      <c r="Q51" s="29">
         <v>0.46800000000000003</v>
       </c>
-      <c r="Q51" s="28" t="s">
-        <v>142</v>
-      </c>
       <c r="R51" s="28" t="s">
         <v>142</v>
       </c>
       <c r="S51" s="28" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="52" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T51" s="28" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="52" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B52" s="29" t="s">
         <v>76</v>
       </c>
@@ -7155,8 +7440,8 @@
       <c r="G52" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H52" s="28" t="s">
-        <v>142</v>
+      <c r="H52" s="52" t="b">
+        <v>0</v>
       </c>
       <c r="I52" s="28" t="s">
         <v>142</v>
@@ -7176,23 +7461,26 @@
       <c r="N52" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="O52" s="26">
+      <c r="O52" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="P52" s="26">
         <v>20</v>
       </c>
-      <c r="P52" s="29">
+      <c r="Q52" s="29">
         <v>0.46800000000000003</v>
       </c>
-      <c r="Q52" s="28" t="s">
-        <v>142</v>
-      </c>
       <c r="R52" s="28" t="s">
         <v>142</v>
       </c>
       <c r="S52" s="28" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="53" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T52" s="28" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="53" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B53" s="29" t="s">
         <v>83</v>
       </c>
@@ -7211,8 +7499,8 @@
       <c r="G53" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H53" s="28" t="s">
-        <v>142</v>
+      <c r="H53" s="52" t="b">
+        <v>0</v>
       </c>
       <c r="I53" s="28" t="s">
         <v>142</v>
@@ -7232,23 +7520,26 @@
       <c r="N53" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="O53" s="26">
+      <c r="O53" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="P53" s="26">
         <v>20</v>
       </c>
-      <c r="P53" s="29">
+      <c r="Q53" s="29">
         <v>0.46800000000000003</v>
       </c>
-      <c r="Q53" s="28" t="s">
-        <v>142</v>
-      </c>
       <c r="R53" s="28" t="s">
         <v>142</v>
       </c>
       <c r="S53" s="28" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="54" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T53" s="28" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="54" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B54" s="29" t="s">
         <v>84</v>
       </c>
@@ -7267,8 +7558,8 @@
       <c r="G54" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H54" s="28" t="s">
-        <v>142</v>
+      <c r="H54" s="52" t="b">
+        <v>0</v>
       </c>
       <c r="I54" s="28" t="s">
         <v>142</v>
@@ -7288,23 +7579,26 @@
       <c r="N54" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="O54" s="26">
+      <c r="O54" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="P54" s="26">
         <v>20</v>
       </c>
-      <c r="P54" s="29">
+      <c r="Q54" s="29">
         <v>0.46800000000000003</v>
       </c>
-      <c r="Q54" s="28" t="s">
-        <v>142</v>
-      </c>
       <c r="R54" s="28" t="s">
         <v>142</v>
       </c>
       <c r="S54" s="28" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="55" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T54" s="28" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="55" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B55" s="29" t="s">
         <v>90</v>
       </c>
@@ -7323,8 +7617,8 @@
       <c r="G55" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H55" s="28" t="s">
-        <v>142</v>
+      <c r="H55" s="52" t="b">
+        <v>0</v>
       </c>
       <c r="I55" s="28" t="s">
         <v>142</v>
@@ -7344,23 +7638,26 @@
       <c r="N55" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="O55" s="26">
+      <c r="O55" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="P55" s="26">
         <v>20</v>
       </c>
-      <c r="P55" s="29">
+      <c r="Q55" s="29">
         <v>0.46800000000000003</v>
       </c>
-      <c r="Q55" s="28" t="s">
-        <v>142</v>
-      </c>
       <c r="R55" s="28" t="s">
         <v>142</v>
       </c>
       <c r="S55" s="28" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="56" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T55" s="28" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="56" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B56" s="29" t="s">
         <v>92</v>
       </c>
@@ -7379,8 +7676,8 @@
       <c r="G56" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H56" s="28" t="s">
-        <v>142</v>
+      <c r="H56" s="52" t="b">
+        <v>0</v>
       </c>
       <c r="I56" s="28" t="s">
         <v>142</v>
@@ -7400,23 +7697,26 @@
       <c r="N56" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="O56" s="26">
+      <c r="O56" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="P56" s="26">
         <v>20</v>
       </c>
-      <c r="P56" s="29">
+      <c r="Q56" s="29">
         <v>0.46800000000000003</v>
       </c>
-      <c r="Q56" s="28" t="s">
-        <v>142</v>
-      </c>
       <c r="R56" s="28" t="s">
         <v>142</v>
       </c>
       <c r="S56" s="28" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="57" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T56" s="28" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="57" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B57" s="29" t="s">
         <v>93</v>
       </c>
@@ -7435,8 +7735,8 @@
       <c r="G57" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H57" s="28" t="s">
-        <v>142</v>
+      <c r="H57" s="52" t="b">
+        <v>0</v>
       </c>
       <c r="I57" s="28" t="s">
         <v>142</v>
@@ -7456,23 +7756,26 @@
       <c r="N57" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="O57" s="26">
+      <c r="O57" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="P57" s="26">
         <v>20</v>
       </c>
-      <c r="P57" s="29">
+      <c r="Q57" s="29">
         <v>0.46800000000000003</v>
       </c>
-      <c r="Q57" s="28" t="s">
-        <v>142</v>
-      </c>
       <c r="R57" s="28" t="s">
         <v>142</v>
       </c>
       <c r="S57" s="28" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="58" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T57" s="28" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="58" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B58" s="29" t="s">
         <v>97</v>
       </c>
@@ -7491,8 +7794,8 @@
       <c r="G58" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H58" s="28" t="s">
-        <v>142</v>
+      <c r="H58" s="52" t="b">
+        <v>0</v>
       </c>
       <c r="I58" s="28" t="s">
         <v>142</v>
@@ -7512,23 +7815,26 @@
       <c r="N58" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="O58" s="26">
+      <c r="O58" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="P58" s="26">
         <v>20</v>
       </c>
-      <c r="P58" s="29">
+      <c r="Q58" s="29">
         <v>0.46800000000000003</v>
       </c>
-      <c r="Q58" s="28" t="s">
-        <v>142</v>
-      </c>
       <c r="R58" s="28" t="s">
         <v>142</v>
       </c>
       <c r="S58" s="28" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="59" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T58" s="28" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="59" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B59" s="29" t="s">
         <v>102</v>
       </c>
@@ -7547,8 +7853,8 @@
       <c r="G59" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H59" s="28" t="s">
-        <v>142</v>
+      <c r="H59" s="52" t="b">
+        <v>0</v>
       </c>
       <c r="I59" s="28" t="s">
         <v>142</v>
@@ -7568,23 +7874,26 @@
       <c r="N59" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="O59" s="26">
+      <c r="O59" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="P59" s="26">
         <v>20</v>
       </c>
-      <c r="P59" s="29">
+      <c r="Q59" s="29">
         <v>0.46800000000000003</v>
       </c>
-      <c r="Q59" s="28" t="s">
-        <v>142</v>
-      </c>
       <c r="R59" s="28" t="s">
         <v>142</v>
       </c>
       <c r="S59" s="28" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="60" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T59" s="28" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="60" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B60" s="29" t="s">
         <v>104</v>
       </c>
@@ -7603,8 +7912,8 @@
       <c r="G60" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H60" s="28" t="s">
-        <v>142</v>
+      <c r="H60" s="52" t="b">
+        <v>0</v>
       </c>
       <c r="I60" s="28" t="s">
         <v>142</v>
@@ -7624,23 +7933,26 @@
       <c r="N60" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="O60" s="26">
+      <c r="O60" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="P60" s="26">
         <v>20</v>
       </c>
-      <c r="P60" s="29">
+      <c r="Q60" s="29">
         <v>0.46800000000000003</v>
       </c>
-      <c r="Q60" s="28" t="s">
-        <v>142</v>
-      </c>
       <c r="R60" s="28" t="s">
         <v>142</v>
       </c>
       <c r="S60" s="28" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="61" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T60" s="28" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="61" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B61" s="29" t="s">
         <v>106</v>
       </c>
@@ -7659,8 +7971,8 @@
       <c r="G61" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H61" s="28" t="s">
-        <v>142</v>
+      <c r="H61" s="52" t="b">
+        <v>0</v>
       </c>
       <c r="I61" s="28" t="s">
         <v>142</v>
@@ -7680,23 +7992,26 @@
       <c r="N61" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="O61" s="26">
+      <c r="O61" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="P61" s="26">
         <v>20</v>
       </c>
-      <c r="P61" s="29">
+      <c r="Q61" s="29">
         <v>0.46800000000000003</v>
       </c>
-      <c r="Q61" s="28" t="s">
-        <v>142</v>
-      </c>
       <c r="R61" s="28" t="s">
         <v>142</v>
       </c>
       <c r="S61" s="28" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="62" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T61" s="28" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="62" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B62" s="29" t="s">
         <v>107</v>
       </c>
@@ -7715,8 +8030,8 @@
       <c r="G62" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H62" s="28" t="s">
-        <v>142</v>
+      <c r="H62" s="52" t="b">
+        <v>0</v>
       </c>
       <c r="I62" s="28" t="s">
         <v>142</v>
@@ -7736,23 +8051,26 @@
       <c r="N62" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="O62" s="26">
+      <c r="O62" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="P62" s="26">
         <v>20</v>
       </c>
-      <c r="P62" s="29">
+      <c r="Q62" s="29">
         <v>0.46800000000000003</v>
       </c>
-      <c r="Q62" s="28" t="s">
-        <v>142</v>
-      </c>
       <c r="R62" s="28" t="s">
         <v>142</v>
       </c>
       <c r="S62" s="28" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="63" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T62" s="28" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="63" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B63" s="29" t="s">
         <v>110</v>
       </c>
@@ -7771,8 +8089,8 @@
       <c r="G63" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H63" s="28" t="s">
-        <v>142</v>
+      <c r="H63" s="52" t="b">
+        <v>0</v>
       </c>
       <c r="I63" s="28" t="s">
         <v>142</v>
@@ -7792,23 +8110,26 @@
       <c r="N63" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="O63" s="26">
+      <c r="O63" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="P63" s="26">
         <v>20</v>
       </c>
-      <c r="P63" s="29">
+      <c r="Q63" s="29">
         <v>0.46800000000000003</v>
       </c>
-      <c r="Q63" s="28" t="s">
-        <v>142</v>
-      </c>
       <c r="R63" s="28" t="s">
         <v>142</v>
       </c>
       <c r="S63" s="28" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="64" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T63" s="28" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="64" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B64" s="29" t="s">
         <v>111</v>
       </c>
@@ -7827,8 +8148,8 @@
       <c r="G64" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H64" s="28" t="s">
-        <v>142</v>
+      <c r="H64" s="52" t="b">
+        <v>0</v>
       </c>
       <c r="I64" s="28" t="s">
         <v>142</v>
@@ -7848,23 +8169,26 @@
       <c r="N64" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="O64" s="26">
+      <c r="O64" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="P64" s="26">
         <v>20</v>
       </c>
-      <c r="P64" s="29">
+      <c r="Q64" s="29">
         <v>0.46800000000000003</v>
       </c>
-      <c r="Q64" s="28" t="s">
-        <v>142</v>
-      </c>
       <c r="R64" s="28" t="s">
         <v>142</v>
       </c>
       <c r="S64" s="28" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="T64" s="28" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" ht="19" x14ac:dyDescent="0.25">
       <c r="B65" s="29" t="s">
         <v>112</v>
       </c>
@@ -7883,8 +8207,8 @@
       <c r="G65" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H65" s="28" t="s">
-        <v>142</v>
+      <c r="H65" s="52" t="b">
+        <v>0</v>
       </c>
       <c r="I65" s="28" t="s">
         <v>142</v>
@@ -7904,28 +8228,36 @@
       <c r="N65" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="O65" s="26">
+      <c r="O65" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="P65" s="26">
         <v>20</v>
       </c>
-      <c r="P65" s="29">
+      <c r="Q65" s="29">
         <v>0.46800000000000003</v>
       </c>
-      <c r="Q65" s="28" t="s">
-        <v>142</v>
-      </c>
       <c r="R65" s="28" t="s">
         <v>142</v>
       </c>
       <c r="S65" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="T65" s="28" t="s">
         <v>142</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="D2:E2"/>
-    <mergeCell ref="O2:S2"/>
-    <mergeCell ref="F2:N2"/>
+    <mergeCell ref="P2:T2"/>
+    <mergeCell ref="F2:O2"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:H1048576" xr:uid="{EF8947E4-428C-CB40-B402-6A23154DA0B3}">
+      <formula1>"True, False"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -7951,34 +8283,34 @@
   <sheetData>
     <row r="1" spans="2:28" ht="58" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="H2" s="47" t="s">
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="H2" s="48" t="s">
         <v>123</v>
       </c>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
-      <c r="M2" s="47"/>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
-      <c r="W2" s="47"/>
-      <c r="X2" s="47"/>
-      <c r="Y2" s="47"/>
-      <c r="Z2" s="47"/>
-      <c r="AA2" s="47"/>
-      <c r="AB2" s="47"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
+      <c r="W2" s="48"/>
+      <c r="X2" s="48"/>
+      <c r="Y2" s="48"/>
+      <c r="Z2" s="48"/>
+      <c r="AA2" s="48"/>
+      <c r="AB2" s="48"/>
     </row>
     <row r="3" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B3" s="5" t="s">
@@ -9175,29 +9507,29 @@
       <c r="E19" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H19" s="47" t="s">
+      <c r="H19" s="48" t="s">
         <v>122</v>
       </c>
-      <c r="I19" s="47"/>
-      <c r="J19" s="47"/>
-      <c r="K19" s="47"/>
-      <c r="L19" s="47"/>
-      <c r="M19" s="47"/>
-      <c r="N19" s="47"/>
-      <c r="O19" s="47"/>
-      <c r="P19" s="47"/>
-      <c r="Q19" s="47"/>
-      <c r="R19" s="47"/>
-      <c r="S19" s="47"/>
-      <c r="T19" s="47"/>
-      <c r="U19" s="47"/>
-      <c r="V19" s="47"/>
-      <c r="W19" s="47"/>
-      <c r="X19" s="47"/>
-      <c r="Y19" s="47"/>
-      <c r="Z19" s="47"/>
-      <c r="AA19" s="47"/>
-      <c r="AB19" s="47"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="48"/>
+      <c r="O19" s="48"/>
+      <c r="P19" s="48"/>
+      <c r="Q19" s="48"/>
+      <c r="R19" s="48"/>
+      <c r="S19" s="48"/>
+      <c r="T19" s="48"/>
+      <c r="U19" s="48"/>
+      <c r="V19" s="48"/>
+      <c r="W19" s="48"/>
+      <c r="X19" s="48"/>
+      <c r="Y19" s="48"/>
+      <c r="Z19" s="48"/>
+      <c r="AA19" s="48"/>
+      <c r="AB19" s="48"/>
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
@@ -11324,20 +11656,20 @@
     </row>
     <row r="2" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B2"/>
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="47"/>
       <c r="O2" s="45"/>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.2">
@@ -12888,283 +13220,126 @@
       </c>
     </row>
     <row r="56" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B56" s="42" t="s">
-        <v>113</v>
-      </c>
-      <c r="C56" s="42">
-        <v>1000</v>
-      </c>
-      <c r="D56" s="2">
-        <v>1112139.5039971056</v>
-      </c>
-      <c r="E56" s="42">
-        <v>0.9</v>
-      </c>
-      <c r="F56" s="42">
-        <v>0.9</v>
-      </c>
+      <c r="B56" s="42"/>
+      <c r="C56" s="42"/>
+      <c r="E56" s="42"/>
+      <c r="F56" s="42"/>
       <c r="G56" s="43"/>
-      <c r="H56" s="44">
-        <v>1</v>
-      </c>
+      <c r="H56" s="44"/>
       <c r="I56" s="42"/>
       <c r="J56" s="43"/>
-      <c r="K56" s="44" t="s">
-        <v>146</v>
-      </c>
+      <c r="K56" s="44"/>
       <c r="L56" s="42"/>
       <c r="M56" s="42"/>
-      <c r="N56" s="42" t="s">
-        <v>149</v>
-      </c>
+      <c r="N56" s="42"/>
     </row>
     <row r="57" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B57" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C57" s="2">
-        <v>547.01</v>
-      </c>
-      <c r="D57" s="2">
-        <v>86000</v>
-      </c>
-      <c r="E57" s="42">
-        <v>0.9</v>
-      </c>
-      <c r="F57" s="42">
-        <v>0.9</v>
-      </c>
+      <c r="B57" s="2"/>
+      <c r="E57" s="42"/>
+      <c r="F57" s="42"/>
       <c r="G57" s="43"/>
-      <c r="H57" s="44">
-        <v>1</v>
-      </c>
+      <c r="H57" s="44"/>
       <c r="I57" s="42"/>
       <c r="J57" s="43"/>
-      <c r="K57" s="44" t="s">
-        <v>146</v>
-      </c>
+      <c r="K57" s="44"/>
       <c r="L57" s="42"/>
       <c r="M57" s="42"/>
-      <c r="N57" s="42" t="s">
-        <v>149</v>
-      </c>
+      <c r="N57" s="42"/>
     </row>
     <row r="58" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B58" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C58" s="2">
-        <v>1509</v>
-      </c>
-      <c r="D58" s="2">
-        <v>279000</v>
-      </c>
-      <c r="E58" s="42">
-        <v>0.9</v>
-      </c>
-      <c r="F58" s="42">
-        <v>0.9</v>
-      </c>
+      <c r="B58" s="2"/>
+      <c r="E58" s="42"/>
+      <c r="F58" s="42"/>
       <c r="G58" s="43"/>
-      <c r="H58" s="44">
-        <v>1</v>
-      </c>
+      <c r="H58" s="44"/>
       <c r="I58" s="42"/>
       <c r="J58" s="43"/>
-      <c r="K58" s="44" t="s">
-        <v>146</v>
-      </c>
+      <c r="K58" s="44"/>
       <c r="L58" s="42"/>
       <c r="M58" s="42"/>
-      <c r="N58" s="42" t="s">
-        <v>149</v>
-      </c>
+      <c r="N58" s="42"/>
     </row>
     <row r="59" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B59" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C59" s="2">
-        <v>498</v>
-      </c>
-      <c r="D59" s="2">
-        <v>251999.99999999997</v>
-      </c>
-      <c r="E59" s="42">
-        <v>0.9</v>
-      </c>
-      <c r="F59" s="42">
-        <v>0.9</v>
-      </c>
+      <c r="B59" s="2"/>
+      <c r="E59" s="42"/>
+      <c r="F59" s="42"/>
       <c r="G59" s="43"/>
-      <c r="H59" s="44">
-        <v>1</v>
-      </c>
+      <c r="H59" s="44"/>
       <c r="I59" s="42"/>
       <c r="J59" s="43"/>
-      <c r="K59" s="44" t="s">
-        <v>146</v>
-      </c>
+      <c r="K59" s="44"/>
       <c r="L59" s="42"/>
       <c r="M59" s="42"/>
-      <c r="N59" s="42" t="s">
-        <v>149</v>
-      </c>
+      <c r="N59" s="42"/>
     </row>
     <row r="60" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B60" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C60" s="2">
-        <v>1458.96</v>
-      </c>
-      <c r="D60" s="2">
-        <v>48842.314624378821</v>
-      </c>
-      <c r="E60" s="42">
-        <v>0.9</v>
-      </c>
-      <c r="F60" s="42">
-        <v>0.9</v>
-      </c>
+      <c r="B60" s="2"/>
+      <c r="E60" s="42"/>
+      <c r="F60" s="42"/>
       <c r="G60" s="43"/>
-      <c r="H60" s="44">
-        <v>1</v>
-      </c>
+      <c r="H60" s="44"/>
       <c r="I60" s="42"/>
       <c r="J60" s="43"/>
-      <c r="K60" s="44" t="s">
-        <v>146</v>
-      </c>
+      <c r="K60" s="44"/>
       <c r="L60" s="42"/>
       <c r="M60" s="42"/>
-      <c r="N60" s="42" t="s">
-        <v>149</v>
-      </c>
+      <c r="N60" s="42"/>
     </row>
     <row r="61" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B61" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C61" s="2">
-        <v>113.85</v>
-      </c>
-      <c r="D61" s="42">
-        <v>115599.99999999997</v>
-      </c>
-      <c r="E61" s="42">
-        <v>0.9</v>
-      </c>
-      <c r="F61" s="42">
-        <v>0.9</v>
-      </c>
+      <c r="B61" s="2"/>
+      <c r="D61" s="42"/>
+      <c r="E61" s="42"/>
+      <c r="F61" s="42"/>
       <c r="G61" s="43"/>
-      <c r="H61" s="44">
-        <v>1</v>
-      </c>
+      <c r="H61" s="44"/>
       <c r="I61" s="42"/>
       <c r="J61" s="43"/>
-      <c r="K61" s="44" t="s">
-        <v>146</v>
-      </c>
+      <c r="K61" s="44"/>
       <c r="L61" s="42"/>
       <c r="M61" s="42"/>
-      <c r="N61" s="42" t="s">
-        <v>149</v>
-      </c>
+      <c r="N61" s="42"/>
     </row>
     <row r="62" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B62" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C62" s="2">
-        <v>15</v>
-      </c>
-      <c r="D62" s="42">
-        <v>115599.99999999997</v>
-      </c>
-      <c r="E62" s="42">
-        <v>0.9</v>
-      </c>
-      <c r="F62" s="42">
-        <v>0.9</v>
-      </c>
+      <c r="B62" s="2"/>
+      <c r="D62" s="42"/>
+      <c r="E62" s="42"/>
+      <c r="F62" s="42"/>
       <c r="G62" s="43"/>
-      <c r="H62" s="44">
-        <v>1</v>
-      </c>
+      <c r="H62" s="44"/>
       <c r="I62" s="42"/>
       <c r="J62" s="43"/>
-      <c r="K62" s="44" t="s">
-        <v>146</v>
-      </c>
+      <c r="K62" s="44"/>
       <c r="L62" s="42"/>
       <c r="M62" s="42"/>
-      <c r="N62" s="42" t="s">
-        <v>149</v>
-      </c>
+      <c r="N62" s="42"/>
     </row>
     <row r="63" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B63" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C63" s="2">
-        <v>161.85</v>
-      </c>
-      <c r="D63" s="2">
-        <v>905.99999999999977</v>
-      </c>
-      <c r="E63" s="42">
-        <v>0.9</v>
-      </c>
-      <c r="F63" s="42">
-        <v>0.9</v>
-      </c>
+      <c r="B63" s="2"/>
+      <c r="E63" s="42"/>
+      <c r="F63" s="42"/>
       <c r="G63" s="43"/>
-      <c r="H63" s="44">
-        <v>1</v>
-      </c>
+      <c r="H63" s="44"/>
       <c r="I63" s="42"/>
       <c r="J63" s="43"/>
-      <c r="K63" s="44" t="s">
-        <v>146</v>
-      </c>
+      <c r="K63" s="44"/>
       <c r="L63" s="42"/>
       <c r="M63" s="42"/>
-      <c r="N63" s="42" t="s">
-        <v>149</v>
-      </c>
+      <c r="N63" s="42"/>
     </row>
     <row r="64" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B64" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C64" s="42">
-        <v>1000</v>
-      </c>
-      <c r="D64" s="42">
-        <v>115599.99999999997</v>
-      </c>
-      <c r="E64" s="42">
-        <v>0.9</v>
-      </c>
-      <c r="F64" s="42">
-        <v>0.9</v>
-      </c>
+      <c r="B64" s="2"/>
+      <c r="C64" s="42"/>
+      <c r="D64" s="42"/>
+      <c r="E64" s="42"/>
+      <c r="F64" s="42"/>
       <c r="G64" s="43"/>
-      <c r="H64" s="44">
-        <v>1</v>
-      </c>
+      <c r="H64" s="44"/>
       <c r="I64" s="42"/>
       <c r="J64" s="43"/>
-      <c r="K64" s="44" t="s">
-        <v>146</v>
-      </c>
+      <c r="K64" s="44"/>
       <c r="L64" s="42"/>
       <c r="M64" s="42"/>
-      <c r="N64" s="42" t="s">
-        <v>149</v>
-      </c>
+      <c r="N64" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -13184,4 +13359,1926 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7B60DB5-92C9-F245-B244-7CC76E316208}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87ED3F32-2AFE-4D4A-9596-D39A8243454D}">
+  <dimension ref="A1:W36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="46" t="s">
+        <v>149</v>
+      </c>
+      <c r="B1" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="C1" s="46" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1" s="46" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>166</v>
+      </c>
+      <c r="B7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>167</v>
+      </c>
+      <c r="B8" t="s">
+        <v>168</v>
+      </c>
+      <c r="C8" t="s">
+        <v>169</v>
+      </c>
+      <c r="D8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>170</v>
+      </c>
+      <c r="B9" t="s">
+        <v>160</v>
+      </c>
+      <c r="C9" t="s">
+        <v>171</v>
+      </c>
+      <c r="D9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>172</v>
+      </c>
+      <c r="B10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C10" t="s">
+        <v>173</v>
+      </c>
+      <c r="D10" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>174</v>
+      </c>
+      <c r="B11" t="s">
+        <v>154</v>
+      </c>
+      <c r="C11" t="s">
+        <v>175</v>
+      </c>
+      <c r="D11" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>177</v>
+      </c>
+      <c r="B12" t="s">
+        <v>178</v>
+      </c>
+      <c r="C12" t="s">
+        <v>179</v>
+      </c>
+      <c r="D12" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>180</v>
+      </c>
+      <c r="B13" t="s">
+        <v>178</v>
+      </c>
+      <c r="C13" t="s">
+        <v>181</v>
+      </c>
+      <c r="D13" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>182</v>
+      </c>
+      <c r="B14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C14" t="s">
+        <v>183</v>
+      </c>
+      <c r="D14" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="17" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="18" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="19" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="24" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="C24" s="48" t="s">
+        <v>123</v>
+      </c>
+      <c r="D24" s="48"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="48"/>
+      <c r="H24" s="48"/>
+      <c r="I24" s="48"/>
+      <c r="J24" s="48"/>
+      <c r="K24" s="48"/>
+      <c r="L24" s="48"/>
+      <c r="M24" s="48"/>
+      <c r="N24" s="48"/>
+      <c r="O24" s="48"/>
+      <c r="P24" s="48"/>
+      <c r="Q24" s="48"/>
+      <c r="R24" s="48"/>
+      <c r="S24" s="48"/>
+      <c r="T24" s="48"/>
+      <c r="U24" s="48"/>
+      <c r="V24" s="48"/>
+      <c r="W24" s="48"/>
+    </row>
+    <row r="25" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B25" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="H25" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="I25" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J25" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="K25" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="L25" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="M25" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="N25" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="O25" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="P25" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q25" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="R25" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="S25" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="T25" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="U25" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="V25" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="W25" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B26" s="2">
+        <v>2015</v>
+      </c>
+      <c r="C26" s="2">
+        <v>48</v>
+      </c>
+      <c r="D26" s="2">
+        <v>66</v>
+      </c>
+      <c r="E26" s="2">
+        <v>91</v>
+      </c>
+      <c r="F26" s="2">
+        <v>156</v>
+      </c>
+      <c r="G26" s="2">
+        <v>50</v>
+      </c>
+      <c r="H26" s="19">
+        <v>16.083600000000001</v>
+      </c>
+      <c r="I26" s="19">
+        <v>0.76319999999999999</v>
+      </c>
+      <c r="J26" s="19">
+        <v>2.0488</v>
+      </c>
+      <c r="K26" s="19">
+        <v>25.8901</v>
+      </c>
+      <c r="L26" s="19">
+        <v>161.17490000000001</v>
+      </c>
+      <c r="M26" s="19">
+        <v>85.712400000000002</v>
+      </c>
+      <c r="N26" s="19">
+        <v>167.51240000000001</v>
+      </c>
+      <c r="O26" s="19">
+        <v>65.737099999999998</v>
+      </c>
+      <c r="P26" s="19">
+        <v>493.36219999999997</v>
+      </c>
+      <c r="Q26" s="19">
+        <v>923.55949999999996</v>
+      </c>
+      <c r="R26" s="19">
+        <v>560.58230000000003</v>
+      </c>
+      <c r="S26" s="19">
+        <v>263.7106</v>
+      </c>
+      <c r="T26" s="19">
+        <v>348.24430000000001</v>
+      </c>
+      <c r="U26" s="19">
+        <v>867.77689999999996</v>
+      </c>
+      <c r="V26" s="19">
+        <v>438.03469999999999</v>
+      </c>
+      <c r="W26" s="19">
+        <v>5.79E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B27" s="2">
+        <v>2016</v>
+      </c>
+      <c r="C27" s="20">
+        <v>70</v>
+      </c>
+      <c r="D27" s="20">
+        <v>87</v>
+      </c>
+      <c r="E27" s="20">
+        <v>100</v>
+      </c>
+      <c r="F27" s="20">
+        <v>177</v>
+      </c>
+      <c r="G27" s="20">
+        <v>57</v>
+      </c>
+      <c r="H27" s="2">
+        <v>16.083600000000001</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0.7732</v>
+      </c>
+      <c r="J27" s="2">
+        <v>2.0488</v>
+      </c>
+      <c r="K27" s="2">
+        <v>26.026</v>
+      </c>
+      <c r="L27" s="2">
+        <v>161.18289999999999</v>
+      </c>
+      <c r="M27" s="2">
+        <v>85.712400000000002</v>
+      </c>
+      <c r="N27" s="2">
+        <v>167.51240000000001</v>
+      </c>
+      <c r="O27" s="2">
+        <v>65.737099999999998</v>
+      </c>
+      <c r="P27" s="2">
+        <v>493.36869999999999</v>
+      </c>
+      <c r="Q27" s="2">
+        <v>923.55949999999996</v>
+      </c>
+      <c r="R27" s="2">
+        <v>561.08230000000003</v>
+      </c>
+      <c r="S27" s="2">
+        <v>265.233</v>
+      </c>
+      <c r="T27" s="2">
+        <v>348.33929999999998</v>
+      </c>
+      <c r="U27" s="2">
+        <v>871.71040000000005</v>
+      </c>
+      <c r="V27" s="2">
+        <v>438.03469999999999</v>
+      </c>
+      <c r="W27" s="2">
+        <v>5.79E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B28" s="2">
+        <v>2017</v>
+      </c>
+      <c r="C28" s="20">
+        <v>88</v>
+      </c>
+      <c r="D28" s="20">
+        <v>102</v>
+      </c>
+      <c r="E28" s="20">
+        <v>106</v>
+      </c>
+      <c r="F28" s="20">
+        <v>197</v>
+      </c>
+      <c r="G28" s="20">
+        <v>61</v>
+      </c>
+      <c r="H28" s="2">
+        <v>16.2136</v>
+      </c>
+      <c r="I28" s="2">
+        <v>0.7732</v>
+      </c>
+      <c r="J28" s="2">
+        <v>2.0488</v>
+      </c>
+      <c r="K28" s="2">
+        <v>26.026</v>
+      </c>
+      <c r="L28" s="2">
+        <v>161.18889999999999</v>
+      </c>
+      <c r="M28" s="2">
+        <v>85.712400000000002</v>
+      </c>
+      <c r="N28" s="2">
+        <v>167.59440000000001</v>
+      </c>
+      <c r="O28" s="2">
+        <v>66.237099999999998</v>
+      </c>
+      <c r="P28" s="2">
+        <v>493.61829999999998</v>
+      </c>
+      <c r="Q28" s="2">
+        <v>924.60550000000001</v>
+      </c>
+      <c r="R28" s="2">
+        <v>561.23230000000001</v>
+      </c>
+      <c r="S28" s="2">
+        <v>265.6748</v>
+      </c>
+      <c r="T28" s="2">
+        <v>348.38830000000002</v>
+      </c>
+      <c r="U28" s="2">
+        <v>872.44929999999999</v>
+      </c>
+      <c r="V28" s="2">
+        <v>438.03469999999999</v>
+      </c>
+      <c r="W28" s="2">
+        <v>5.79E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B29" s="2">
+        <v>2018</v>
+      </c>
+      <c r="C29" s="20">
+        <v>104</v>
+      </c>
+      <c r="D29" s="20">
+        <v>116</v>
+      </c>
+      <c r="E29" s="20">
+        <v>112</v>
+      </c>
+      <c r="F29" s="20">
+        <v>248</v>
+      </c>
+      <c r="G29" s="20">
+        <v>66</v>
+      </c>
+      <c r="H29" s="2">
+        <v>16.2136</v>
+      </c>
+      <c r="I29" s="2">
+        <v>0.7732</v>
+      </c>
+      <c r="J29" s="2">
+        <v>2.0488</v>
+      </c>
+      <c r="K29" s="2">
+        <v>26.026</v>
+      </c>
+      <c r="L29" s="2">
+        <v>162.33269999999999</v>
+      </c>
+      <c r="M29" s="2">
+        <v>85.712400000000002</v>
+      </c>
+      <c r="N29" s="2">
+        <v>167.59440000000001</v>
+      </c>
+      <c r="O29" s="2">
+        <v>66.237099999999998</v>
+      </c>
+      <c r="P29" s="2">
+        <v>533.87070000000006</v>
+      </c>
+      <c r="Q29" s="2">
+        <v>924.60550000000001</v>
+      </c>
+      <c r="R29" s="2">
+        <v>561.24220000000003</v>
+      </c>
+      <c r="S29" s="2">
+        <v>268.02179999999998</v>
+      </c>
+      <c r="T29" s="2">
+        <v>360.38830000000002</v>
+      </c>
+      <c r="U29" s="2">
+        <v>875.58929999999998</v>
+      </c>
+      <c r="V29" s="2">
+        <v>441.37970000000001</v>
+      </c>
+      <c r="W29" s="2">
+        <v>5.79E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B30" s="2">
+        <v>2019</v>
+      </c>
+      <c r="C30" s="20">
+        <v>137</v>
+      </c>
+      <c r="D30" s="20">
+        <v>156</v>
+      </c>
+      <c r="E30" s="20">
+        <v>126</v>
+      </c>
+      <c r="F30" s="20">
+        <v>403</v>
+      </c>
+      <c r="G30" s="20">
+        <v>69</v>
+      </c>
+      <c r="H30" s="2">
+        <v>17.7136</v>
+      </c>
+      <c r="I30" s="2">
+        <v>0.7732</v>
+      </c>
+      <c r="J30" s="2">
+        <v>2.0488</v>
+      </c>
+      <c r="K30" s="2">
+        <v>26.105799999999999</v>
+      </c>
+      <c r="L30" s="2">
+        <v>162.33269999999999</v>
+      </c>
+      <c r="M30" s="2">
+        <v>98.909400000000005</v>
+      </c>
+      <c r="N30" s="2">
+        <v>753.23509999999999</v>
+      </c>
+      <c r="O30" s="2">
+        <v>66.237099999999998</v>
+      </c>
+      <c r="P30" s="2">
+        <v>712.34559999999999</v>
+      </c>
+      <c r="Q30" s="2">
+        <v>1729.8141000000001</v>
+      </c>
+      <c r="R30" s="2">
+        <v>1072.3669</v>
+      </c>
+      <c r="S30" s="2">
+        <v>269.98910000000001</v>
+      </c>
+      <c r="T30" s="2">
+        <v>360.38830000000002</v>
+      </c>
+      <c r="U30" s="2">
+        <v>1469.12</v>
+      </c>
+      <c r="V30" s="2">
+        <v>1103.5744999999999</v>
+      </c>
+      <c r="W30" s="2">
+        <v>5.79E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B31" s="2">
+        <v>2020</v>
+      </c>
+      <c r="C31" s="20">
+        <v>162</v>
+      </c>
+      <c r="D31" s="20">
+        <v>188</v>
+      </c>
+      <c r="E31" s="20">
+        <v>136</v>
+      </c>
+      <c r="F31" s="20">
+        <v>524</v>
+      </c>
+      <c r="G31" s="20">
+        <v>73</v>
+      </c>
+      <c r="H31" s="2">
+        <v>17.7136</v>
+      </c>
+      <c r="I31" s="2">
+        <v>0.7732</v>
+      </c>
+      <c r="J31" s="2">
+        <v>2.0488</v>
+      </c>
+      <c r="K31" s="2">
+        <v>50.105800000000002</v>
+      </c>
+      <c r="L31" s="2">
+        <v>162.93270000000001</v>
+      </c>
+      <c r="M31" s="2">
+        <v>98.909400000000005</v>
+      </c>
+      <c r="N31" s="2">
+        <v>1099.1387999999999</v>
+      </c>
+      <c r="O31" s="2">
+        <v>66.737099999999998</v>
+      </c>
+      <c r="P31" s="2">
+        <v>840.77179999999998</v>
+      </c>
+      <c r="Q31" s="2">
+        <v>1925.1898000000001</v>
+      </c>
+      <c r="R31" s="2">
+        <v>2328.7757999999999</v>
+      </c>
+      <c r="S31" s="2">
+        <v>276.38810000000001</v>
+      </c>
+      <c r="T31" s="2">
+        <v>364.29910000000001</v>
+      </c>
+      <c r="U31" s="2">
+        <v>2089.4504999999999</v>
+      </c>
+      <c r="V31" s="2">
+        <v>1218.7228</v>
+      </c>
+      <c r="W31" s="2">
+        <v>5.79E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B32" s="2">
+        <v>2021</v>
+      </c>
+      <c r="C32" s="20">
+        <v>297</v>
+      </c>
+      <c r="D32" s="20">
+        <v>284</v>
+      </c>
+      <c r="E32" s="20">
+        <v>172</v>
+      </c>
+      <c r="F32" s="20">
+        <v>721</v>
+      </c>
+      <c r="G32" s="20">
+        <v>327</v>
+      </c>
+      <c r="H32" s="2">
+        <v>17.683499999999999</v>
+      </c>
+      <c r="I32" s="2">
+        <v>0.73709999999999998</v>
+      </c>
+      <c r="J32" s="2">
+        <v>3.5488</v>
+      </c>
+      <c r="K32" s="2">
+        <v>50.525500000000001</v>
+      </c>
+      <c r="L32" s="2">
+        <v>163.55269999999999</v>
+      </c>
+      <c r="M32" s="2">
+        <v>99.759100000000004</v>
+      </c>
+      <c r="N32" s="2">
+        <v>1503.5422000000001</v>
+      </c>
+      <c r="O32" s="2">
+        <v>66.436300000000003</v>
+      </c>
+      <c r="P32" s="2">
+        <v>1030.7711999999999</v>
+      </c>
+      <c r="Q32" s="2">
+        <v>2824.7231999999999</v>
+      </c>
+      <c r="R32" s="2">
+        <v>3365.6097</v>
+      </c>
+      <c r="S32" s="2">
+        <v>279.33749999999998</v>
+      </c>
+      <c r="T32" s="2">
+        <v>404.96940000000001</v>
+      </c>
+      <c r="U32" s="2">
+        <v>2968.2550999999999</v>
+      </c>
+      <c r="V32" s="2">
+        <v>1302.9530999999999</v>
+      </c>
+      <c r="W32" s="2">
+        <v>5.79E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B33" s="2">
+        <v>2022</v>
+      </c>
+      <c r="C33" s="20">
+        <v>482</v>
+      </c>
+      <c r="D33" s="20">
+        <v>461</v>
+      </c>
+      <c r="E33" s="20">
+        <v>315</v>
+      </c>
+      <c r="F33" s="20">
+        <v>877</v>
+      </c>
+      <c r="G33" s="20">
+        <v>524</v>
+      </c>
+      <c r="H33" s="2">
+        <v>17.782699999999998</v>
+      </c>
+      <c r="I33" s="2">
+        <v>0.79710000000000003</v>
+      </c>
+      <c r="J33" s="2">
+        <v>3.6738</v>
+      </c>
+      <c r="K33" s="2">
+        <v>50.685499999999998</v>
+      </c>
+      <c r="L33" s="2">
+        <v>163.55269999999999</v>
+      </c>
+      <c r="M33" s="2">
+        <v>99.859099999999998</v>
+      </c>
+      <c r="N33" s="2">
+        <v>1810.9880000000001</v>
+      </c>
+      <c r="O33" s="2">
+        <v>66.436300000000003</v>
+      </c>
+      <c r="P33" s="2">
+        <v>1396.5757000000001</v>
+      </c>
+      <c r="Q33" s="2">
+        <v>3893.9758000000002</v>
+      </c>
+      <c r="R33" s="2">
+        <v>5319.424</v>
+      </c>
+      <c r="S33" s="2">
+        <v>284.7353</v>
+      </c>
+      <c r="T33" s="2">
+        <v>410.04539999999997</v>
+      </c>
+      <c r="U33" s="2">
+        <v>3917.9250999999999</v>
+      </c>
+      <c r="V33" s="2">
+        <v>1404.2308</v>
+      </c>
+      <c r="W33" s="2">
+        <v>5.79E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B34" s="2">
+        <v>2023</v>
+      </c>
+      <c r="C34" s="20">
+        <v>752</v>
+      </c>
+      <c r="D34" s="20">
+        <v>1025</v>
+      </c>
+      <c r="E34" s="20">
+        <v>474</v>
+      </c>
+      <c r="F34" s="20">
+        <v>1066</v>
+      </c>
+      <c r="G34" s="20">
+        <v>553</v>
+      </c>
+      <c r="H34" s="2">
+        <v>19.332699999999999</v>
+      </c>
+      <c r="I34" s="2">
+        <v>0.87619999999999998</v>
+      </c>
+      <c r="J34" s="2">
+        <v>3.9238</v>
+      </c>
+      <c r="K34" s="2">
+        <v>57.3155</v>
+      </c>
+      <c r="L34" s="2">
+        <v>172.2927</v>
+      </c>
+      <c r="M34" s="2">
+        <v>103.6181</v>
+      </c>
+      <c r="N34" s="2">
+        <v>2259.2469000000001</v>
+      </c>
+      <c r="O34" s="2">
+        <v>152.04130000000001</v>
+      </c>
+      <c r="P34" s="2">
+        <v>1909.9184</v>
+      </c>
+      <c r="Q34" s="2">
+        <v>5764.7286999999997</v>
+      </c>
+      <c r="R34" s="2">
+        <v>6014.6284999999998</v>
+      </c>
+      <c r="S34" s="2">
+        <v>293.39640000000003</v>
+      </c>
+      <c r="T34" s="2">
+        <v>443.1404</v>
+      </c>
+      <c r="U34" s="2">
+        <v>4957.8874999999998</v>
+      </c>
+      <c r="V34" s="2">
+        <v>1553.2028</v>
+      </c>
+      <c r="W34" s="2">
+        <v>5.79E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B35" s="2">
+        <v>2024</v>
+      </c>
+      <c r="C35" s="20">
+        <v>946</v>
+      </c>
+      <c r="D35" s="20">
+        <v>1601</v>
+      </c>
+      <c r="E35" s="20">
+        <v>595</v>
+      </c>
+      <c r="F35" s="20">
+        <v>1878</v>
+      </c>
+      <c r="G35" s="20">
+        <v>621</v>
+      </c>
+      <c r="H35" s="2">
+        <v>19.4649</v>
+      </c>
+      <c r="I35" s="2">
+        <v>0.93620000000000003</v>
+      </c>
+      <c r="J35" s="2">
+        <v>7.5818000000000003</v>
+      </c>
+      <c r="K35" s="2">
+        <v>59.515500000000003</v>
+      </c>
+      <c r="L35" s="2">
+        <v>234.41380000000001</v>
+      </c>
+      <c r="M35" s="2">
+        <v>105.11409999999999</v>
+      </c>
+      <c r="N35" s="2">
+        <v>2781.4018999999998</v>
+      </c>
+      <c r="O35" s="2">
+        <v>152.05860000000001</v>
+      </c>
+      <c r="P35" s="2">
+        <v>2402.6529</v>
+      </c>
+      <c r="Q35" s="2">
+        <v>6752.4339</v>
+      </c>
+      <c r="R35" s="2">
+        <v>6715.3987999999999</v>
+      </c>
+      <c r="S35" s="2">
+        <v>308.52460000000002</v>
+      </c>
+      <c r="T35" s="2">
+        <v>477.52710000000002</v>
+      </c>
+      <c r="U35" s="2">
+        <v>6559.0370000000003</v>
+      </c>
+      <c r="V35" s="2">
+        <v>1690.5808</v>
+      </c>
+      <c r="W35" s="2">
+        <v>5.79E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B36" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C36" s="20">
+        <v>1326</v>
+      </c>
+      <c r="D36" s="20">
+        <v>1927</v>
+      </c>
+      <c r="E36" s="20">
+        <v>677</v>
+      </c>
+      <c r="F36" s="20">
+        <v>2192</v>
+      </c>
+      <c r="G36" s="20">
+        <v>691</v>
+      </c>
+      <c r="H36" s="2">
+        <v>19.4649</v>
+      </c>
+      <c r="I36" s="2">
+        <v>0.93620000000000003</v>
+      </c>
+      <c r="J36" s="2">
+        <v>7.5818000000000003</v>
+      </c>
+      <c r="K36" s="2">
+        <v>62.514499999999998</v>
+      </c>
+      <c r="L36" s="2">
+        <v>279.63279999999997</v>
+      </c>
+      <c r="M36" s="2">
+        <v>105.11409999999999</v>
+      </c>
+      <c r="N36" s="2">
+        <v>3122.9047999999998</v>
+      </c>
+      <c r="O36" s="2">
+        <v>152.05860000000001</v>
+      </c>
+      <c r="P36" s="2">
+        <v>3964.9854</v>
+      </c>
+      <c r="Q36" s="2">
+        <v>7744.6749</v>
+      </c>
+      <c r="R36" s="2">
+        <v>7094.5673999999999</v>
+      </c>
+      <c r="S36" s="2">
+        <v>414.77620000000002</v>
+      </c>
+      <c r="T36" s="2">
+        <v>572.47410000000002</v>
+      </c>
+      <c r="U36" s="2">
+        <v>8186.1710000000003</v>
+      </c>
+      <c r="V36" s="2">
+        <v>1796.0708</v>
+      </c>
+      <c r="W36" s="2">
+        <v>5.79E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C24:W24"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57FD5248-C7A5-664D-AD0D-5AECEF6931A7}">
+  <dimension ref="C5:W17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="10.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="D5" s="48" t="s">
+        <v>123</v>
+      </c>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48"/>
+      <c r="L5" s="48"/>
+      <c r="M5" s="48"/>
+      <c r="N5" s="48"/>
+      <c r="O5" s="48"/>
+      <c r="P5" s="48"/>
+      <c r="Q5" s="48"/>
+      <c r="R5" s="48"/>
+      <c r="S5" s="48"/>
+      <c r="T5" s="48"/>
+      <c r="U5" s="48"/>
+      <c r="V5" s="48"/>
+      <c r="W5" s="48"/>
+    </row>
+    <row r="6" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="C6" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="I6" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="L6" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="M6" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="N6" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="O6" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="P6" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q6" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="R6" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="S6" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="T6" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="U6" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="V6" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="W6" s="19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="C7" s="2">
+        <v>2015</v>
+      </c>
+      <c r="D7" s="2">
+        <v>48</v>
+      </c>
+      <c r="E7" s="2">
+        <v>66</v>
+      </c>
+      <c r="F7" s="2">
+        <v>91</v>
+      </c>
+      <c r="G7" s="2">
+        <v>156</v>
+      </c>
+      <c r="H7" s="2">
+        <v>50</v>
+      </c>
+      <c r="I7" s="19">
+        <v>16.083600000000001</v>
+      </c>
+      <c r="J7" s="19">
+        <v>0.76319999999999999</v>
+      </c>
+      <c r="K7" s="19">
+        <v>2.0488</v>
+      </c>
+      <c r="L7" s="19">
+        <v>25.8901</v>
+      </c>
+      <c r="M7" s="19">
+        <v>161.17490000000001</v>
+      </c>
+      <c r="N7" s="19">
+        <v>85.712400000000002</v>
+      </c>
+      <c r="O7" s="19">
+        <v>167.51240000000001</v>
+      </c>
+      <c r="P7" s="19">
+        <v>65.737099999999998</v>
+      </c>
+      <c r="Q7" s="19">
+        <v>493.36219999999997</v>
+      </c>
+      <c r="R7" s="19">
+        <v>923.55949999999996</v>
+      </c>
+      <c r="S7" s="19">
+        <v>560.58230000000003</v>
+      </c>
+      <c r="T7" s="19">
+        <v>263.7106</v>
+      </c>
+      <c r="U7" s="19">
+        <v>348.24430000000001</v>
+      </c>
+      <c r="V7" s="19">
+        <v>867.77689999999996</v>
+      </c>
+      <c r="W7" s="19">
+        <v>438.03469999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="C8" s="2">
+        <v>2016</v>
+      </c>
+      <c r="D8" s="20">
+        <v>70</v>
+      </c>
+      <c r="E8" s="20">
+        <v>87</v>
+      </c>
+      <c r="F8" s="20">
+        <v>100</v>
+      </c>
+      <c r="G8" s="20">
+        <v>177</v>
+      </c>
+      <c r="H8" s="20">
+        <v>57</v>
+      </c>
+      <c r="I8" s="2">
+        <v>16.083600000000001</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0.7732</v>
+      </c>
+      <c r="K8" s="2">
+        <v>2.0488</v>
+      </c>
+      <c r="L8" s="2">
+        <v>26.026</v>
+      </c>
+      <c r="M8" s="2">
+        <v>161.18289999999999</v>
+      </c>
+      <c r="N8" s="2">
+        <v>85.712400000000002</v>
+      </c>
+      <c r="O8" s="2">
+        <v>167.51240000000001</v>
+      </c>
+      <c r="P8" s="2">
+        <v>65.737099999999998</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>493.36869999999999</v>
+      </c>
+      <c r="R8" s="2">
+        <v>923.55949999999996</v>
+      </c>
+      <c r="S8" s="2">
+        <v>561.08230000000003</v>
+      </c>
+      <c r="T8" s="2">
+        <v>265.233</v>
+      </c>
+      <c r="U8" s="2">
+        <v>348.33929999999998</v>
+      </c>
+      <c r="V8" s="2">
+        <v>871.71040000000005</v>
+      </c>
+      <c r="W8" s="2">
+        <v>438.03469999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="C9" s="2">
+        <v>2017</v>
+      </c>
+      <c r="D9" s="20">
+        <v>88</v>
+      </c>
+      <c r="E9" s="20">
+        <v>102</v>
+      </c>
+      <c r="F9" s="20">
+        <v>106</v>
+      </c>
+      <c r="G9" s="20">
+        <v>197</v>
+      </c>
+      <c r="H9" s="20">
+        <v>61</v>
+      </c>
+      <c r="I9" s="2">
+        <v>16.2136</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0.7732</v>
+      </c>
+      <c r="K9" s="2">
+        <v>2.0488</v>
+      </c>
+      <c r="L9" s="2">
+        <v>26.026</v>
+      </c>
+      <c r="M9" s="2">
+        <v>161.18889999999999</v>
+      </c>
+      <c r="N9" s="2">
+        <v>85.712400000000002</v>
+      </c>
+      <c r="O9" s="2">
+        <v>167.59440000000001</v>
+      </c>
+      <c r="P9" s="2">
+        <v>66.237099999999998</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>493.61829999999998</v>
+      </c>
+      <c r="R9" s="2">
+        <v>924.60550000000001</v>
+      </c>
+      <c r="S9" s="2">
+        <v>561.23230000000001</v>
+      </c>
+      <c r="T9" s="2">
+        <v>265.6748</v>
+      </c>
+      <c r="U9" s="2">
+        <v>348.38830000000002</v>
+      </c>
+      <c r="V9" s="2">
+        <v>872.44929999999999</v>
+      </c>
+      <c r="W9" s="2">
+        <v>438.03469999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="C10" s="2">
+        <v>2018</v>
+      </c>
+      <c r="D10" s="20">
+        <v>104</v>
+      </c>
+      <c r="E10" s="20">
+        <v>116</v>
+      </c>
+      <c r="F10" s="20">
+        <v>112</v>
+      </c>
+      <c r="G10" s="20">
+        <v>248</v>
+      </c>
+      <c r="H10" s="20">
+        <v>66</v>
+      </c>
+      <c r="I10" s="2">
+        <v>16.2136</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0.7732</v>
+      </c>
+      <c r="K10" s="2">
+        <v>2.0488</v>
+      </c>
+      <c r="L10" s="2">
+        <v>26.026</v>
+      </c>
+      <c r="M10" s="2">
+        <v>162.33269999999999</v>
+      </c>
+      <c r="N10" s="2">
+        <v>85.712400000000002</v>
+      </c>
+      <c r="O10" s="2">
+        <v>167.59440000000001</v>
+      </c>
+      <c r="P10" s="2">
+        <v>66.237099999999998</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>533.87070000000006</v>
+      </c>
+      <c r="R10" s="2">
+        <v>924.60550000000001</v>
+      </c>
+      <c r="S10" s="2">
+        <v>561.24220000000003</v>
+      </c>
+      <c r="T10" s="2">
+        <v>268.02179999999998</v>
+      </c>
+      <c r="U10" s="2">
+        <v>360.38830000000002</v>
+      </c>
+      <c r="V10" s="2">
+        <v>875.58929999999998</v>
+      </c>
+      <c r="W10" s="2">
+        <v>441.37970000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="C11" s="2">
+        <v>2019</v>
+      </c>
+      <c r="D11" s="20">
+        <v>137</v>
+      </c>
+      <c r="E11" s="20">
+        <v>156</v>
+      </c>
+      <c r="F11" s="20">
+        <v>126</v>
+      </c>
+      <c r="G11" s="20">
+        <v>403</v>
+      </c>
+      <c r="H11" s="20">
+        <v>69</v>
+      </c>
+      <c r="I11" s="2">
+        <v>17.7136</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0.7732</v>
+      </c>
+      <c r="K11" s="2">
+        <v>2.0488</v>
+      </c>
+      <c r="L11" s="2">
+        <v>26.105799999999999</v>
+      </c>
+      <c r="M11" s="2">
+        <v>162.33269999999999</v>
+      </c>
+      <c r="N11" s="2">
+        <v>98.909400000000005</v>
+      </c>
+      <c r="O11" s="2">
+        <v>753.23509999999999</v>
+      </c>
+      <c r="P11" s="2">
+        <v>66.237099999999998</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>712.34559999999999</v>
+      </c>
+      <c r="R11" s="2">
+        <v>1729.8141000000001</v>
+      </c>
+      <c r="S11" s="2">
+        <v>1072.3669</v>
+      </c>
+      <c r="T11" s="2">
+        <v>269.98910000000001</v>
+      </c>
+      <c r="U11" s="2">
+        <v>360.38830000000002</v>
+      </c>
+      <c r="V11" s="2">
+        <v>1469.12</v>
+      </c>
+      <c r="W11" s="2">
+        <v>1103.5744999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="C12" s="2">
+        <v>2020</v>
+      </c>
+      <c r="D12" s="20">
+        <v>162</v>
+      </c>
+      <c r="E12" s="20">
+        <v>188</v>
+      </c>
+      <c r="F12" s="20">
+        <v>136</v>
+      </c>
+      <c r="G12" s="20">
+        <v>524</v>
+      </c>
+      <c r="H12" s="20">
+        <v>73</v>
+      </c>
+      <c r="I12" s="2">
+        <v>17.7136</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0.7732</v>
+      </c>
+      <c r="K12" s="2">
+        <v>2.0488</v>
+      </c>
+      <c r="L12" s="2">
+        <v>50.105800000000002</v>
+      </c>
+      <c r="M12" s="2">
+        <v>162.93270000000001</v>
+      </c>
+      <c r="N12" s="2">
+        <v>98.909400000000005</v>
+      </c>
+      <c r="O12" s="2">
+        <v>1099.1387999999999</v>
+      </c>
+      <c r="P12" s="2">
+        <v>66.737099999999998</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>840.77179999999998</v>
+      </c>
+      <c r="R12" s="2">
+        <v>1925.1898000000001</v>
+      </c>
+      <c r="S12" s="2">
+        <v>2328.7757999999999</v>
+      </c>
+      <c r="T12" s="2">
+        <v>276.38810000000001</v>
+      </c>
+      <c r="U12" s="2">
+        <v>364.29910000000001</v>
+      </c>
+      <c r="V12" s="2">
+        <v>2089.4504999999999</v>
+      </c>
+      <c r="W12" s="2">
+        <v>1218.7228</v>
+      </c>
+    </row>
+    <row r="13" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="C13" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D13" s="20">
+        <v>297</v>
+      </c>
+      <c r="E13" s="20">
+        <v>284</v>
+      </c>
+      <c r="F13" s="20">
+        <v>172</v>
+      </c>
+      <c r="G13" s="20">
+        <v>721</v>
+      </c>
+      <c r="H13" s="20">
+        <v>327</v>
+      </c>
+      <c r="I13" s="2">
+        <v>17.683499999999999</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0.73709999999999998</v>
+      </c>
+      <c r="K13" s="2">
+        <v>3.5488</v>
+      </c>
+      <c r="L13" s="2">
+        <v>50.525500000000001</v>
+      </c>
+      <c r="M13" s="2">
+        <v>163.55269999999999</v>
+      </c>
+      <c r="N13" s="2">
+        <v>99.759100000000004</v>
+      </c>
+      <c r="O13" s="2">
+        <v>1503.5422000000001</v>
+      </c>
+      <c r="P13" s="2">
+        <v>66.436300000000003</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>1030.7711999999999</v>
+      </c>
+      <c r="R13" s="2">
+        <v>2824.7231999999999</v>
+      </c>
+      <c r="S13" s="2">
+        <v>3365.6097</v>
+      </c>
+      <c r="T13" s="2">
+        <v>279.33749999999998</v>
+      </c>
+      <c r="U13" s="2">
+        <v>404.96940000000001</v>
+      </c>
+      <c r="V13" s="2">
+        <v>2968.2550999999999</v>
+      </c>
+      <c r="W13" s="2">
+        <v>1302.9530999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="C14" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D14" s="20">
+        <v>482</v>
+      </c>
+      <c r="E14" s="20">
+        <v>461</v>
+      </c>
+      <c r="F14" s="20">
+        <v>315</v>
+      </c>
+      <c r="G14" s="20">
+        <v>877</v>
+      </c>
+      <c r="H14" s="20">
+        <v>524</v>
+      </c>
+      <c r="I14" s="2">
+        <v>17.782699999999998</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0.79710000000000003</v>
+      </c>
+      <c r="K14" s="2">
+        <v>3.6738</v>
+      </c>
+      <c r="L14" s="2">
+        <v>50.685499999999998</v>
+      </c>
+      <c r="M14" s="2">
+        <v>163.55269999999999</v>
+      </c>
+      <c r="N14" s="2">
+        <v>99.859099999999998</v>
+      </c>
+      <c r="O14" s="2">
+        <v>1810.9880000000001</v>
+      </c>
+      <c r="P14" s="2">
+        <v>66.436300000000003</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>1396.5757000000001</v>
+      </c>
+      <c r="R14" s="2">
+        <v>3893.9758000000002</v>
+      </c>
+      <c r="S14" s="2">
+        <v>5319.424</v>
+      </c>
+      <c r="T14" s="2">
+        <v>284.7353</v>
+      </c>
+      <c r="U14" s="2">
+        <v>410.04539999999997</v>
+      </c>
+      <c r="V14" s="2">
+        <v>3917.9250999999999</v>
+      </c>
+      <c r="W14" s="2">
+        <v>1404.2308</v>
+      </c>
+    </row>
+    <row r="15" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="C15" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D15" s="20">
+        <v>752</v>
+      </c>
+      <c r="E15" s="20">
+        <v>1025</v>
+      </c>
+      <c r="F15" s="20">
+        <v>474</v>
+      </c>
+      <c r="G15" s="20">
+        <v>1066</v>
+      </c>
+      <c r="H15" s="20">
+        <v>553</v>
+      </c>
+      <c r="I15" s="2">
+        <v>19.332699999999999</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0.87619999999999998</v>
+      </c>
+      <c r="K15" s="2">
+        <v>3.9238</v>
+      </c>
+      <c r="L15" s="2">
+        <v>57.3155</v>
+      </c>
+      <c r="M15" s="2">
+        <v>172.2927</v>
+      </c>
+      <c r="N15" s="2">
+        <v>103.6181</v>
+      </c>
+      <c r="O15" s="2">
+        <v>2259.2469000000001</v>
+      </c>
+      <c r="P15" s="2">
+        <v>152.04130000000001</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>1909.9184</v>
+      </c>
+      <c r="R15" s="2">
+        <v>5764.7286999999997</v>
+      </c>
+      <c r="S15" s="2">
+        <v>6014.6284999999998</v>
+      </c>
+      <c r="T15" s="2">
+        <v>293.39640000000003</v>
+      </c>
+      <c r="U15" s="2">
+        <v>443.1404</v>
+      </c>
+      <c r="V15" s="2">
+        <v>4957.8874999999998</v>
+      </c>
+      <c r="W15" s="2">
+        <v>1553.2028</v>
+      </c>
+    </row>
+    <row r="16" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="C16" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D16" s="20">
+        <v>946</v>
+      </c>
+      <c r="E16" s="20">
+        <v>1601</v>
+      </c>
+      <c r="F16" s="20">
+        <v>595</v>
+      </c>
+      <c r="G16" s="20">
+        <v>1878</v>
+      </c>
+      <c r="H16" s="20">
+        <v>621</v>
+      </c>
+      <c r="I16" s="2">
+        <v>19.4649</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0.93620000000000003</v>
+      </c>
+      <c r="K16" s="2">
+        <v>7.5818000000000003</v>
+      </c>
+      <c r="L16" s="2">
+        <v>59.515500000000003</v>
+      </c>
+      <c r="M16" s="2">
+        <v>234.41380000000001</v>
+      </c>
+      <c r="N16" s="2">
+        <v>105.11409999999999</v>
+      </c>
+      <c r="O16" s="2">
+        <v>2781.4018999999998</v>
+      </c>
+      <c r="P16" s="2">
+        <v>152.05860000000001</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>2402.6529</v>
+      </c>
+      <c r="R16" s="2">
+        <v>6752.4339</v>
+      </c>
+      <c r="S16" s="2">
+        <v>6715.3987999999999</v>
+      </c>
+      <c r="T16" s="2">
+        <v>308.52460000000002</v>
+      </c>
+      <c r="U16" s="2">
+        <v>477.52710000000002</v>
+      </c>
+      <c r="V16" s="2">
+        <v>6559.0370000000003</v>
+      </c>
+      <c r="W16" s="2">
+        <v>1690.5808</v>
+      </c>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="C17" s="2">
+        <v>2025</v>
+      </c>
+      <c r="D17" s="20">
+        <v>1326</v>
+      </c>
+      <c r="E17" s="20">
+        <v>1927</v>
+      </c>
+      <c r="F17" s="20">
+        <v>677</v>
+      </c>
+      <c r="G17" s="20">
+        <v>2192</v>
+      </c>
+      <c r="H17" s="20">
+        <v>691</v>
+      </c>
+      <c r="I17" s="2">
+        <v>19.4649</v>
+      </c>
+      <c r="J17" s="2">
+        <v>0.93620000000000003</v>
+      </c>
+      <c r="K17" s="2">
+        <v>7.5818000000000003</v>
+      </c>
+      <c r="L17" s="2">
+        <v>62.514499999999998</v>
+      </c>
+      <c r="M17" s="2">
+        <v>279.63279999999997</v>
+      </c>
+      <c r="N17" s="2">
+        <v>105.11409999999999</v>
+      </c>
+      <c r="O17" s="2">
+        <v>3122.9047999999998</v>
+      </c>
+      <c r="P17" s="2">
+        <v>152.05860000000001</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>3964.9854</v>
+      </c>
+      <c r="R17" s="2">
+        <v>7744.6749</v>
+      </c>
+      <c r="S17" s="2">
+        <v>7094.5673999999999</v>
+      </c>
+      <c r="T17" s="2">
+        <v>414.77620000000002</v>
+      </c>
+      <c r="U17" s="2">
+        <v>572.47410000000002</v>
+      </c>
+      <c r="V17" s="2">
+        <v>8186.1710000000003</v>
+      </c>
+      <c r="W17" s="2">
+        <v>1796.0708</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D5:W5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/DC OPF/GridInputs.xlsx
+++ b/DC OPF/GridInputs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/76f4b4c107b736ef/Programación/Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="399" documentId="14_{D584702F-B3CD-3F47-A25C-44363057DD2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D13FC94-C881-3542-A4C6-C198D2992F50}"/>
+  <xr:revisionPtr revIDLastSave="3430" documentId="14_{D584702F-B3CD-3F47-A25C-44363057DD2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DAF743B-9B8D-2D44-89D3-5D07FFAFBB8F}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" tabRatio="714" activeTab="3" xr2:uid="{36617186-47CB-F249-899F-182F2423F0BD}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" tabRatio="714" xr2:uid="{36617186-47CB-F249-899F-182F2423F0BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Net_Buses" sheetId="5" r:id="rId1"/>
@@ -19,9 +19,6 @@
     <sheet name="Gen_Dispatchable" sheetId="7" r:id="rId4"/>
     <sheet name="Gen_PV_and_Wind" sheetId="8" r:id="rId5"/>
     <sheet name="StorageUnit" sheetId="13" r:id="rId6"/>
-    <sheet name="Tareas" sheetId="21" r:id="rId7"/>
-    <sheet name="Sheet4" sheetId="22" r:id="rId8"/>
-    <sheet name="Sheet1" sheetId="24" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="PV_Day">#REF!</definedName>
@@ -177,7 +174,6 @@
             <sz val="12"/>
             <color rgb="FF000000"/>
             <rFont val="Aptos Narrow"/>
-            <scheme val="minor"/>
           </rPr>
           <t>Takes a value of 1 if left empty</t>
         </r>
@@ -186,7 +182,6 @@
             <sz val="7"/>
             <color rgb="FF000000"/>
             <rFont val="Aptos Narrow"/>
-            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -245,7 +240,6 @@
             <sz val="12"/>
             <color rgb="FF000000"/>
             <rFont val="Aptos Narrow"/>
-            <scheme val="minor"/>
           </rPr>
           <t>Takes a value of 0 if left empty</t>
         </r>
@@ -254,7 +248,6 @@
             <sz val="7"/>
             <color rgb="FF000000"/>
             <rFont val="Aptos Narrow"/>
-            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -564,7 +557,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="151">
   <si>
     <t>From</t>
   </si>
@@ -1034,121 +1027,7 @@
     </r>
   </si>
   <si>
-    <t>Tipo</t>
-  </si>
-  <si>
-    <t>Objetivo</t>
-  </si>
-  <si>
-    <t>Restricciones</t>
-  </si>
-  <si>
-    <t>Variables</t>
-  </si>
-  <si>
-    <t>LP</t>
-  </si>
-  <si>
-    <t>Lineal</t>
-  </si>
-  <si>
-    <t>Lineales</t>
-  </si>
-  <si>
-    <t>Continuas</t>
-  </si>
-  <si>
-    <t>QP</t>
-  </si>
-  <si>
-    <t>Cuadrático</t>
-  </si>
-  <si>
-    <t>NLP</t>
-  </si>
-  <si>
-    <t>No lineal</t>
-  </si>
-  <si>
-    <t>Lineales/no lineales</t>
-  </si>
-  <si>
-    <t>ILP</t>
-  </si>
-  <si>
-    <t>Enteras</t>
-  </si>
-  <si>
-    <t>MILP</t>
-  </si>
-  <si>
-    <t>Continuas + enteras</t>
-  </si>
-  <si>
-    <t>MIQP</t>
-  </si>
-  <si>
-    <t>MIQCP</t>
-  </si>
-  <si>
-    <t>Lineal/cuadrático</t>
-  </si>
-  <si>
-    <t>Cuadráticas</t>
-  </si>
-  <si>
-    <t>MINLP</t>
-  </si>
-  <si>
-    <t>No lineales</t>
-  </si>
-  <si>
-    <t>SOCP</t>
-  </si>
-  <si>
-    <t>Cónicas de segundo orden</t>
-  </si>
-  <si>
-    <t>SDP</t>
-  </si>
-  <si>
-    <t>Matriciales semidefinidas</t>
-  </si>
-  <si>
-    <t>Continuas/matriciales</t>
-  </si>
-  <si>
-    <t>Estocástica</t>
-  </si>
-  <si>
-    <t>Depende</t>
-  </si>
-  <si>
-    <t>Con escenarios</t>
-  </si>
-  <si>
-    <t>Robusta</t>
-  </si>
-  <si>
-    <t>Incertidumbre acotada</t>
-  </si>
-  <si>
-    <t>Dinámica</t>
-  </si>
-  <si>
-    <t>Secuenciales</t>
-  </si>
-  <si>
-    <t>DC OPF</t>
-  </si>
-  <si>
-    <t>PF</t>
-  </si>
-  <si>
-    <t>ED</t>
-  </si>
-  <si>
-    <t>AC OPF</t>
+    <t>BatteryStore</t>
   </si>
   <si>
     <t>Committable</t>
@@ -1158,11 +1037,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1222,19 +1102,6 @@
       <name val="Aptos Narrow"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="7"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -1288,15 +1155,21 @@
       <name val="Aptos Narrow"/>
     </font>
     <font>
-      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1327,14 +1200,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1383,11 +1250,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1430,7 +1313,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1440,7 +1323,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1452,84 +1335,98 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFEDFFA7"/>
+      <color rgb="FFE4F5FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2725,7 +2622,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -2750,12 +2647,12 @@
       <c r="E1"/>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B3" s="6" t="s">
@@ -2782,7 +2679,7 @@
         <v>3.771148293152772</v>
       </c>
       <c r="E4" s="1">
-        <v>4558.0649051982573</v>
+        <v>4102.258414678432</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.2">
@@ -2796,7 +2693,7 @@
         <v>1.189168390126373</v>
       </c>
       <c r="E5" s="1">
-        <v>7507.4010203265416</v>
+        <v>6756.6609182938873</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.2">
@@ -2810,7 +2707,7 @@
         <v>15.19727572333105</v>
       </c>
       <c r="E6" s="1">
-        <v>2770.5884717871759</v>
+        <v>2493.5296246084586</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.2">
@@ -2824,7 +2721,7 @@
         <v>4.9639872157825842</v>
       </c>
       <c r="E7" s="1">
-        <v>5853.9853194212919</v>
+        <v>5268.5867874791629</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.2">
@@ -2838,7 +2735,7 @@
         <v>20.76176655107923</v>
       </c>
       <c r="E8" s="1">
-        <v>1787.476433411081</v>
+        <v>1608.728790069973</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.2">
@@ -2852,7 +2749,7 @@
         <v>19.367937595905889</v>
       </c>
       <c r="E9" s="1">
-        <v>2279.0324525991291</v>
+        <v>2051.1292073392165</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.2">
@@ -2866,7 +2763,7 @@
         <v>4.4957232191448391</v>
       </c>
       <c r="E10" s="1">
-        <v>9116.1298103965164</v>
+        <v>8204.5168293568659</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.2">
@@ -2880,7 +2777,7 @@
         <v>8.0869200996521418</v>
       </c>
       <c r="E11" s="1">
-        <v>7149.9057336443257</v>
+        <v>6434.9151602798929</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.2">
@@ -2894,7 +2791,7 @@
         <v>22.798521515909069</v>
       </c>
       <c r="E12" s="1">
-        <v>3574.9528668221628</v>
+        <v>3217.4575801399465</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -2908,7 +2805,7 @@
         <v>6.1443900948176768</v>
       </c>
       <c r="E13" s="1">
-        <v>9116.1298103965164</v>
+        <v>8204.5168293568659</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.2">
@@ -2922,7 +2819,7 @@
         <v>50.185457717991603</v>
       </c>
       <c r="E14" s="1">
-        <v>1787.476433411081</v>
+        <v>1608.728790069973</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
@@ -2936,7 +2833,7 @@
         <v>64.076488300098703</v>
       </c>
       <c r="E15" s="1">
-        <v>1787.476433411081</v>
+        <v>1608.728790069973</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
@@ -2950,7 +2847,7 @@
         <v>9.1250844926263959</v>
       </c>
       <c r="E16" s="1">
-        <v>4558.0649051982573</v>
+        <v>4102.258414678432</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.2">
@@ -2964,7 +2861,7 @@
         <v>7.3327502800072866</v>
       </c>
       <c r="E17" s="1">
-        <v>4558.0649051982582</v>
+        <v>4102.2584146784329</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.2">
@@ -2978,7 +2875,7 @@
         <v>14.98492961302933</v>
       </c>
       <c r="E18" s="1">
-        <v>3574.9528668221628</v>
+        <v>3217.4575801399465</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.2">
@@ -2992,7 +2889,7 @@
         <v>18.135411696187919</v>
       </c>
       <c r="E19" s="1">
-        <v>2279.0324525991291</v>
+        <v>2051.1292073392165</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.2">
@@ -3006,7 +2903,7 @@
         <v>11.93009647235408</v>
       </c>
       <c r="E20" s="1">
-        <v>5362.4293002332442</v>
+        <v>4826.1863702099199</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.2">
@@ -3020,7 +2917,7 @@
         <v>20.347924381475689</v>
       </c>
       <c r="E21" s="1">
-        <v>3574.9528668221628</v>
+        <v>3217.4575801399465</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.2">
@@ -3034,7 +2931,7 @@
         <v>5.9344609862331126</v>
       </c>
       <c r="E22" s="1">
-        <v>3262.1444909752231</v>
+        <v>2935.9300418777007</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.2">
@@ -3048,7 +2945,7 @@
         <v>3.355274178283929</v>
       </c>
       <c r="E23" s="1">
-        <v>6837.0973577973864</v>
+        <v>6153.387622017648</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.2">
@@ -3062,7 +2959,7 @@
         <v>17.21068679632468</v>
       </c>
       <c r="E24" s="1">
-        <v>983.1120383760948</v>
+        <v>884.80083453848533</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.2">
@@ -3076,7 +2973,7 @@
         <v>5.7788685504777799</v>
       </c>
       <c r="E25" s="1">
-        <v>6345.5413386093387</v>
+        <v>5710.987204748405</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.2">
@@ -3090,7 +2987,7 @@
         <v>5.3610610756907864</v>
       </c>
       <c r="E26" s="1">
-        <v>4066.5088860102101</v>
+        <v>3659.857997409189</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.2">
@@ -3104,7 +3001,7 @@
         <v>13.781499068113821</v>
       </c>
       <c r="E27" s="1">
-        <v>1474.6680575641419</v>
+        <v>1327.2012518077277</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.2">
@@ -3118,7 +3015,7 @@
         <v>43.685334258652667</v>
       </c>
       <c r="E28" s="1">
-        <v>491.5560191880474</v>
+        <v>442.40041726924267</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.2">
@@ -3132,7 +3029,7 @@
         <v>6.1663688648245394</v>
       </c>
       <c r="E29" s="1">
-        <v>5049.620924386305</v>
+        <v>4544.658831947675</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.2">
@@ -3146,7 +3043,7 @@
         <v>37.951153841375977</v>
       </c>
       <c r="E30" s="1">
-        <v>491.5560191880474</v>
+        <v>442.40041726924267</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.2">
@@ -3160,7 +3057,7 @@
         <v>10.27898564926444</v>
       </c>
       <c r="E31" s="1">
-        <v>5853.9853194212919</v>
+        <v>5268.5867874791629</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.2">
@@ -3174,7 +3071,7 @@
         <v>33.702454023403789</v>
       </c>
       <c r="E32" s="1">
-        <v>3574.9528668221628</v>
+        <v>3217.4575801399465</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.2">
@@ -3188,7 +3085,7 @@
         <v>3.170183873175807</v>
       </c>
       <c r="E33" s="1">
-        <v>8624.5737912084678</v>
+        <v>7762.116412087621</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.2">
@@ -3202,7 +3099,7 @@
         <v>9.4893334613810012</v>
       </c>
       <c r="E34" s="1">
-        <v>1474.6680575641419</v>
+        <v>1327.2012518077277</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.2">
@@ -3216,7 +3113,7 @@
         <v>51.682466396259507</v>
       </c>
       <c r="E35" s="1">
-        <v>491.5560191880474</v>
+        <v>442.40041726924267</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.2">
@@ -3230,7 +3127,7 @@
         <v>9.3474146471665147</v>
       </c>
       <c r="E36" s="1">
-        <v>2770.5884717871759</v>
+        <v>2493.5296246084586</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.2">
@@ -3244,7 +3141,7 @@
         <v>15.17024771745659</v>
       </c>
       <c r="E37" s="1">
-        <v>3574.9528668221628</v>
+        <v>3217.4575801399465</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.2">
@@ -3258,7 +3155,7 @@
         <v>6.0063621505996627</v>
       </c>
       <c r="E38" s="1">
-        <v>8937.3821670554062</v>
+        <v>8043.6439503498659</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.2">
@@ -3272,7 +3169,7 @@
         <v>38.754656365511202</v>
       </c>
       <c r="E39" s="1">
-        <v>491.5560191880474</v>
+        <v>442.40041726924267</v>
       </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.2">
@@ -3286,7 +3183,7 @@
         <v>9.7761395859728708</v>
       </c>
       <c r="E40" s="1">
-        <v>3574.9528668221628</v>
+        <v>3217.4575801399465</v>
       </c>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.2">
@@ -3300,7 +3197,7 @@
         <v>31.39517089933253</v>
       </c>
       <c r="E41" s="1">
-        <v>1787.476433411081</v>
+        <v>1608.728790069973</v>
       </c>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.2">
@@ -3314,7 +3211,7 @@
         <v>7.6840210322972888</v>
       </c>
       <c r="E42" s="1">
-        <v>5362.4293002332442</v>
+        <v>4826.1863702099199</v>
       </c>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.2">
@@ -3328,7 +3225,7 @@
         <v>24.456290357259832</v>
       </c>
       <c r="E43" s="1">
-        <v>3574.9528668221628</v>
+        <v>3217.4575801399465</v>
       </c>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.2">
@@ -3342,7 +3239,7 @@
         <v>8.2066498426623049</v>
       </c>
       <c r="E44" s="1">
-        <v>7641.4617528323733</v>
+        <v>6877.3155775491359</v>
       </c>
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.2">
@@ -3356,7 +3253,7 @@
         <v>9.5772413510664727</v>
       </c>
       <c r="E45" s="1">
-        <v>5362.4293002332442</v>
+        <v>4826.1863702099199</v>
       </c>
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.2">
@@ -3370,7 +3267,7 @@
         <v>5.0084065894657384</v>
       </c>
       <c r="E46" s="1">
-        <v>3262.144490975224</v>
+        <v>2935.9300418777016</v>
       </c>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.2">
@@ -3384,7 +3281,7 @@
         <v>10.77290038700051</v>
       </c>
       <c r="E47" s="1">
-        <v>7149.9057336443257</v>
+        <v>6434.9151602798929</v>
       </c>
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.2">
@@ -3398,7 +3295,7 @@
         <v>26.29581783744591</v>
       </c>
       <c r="E48" s="1">
-        <v>3574.9528668221628</v>
+        <v>3217.4575801399465</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.2">
@@ -3412,7 +3309,7 @@
         <v>2.438230812553547</v>
       </c>
       <c r="E49" s="1">
-        <v>5049.620924386305</v>
+        <v>4544.658831947675</v>
       </c>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.2">
@@ -3426,7 +3323,7 @@
         <v>3.9528590900128808</v>
       </c>
       <c r="E50" s="1">
-        <v>8624.5737912084678</v>
+        <v>7762.116412087621</v>
       </c>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.2">
@@ -3440,7 +3337,7 @@
         <v>22.904276923891349</v>
       </c>
       <c r="E51" s="1">
-        <v>491.5560191880474</v>
+        <v>442.40041726924267</v>
       </c>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.2">
@@ -3454,7 +3351,7 @@
         <v>10.6400523092545</v>
       </c>
       <c r="E52" s="1">
-        <v>983.1120383760948</v>
+        <v>884.80083453848533</v>
       </c>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.2">
@@ -3468,7 +3365,7 @@
         <v>53.847398777897503</v>
       </c>
       <c r="E53" s="1">
-        <v>491.5560191880474</v>
+        <v>442.40041726924267</v>
       </c>
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.2">
@@ -3482,7 +3379,7 @@
         <v>6.1483616502760858</v>
       </c>
       <c r="E54" s="1">
-        <v>4558.0649051982573</v>
+        <v>4102.258414678432</v>
       </c>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.2">
@@ -3496,7 +3393,7 @@
         <v>4.4098020662931594</v>
       </c>
       <c r="E55" s="1">
-        <v>5541.1769435743527</v>
+        <v>4987.0592492169171</v>
       </c>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.2">
@@ -3510,7 +3407,7 @@
         <v>59.023485202067093</v>
       </c>
       <c r="E56" s="1">
-        <v>1787.476433411081</v>
+        <v>1608.728790069973</v>
       </c>
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.2">
@@ -3524,7 +3421,7 @@
         <v>13.553445015744179</v>
       </c>
       <c r="E57" s="1">
-        <v>3574.9528668221628</v>
+        <v>3217.4575801399465</v>
       </c>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.2">
@@ -3538,7 +3435,7 @@
         <v>53.928588651644233</v>
       </c>
       <c r="E58" s="1">
-        <v>1787.476433411081</v>
+        <v>1608.728790069973</v>
       </c>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.2">
@@ -3552,7 +3449,7 @@
         <v>9.5985315079568263</v>
       </c>
       <c r="E59" s="1">
-        <v>4558.0649051982573</v>
+        <v>4102.258414678432</v>
       </c>
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.2">
@@ -3566,7 +3463,7 @@
         <v>1.0739994422846919</v>
       </c>
       <c r="E60" s="1">
-        <v>10277.98949211372</v>
+        <v>9250.1905429023482</v>
       </c>
     </row>
     <row r="61" spans="2:5" x14ac:dyDescent="0.2">
@@ -3580,7 +3477,7 @@
         <v>9.7511141012394251</v>
       </c>
       <c r="E61" s="1">
-        <v>5362.4293002332442</v>
+        <v>4826.1863702099199</v>
       </c>
     </row>
     <row r="62" spans="2:5" x14ac:dyDescent="0.2">
@@ -3594,7 +3491,7 @@
         <v>23.473652123913599</v>
       </c>
       <c r="E62" s="1">
-        <v>491.5560191880474</v>
+        <v>442.40041726924267</v>
       </c>
     </row>
     <row r="63" spans="2:5" x14ac:dyDescent="0.2">
@@ -3608,7 +3505,7 @@
         <v>9.4640801992941537</v>
       </c>
       <c r="E63" s="1">
-        <v>2279.0324525991291</v>
+        <v>2051.1292073392165</v>
       </c>
     </row>
     <row r="64" spans="2:5" x14ac:dyDescent="0.2">
@@ -3622,7 +3519,7 @@
         <v>5.5250559432147233</v>
       </c>
       <c r="E64" s="1">
-        <v>3262.144490975224</v>
+        <v>2935.9300418777016</v>
       </c>
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.2">
@@ -3636,7 +3533,7 @@
         <v>29.331608423697851</v>
       </c>
       <c r="E65" s="1">
-        <v>1787.476433411081</v>
+        <v>1608.728790069973</v>
       </c>
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.2">
@@ -3650,7 +3547,7 @@
         <v>32.061942449719403</v>
       </c>
       <c r="E66" s="1">
-        <v>491.5560191880474</v>
+        <v>442.40041726924267</v>
       </c>
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.2">
@@ -3664,7 +3561,7 @@
         <v>9.3497507130760145</v>
       </c>
       <c r="E67" s="1">
-        <v>4066.5088860102101</v>
+        <v>3659.857997409189</v>
       </c>
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.2">
@@ -3678,7 +3575,7 @@
         <v>4.2960522923759257</v>
       </c>
       <c r="E68" s="1">
-        <v>5853.9853194212919</v>
+        <v>5268.5867874791629</v>
       </c>
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.2">
@@ -3692,7 +3589,7 @@
         <v>9.2685176508316616</v>
       </c>
       <c r="E69" s="1">
-        <v>1966.2240767521901</v>
+        <v>1769.6016690769711</v>
       </c>
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.2">
@@ -3706,7 +3603,7 @@
         <v>7.6841294141877947</v>
       </c>
       <c r="E70" s="1">
-        <v>4066.5088860102101</v>
+        <v>3659.857997409189</v>
       </c>
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.2">
@@ -3720,7 +3617,7 @@
         <v>40.952331871216593</v>
       </c>
       <c r="E71" s="1">
-        <v>1787.476433411081</v>
+        <v>1608.728790069973</v>
       </c>
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.2">
@@ -3734,7 +3631,7 @@
         <v>7.0963703767689337</v>
       </c>
       <c r="E72" s="1">
-        <v>1474.6680575641419</v>
+        <v>1327.2012518077277</v>
       </c>
     </row>
     <row r="73" spans="2:5" x14ac:dyDescent="0.2">
@@ -3748,7 +3645,7 @@
         <v>21.39058670728862</v>
       </c>
       <c r="E73" s="1">
-        <v>983.1120383760948</v>
+        <v>884.80083453848533</v>
       </c>
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.2">
@@ -3762,7 +3659,7 @@
         <v>34.272769298922341</v>
       </c>
       <c r="E74" s="1">
-        <v>491.5560191880474</v>
+        <v>442.40041726924267</v>
       </c>
     </row>
     <row r="75" spans="2:5" x14ac:dyDescent="0.2">
@@ -3776,7 +3673,7 @@
         <v>3.015405987701675</v>
       </c>
       <c r="E75" s="1">
-        <v>9116.1298103965146</v>
+        <v>8204.516829356864</v>
       </c>
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.2">
@@ -3790,7 +3687,7 @@
         <v>37.853195073141762</v>
       </c>
       <c r="E76" s="1">
-        <v>1787.476433411081</v>
+        <v>1608.728790069973</v>
       </c>
     </row>
     <row r="77" spans="2:5" x14ac:dyDescent="0.2">
@@ -3804,7 +3701,7 @@
         <v>13.217057608613059</v>
       </c>
       <c r="E77" s="1">
-        <v>5362.4293002332442</v>
+        <v>4826.1863702099199</v>
       </c>
     </row>
     <row r="78" spans="2:5" x14ac:dyDescent="0.2">
@@ -3818,7 +3715,7 @@
         <v>23.2202657686422</v>
       </c>
       <c r="E78" s="1">
-        <v>1787.476433411081</v>
+        <v>1608.728790069973</v>
       </c>
     </row>
     <row r="79" spans="2:5" x14ac:dyDescent="0.2">
@@ -3832,7 +3729,7 @@
         <v>18.982176181979089</v>
       </c>
       <c r="E79" s="1">
-        <v>3574.9528668221628</v>
+        <v>3217.4575801399465</v>
       </c>
     </row>
     <row r="80" spans="2:5" x14ac:dyDescent="0.2">
@@ -3846,7 +3743,7 @@
         <v>3.1784868645964859</v>
       </c>
       <c r="E80" s="1">
-        <v>2457.7800959402371</v>
+        <v>2212.0020863462132</v>
       </c>
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.2">
@@ -3860,7 +3757,7 @@
         <v>0</v>
       </c>
       <c r="E81" s="1">
-        <v>3396.21</v>
+        <v>3056.5889999999999</v>
       </c>
     </row>
     <row r="82" spans="2:5" x14ac:dyDescent="0.2">
@@ -3874,7 +3771,7 @@
         <v>6.4541943522926557</v>
       </c>
       <c r="E82" s="1">
-        <v>4066.5088860102101</v>
+        <v>3659.857997409189</v>
       </c>
     </row>
     <row r="83" spans="2:5" x14ac:dyDescent="0.2">
@@ -3888,7 +3785,7 @@
         <v>15.71226546698772</v>
       </c>
       <c r="E83" s="1">
-        <v>3574.9528668221628</v>
+        <v>3217.4575801399465</v>
       </c>
     </row>
     <row r="84" spans="2:5" x14ac:dyDescent="0.2">
@@ -3902,7 +3799,7 @@
         <v>0</v>
       </c>
       <c r="E84" s="1">
-        <v>3396.21</v>
+        <v>3056.5889999999999</v>
       </c>
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.2">
@@ -3916,7 +3813,7 @@
         <v>7.8585521939249183</v>
       </c>
       <c r="E85" s="1">
-        <v>4558.0649051982582</v>
+        <v>4102.2584146784329</v>
       </c>
     </row>
     <row r="86" spans="2:5" x14ac:dyDescent="0.2">
@@ -3930,7 +3827,7 @@
         <v>5.0355148388024782</v>
       </c>
       <c r="E86" s="1">
-        <v>5049.620924386305</v>
+        <v>4544.658831947675</v>
       </c>
     </row>
     <row r="87" spans="2:5" x14ac:dyDescent="0.2">
@@ -3944,7 +3841,7 @@
         <v>9.2751933805249021</v>
       </c>
       <c r="E87" s="1">
-        <v>4558.0649051982582</v>
+        <v>4102.2584146784329</v>
       </c>
     </row>
     <row r="88" spans="2:5" x14ac:dyDescent="0.2">
@@ -3958,7 +3855,7 @@
         <v>34.635602148382418</v>
       </c>
       <c r="E88" s="1">
-        <v>1787.476433411081</v>
+        <v>1608.728790069973</v>
       </c>
     </row>
     <row r="89" spans="2:5" x14ac:dyDescent="0.2">
@@ -3972,7 +3869,7 @@
         <v>16.575315424120681</v>
       </c>
       <c r="E89" s="1">
-        <v>3574.9528668221628</v>
+        <v>3217.4575801399465</v>
       </c>
     </row>
     <row r="90" spans="2:5" x14ac:dyDescent="0.2">
@@ -3986,7 +3883,7 @@
         <v>3.6295743306124741</v>
       </c>
       <c r="E90" s="1">
-        <v>6524.2889819504471</v>
+        <v>5871.8600837554022</v>
       </c>
     </row>
     <row r="91" spans="2:5" x14ac:dyDescent="0.2">
@@ -4000,7 +3897,7 @@
         <v>29.528287650174502</v>
       </c>
       <c r="E91" s="1">
-        <v>1787.476433411081</v>
+        <v>1608.728790069973</v>
       </c>
     </row>
     <row r="92" spans="2:5" x14ac:dyDescent="0.2">
@@ -4014,7 +3911,7 @@
         <v>4.0870533580497641</v>
       </c>
       <c r="E92" s="1">
-        <v>5541.1769435743518</v>
+        <v>4987.0592492169171</v>
       </c>
     </row>
     <row r="93" spans="2:5" x14ac:dyDescent="0.2">
@@ -4028,7 +3925,7 @@
         <v>8.3499774609687787</v>
       </c>
       <c r="E93" s="1">
-        <v>8937.3821670554062</v>
+        <v>8043.6439503498659</v>
       </c>
     </row>
     <row r="94" spans="2:5" x14ac:dyDescent="0.2">
@@ -4042,7 +3939,7 @@
         <v>2.497793180304178</v>
       </c>
       <c r="E94" s="1">
-        <v>11886.71828218369</v>
+        <v>10698.046453965322</v>
       </c>
     </row>
     <row r="95" spans="2:5" x14ac:dyDescent="0.2">
@@ -4056,7 +3953,7 @@
         <v>0</v>
       </c>
       <c r="E95" s="1">
-        <v>3396.21</v>
+        <v>3056.5889999999999</v>
       </c>
     </row>
     <row r="96" spans="2:5" x14ac:dyDescent="0.2">
@@ -4070,7 +3967,7 @@
         <v>18.259514372761348</v>
       </c>
       <c r="E96" s="1">
-        <v>983.1120383760948</v>
+        <v>884.80083453848533</v>
       </c>
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.2">
@@ -4084,7 +3981,7 @@
         <v>44.111583857028762</v>
       </c>
       <c r="E97" s="1">
-        <v>1787.476433411081</v>
+        <v>1608.728790069973</v>
       </c>
     </row>
     <row r="98" spans="2:5" x14ac:dyDescent="0.2">
@@ -4098,7 +3995,7 @@
         <v>5.5549419631575443</v>
       </c>
       <c r="E98" s="1">
-        <v>3262.1444909752231</v>
+        <v>2935.9300418777007</v>
       </c>
     </row>
     <row r="99" spans="2:5" x14ac:dyDescent="0.2">
@@ -4112,7 +4009,7 @@
         <v>7.3645009402854908</v>
       </c>
       <c r="E99" s="1">
-        <v>3262.1444909752231</v>
+        <v>2935.9300418777007</v>
       </c>
     </row>
     <row r="100" spans="2:5" x14ac:dyDescent="0.2">
@@ -4126,7 +4023,7 @@
         <v>33.485661133224987</v>
       </c>
       <c r="E100" s="1">
-        <v>1787.476433411081</v>
+        <v>1608.728790069973</v>
       </c>
     </row>
     <row r="101" spans="2:5" x14ac:dyDescent="0.2">
@@ -4140,7 +4037,7 @@
         <v>30.907247323775319</v>
       </c>
       <c r="E101" s="1">
-        <v>1787.476433411081</v>
+        <v>1608.728790069973</v>
       </c>
     </row>
     <row r="102" spans="2:5" x14ac:dyDescent="0.2">
@@ -4154,7 +4051,7 @@
         <v>3.0263996591392668</v>
       </c>
       <c r="E102" s="1">
-        <v>10412.05022461955</v>
+        <v>9370.8452021575958</v>
       </c>
     </row>
   </sheetData>
@@ -4188,11 +4085,11 @@
       <c r="D1"/>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
       <c r="F2" s="7"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
@@ -4395,11 +4292,11 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5" customWidth="1"/>
-    <col min="2" max="2" width="23.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.5" style="1" customWidth="1"/>
     <col min="9" max="9" width="25.5" style="2" customWidth="1"/>
@@ -4411,9 +4308,8 @@
     <col min="15" max="15" width="17.83203125" style="2" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="7.83203125" style="2" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="10.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="20" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:20" ht="70" customHeight="1" x14ac:dyDescent="0.2">
@@ -4438,8 +4334,8 @@
       <c r="T1"/>
     </row>
     <row r="2" spans="2:20" ht="19" x14ac:dyDescent="0.25">
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
       <c r="D2" s="49" t="s">
         <v>41</v>
       </c>
@@ -4465,16 +4361,16 @@
       <c r="T2" s="50"/>
     </row>
     <row r="3" spans="2:20" ht="21" x14ac:dyDescent="0.2">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="C3" s="44" t="s">
         <v>138</v>
       </c>
       <c r="D3" s="30" t="s">
         <v>148</v>
       </c>
-      <c r="E3" s="53" t="s">
+      <c r="E3" s="44" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="30" t="s">
@@ -4483,8 +4379,8 @@
       <c r="G3" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="53" t="s">
-        <v>188</v>
+      <c r="H3" s="44" t="s">
+        <v>150</v>
       </c>
       <c r="I3" s="30" t="s">
         <v>42</v>
@@ -4542,7 +4438,7 @@
       <c r="G4" s="29">
         <v>0.05</v>
       </c>
-      <c r="H4" s="52" t="b">
+      <c r="H4" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I4" s="29">
@@ -4566,8 +4462,8 @@
       <c r="O4" s="29">
         <v>2659.2149999999997</v>
       </c>
-      <c r="P4" s="35">
-        <v>27.32280368098159</v>
+      <c r="P4" s="37">
+        <v>10</v>
       </c>
       <c r="Q4" s="36">
         <v>1</v>
@@ -4576,11 +4472,11 @@
         <f>E4*95</f>
         <v>252625.42499999996</v>
       </c>
-      <c r="S4" s="36">
-        <v>0</v>
-      </c>
-      <c r="T4" s="36">
-        <v>0</v>
+      <c r="S4" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="T4" s="35" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="2:20" ht="19" x14ac:dyDescent="0.25">
@@ -4602,7 +4498,7 @@
       <c r="G5" s="29">
         <v>0.05</v>
       </c>
-      <c r="H5" s="52" t="b">
+      <c r="H5" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I5" s="29">
@@ -4626,8 +4522,8 @@
       <c r="O5" s="29">
         <v>900.77</v>
       </c>
-      <c r="P5" s="35">
-        <v>27.32280368098159</v>
+      <c r="P5" s="37">
+        <v>10</v>
       </c>
       <c r="Q5" s="36">
         <v>1</v>
@@ -4636,11 +4532,11 @@
         <f t="shared" ref="R5:R7" si="0">E5*95</f>
         <v>85573.15</v>
       </c>
-      <c r="S5" s="36">
-        <v>0</v>
-      </c>
-      <c r="T5" s="36">
-        <v>0</v>
+      <c r="S5" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="T5" s="35" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="2:20" ht="19" x14ac:dyDescent="0.25">
@@ -4662,7 +4558,7 @@
       <c r="G6" s="29">
         <v>0.05</v>
       </c>
-      <c r="H6" s="52" t="b">
+      <c r="H6" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I6" s="29">
@@ -4686,21 +4582,21 @@
       <c r="O6" s="29">
         <v>931.18999999999994</v>
       </c>
-      <c r="P6" s="35">
-        <v>27.32280368098159</v>
+      <c r="P6" s="37">
+        <v>10</v>
       </c>
       <c r="Q6" s="36">
         <v>1</v>
       </c>
       <c r="R6" s="37">
-        <f t="shared" si="0"/>
+        <f>E6*95</f>
         <v>88463.049999999988</v>
       </c>
-      <c r="S6" s="36">
-        <v>0</v>
-      </c>
-      <c r="T6" s="36">
-        <v>0</v>
+      <c r="S6" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="T6" s="35" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="2:20" ht="19" x14ac:dyDescent="0.25">
@@ -4722,7 +4618,7 @@
       <c r="G7" s="29">
         <v>0.05</v>
       </c>
-      <c r="H7" s="52" t="b">
+      <c r="H7" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I7" s="29">
@@ -4746,8 +4642,8 @@
       <c r="O7" s="29">
         <v>1768.585</v>
       </c>
-      <c r="P7" s="35">
-        <v>27.32280368098159</v>
+      <c r="P7" s="37">
+        <v>10</v>
       </c>
       <c r="Q7" s="38">
         <v>1</v>
@@ -4756,11 +4652,11 @@
         <f t="shared" si="0"/>
         <v>168015.57500000001</v>
       </c>
-      <c r="S7" s="36">
-        <v>0</v>
-      </c>
-      <c r="T7" s="36">
-        <v>0</v>
+      <c r="S7" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="T7" s="35" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="2:20" ht="19" x14ac:dyDescent="0.25">
@@ -4783,7 +4679,7 @@
       <c r="G8" s="36">
         <v>0.5</v>
       </c>
-      <c r="H8" s="52" t="b">
+      <c r="H8" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I8" s="36">
@@ -4844,7 +4740,7 @@
       <c r="G9" s="36">
         <v>0.5</v>
       </c>
-      <c r="H9" s="52" t="b">
+      <c r="H9" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I9" s="36">
@@ -4905,7 +4801,7 @@
       <c r="G10" s="36">
         <v>0.5</v>
       </c>
-      <c r="H10" s="52" t="b">
+      <c r="H10" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I10" s="36">
@@ -4966,7 +4862,7 @@
       <c r="G11" s="36">
         <v>0.5</v>
       </c>
-      <c r="H11" s="52" t="b">
+      <c r="H11" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I11" s="36">
@@ -5027,7 +4923,7 @@
       <c r="G12" s="36">
         <v>0.5</v>
       </c>
-      <c r="H12" s="52" t="b">
+      <c r="H12" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I12" s="36">
@@ -5088,7 +4984,7 @@
       <c r="G13" s="36">
         <v>0.5</v>
       </c>
-      <c r="H13" s="52" t="b">
+      <c r="H13" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I13" s="36">
@@ -5149,7 +5045,7 @@
       <c r="G14" s="36">
         <v>0.5</v>
       </c>
-      <c r="H14" s="52" t="b">
+      <c r="H14" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I14" s="36">
@@ -5210,7 +5106,7 @@
       <c r="G15" s="36">
         <v>0.5</v>
       </c>
-      <c r="H15" s="52" t="b">
+      <c r="H15" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I15" s="36">
@@ -5271,7 +5167,7 @@
       <c r="G16" s="36">
         <v>0.5</v>
       </c>
-      <c r="H16" s="52" t="b">
+      <c r="H16" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I16" s="36">
@@ -5302,7 +5198,7 @@
         <v>0.6</v>
       </c>
       <c r="R16" s="36">
-        <f t="shared" si="2"/>
+        <f>E16*40</f>
         <v>34240</v>
       </c>
       <c r="S16" s="36">
@@ -5332,7 +5228,7 @@
       <c r="G17" s="36">
         <v>0.5</v>
       </c>
-      <c r="H17" s="52" t="b">
+      <c r="H17" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I17" s="36">
@@ -5393,7 +5289,7 @@
       <c r="G18" s="36">
         <v>0.5</v>
       </c>
-      <c r="H18" s="52" t="b">
+      <c r="H18" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I18" s="36">
@@ -5454,7 +5350,7 @@
       <c r="G19" s="36">
         <v>0.5</v>
       </c>
-      <c r="H19" s="52" t="b">
+      <c r="H19" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I19" s="36">
@@ -5515,7 +5411,7 @@
       <c r="G20" s="36">
         <v>0.5</v>
       </c>
-      <c r="H20" s="52" t="b">
+      <c r="H20" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I20" s="36">
@@ -5576,7 +5472,7 @@
       <c r="G21" s="36">
         <v>0.5</v>
       </c>
-      <c r="H21" s="52" t="b">
+      <c r="H21" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I21" s="36">
@@ -5637,7 +5533,7 @@
       <c r="G22" s="36">
         <v>0.5</v>
       </c>
-      <c r="H22" s="52" t="b">
+      <c r="H22" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I22" s="36">
@@ -5698,7 +5594,7 @@
       <c r="G23" s="36">
         <v>0.5</v>
       </c>
-      <c r="H23" s="52" t="b">
+      <c r="H23" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I23" s="36">
@@ -5759,7 +5655,7 @@
       <c r="G24" s="36">
         <v>0.5</v>
       </c>
-      <c r="H24" s="52" t="b">
+      <c r="H24" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I24" s="36">
@@ -5820,7 +5716,7 @@
       <c r="G25" s="36">
         <v>0.5</v>
       </c>
-      <c r="H25" s="52" t="b">
+      <c r="H25" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I25" s="36">
@@ -5881,7 +5777,7 @@
       <c r="G26" s="36">
         <v>0.5</v>
       </c>
-      <c r="H26" s="52" t="b">
+      <c r="H26" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I26" s="36">
@@ -5942,7 +5838,7 @@
       <c r="G27" s="36">
         <v>0.5</v>
       </c>
-      <c r="H27" s="52" t="b">
+      <c r="H27" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I27" s="36">
@@ -6003,7 +5899,7 @@
       <c r="G28" s="36">
         <v>0.5</v>
       </c>
-      <c r="H28" s="52" t="b">
+      <c r="H28" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I28" s="36">
@@ -6064,7 +5960,7 @@
       <c r="G29" s="36">
         <v>0.5</v>
       </c>
-      <c r="H29" s="52" t="b">
+      <c r="H29" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I29" s="36">
@@ -6125,7 +6021,7 @@
       <c r="G30" s="36">
         <v>0.5</v>
       </c>
-      <c r="H30" s="52" t="b">
+      <c r="H30" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I30" s="36">
@@ -6186,7 +6082,7 @@
       <c r="G31" s="36">
         <v>0.5</v>
       </c>
-      <c r="H31" s="52" t="b">
+      <c r="H31" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I31" s="36">
@@ -6247,7 +6143,7 @@
       <c r="G32" s="36">
         <v>0.5</v>
       </c>
-      <c r="H32" s="52" t="b">
+      <c r="H32" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I32" s="36">
@@ -6308,7 +6204,7 @@
       <c r="G33" s="36">
         <v>0.5</v>
       </c>
-      <c r="H33" s="52" t="b">
+      <c r="H33" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I33" s="36">
@@ -6369,7 +6265,7 @@
       <c r="G34" s="36">
         <v>0.5</v>
       </c>
-      <c r="H34" s="52" t="b">
+      <c r="H34" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I34" s="36">
@@ -6430,7 +6326,7 @@
       <c r="G35" s="36">
         <v>0.5</v>
       </c>
-      <c r="H35" s="52" t="b">
+      <c r="H35" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I35" s="36">
@@ -6491,7 +6387,7 @@
       <c r="G36" s="36">
         <v>0.5</v>
       </c>
-      <c r="H36" s="52" t="b">
+      <c r="H36" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I36" s="36">
@@ -6552,7 +6448,7 @@
       <c r="G37" s="36">
         <v>0.5</v>
       </c>
-      <c r="H37" s="52" t="b">
+      <c r="H37" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I37" s="36">
@@ -6613,7 +6509,7 @@
       <c r="G38" s="36">
         <v>0.5</v>
       </c>
-      <c r="H38" s="52" t="b">
+      <c r="H38" s="43" t="b">
         <v>1</v>
       </c>
       <c r="I38" s="36">
@@ -6673,7 +6569,7 @@
       <c r="G39" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="H39" s="52" t="b">
+      <c r="H39" s="43" t="b">
         <v>0</v>
       </c>
       <c r="I39" s="35" t="s">
@@ -6732,7 +6628,7 @@
       <c r="G40" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="H40" s="52" t="b">
+      <c r="H40" s="43" t="b">
         <v>0</v>
       </c>
       <c r="I40" s="35" t="s">
@@ -6791,7 +6687,7 @@
       <c r="G41" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="H41" s="52" t="b">
+      <c r="H41" s="43" t="b">
         <v>0</v>
       </c>
       <c r="I41" s="35" t="s">
@@ -6850,7 +6746,7 @@
       <c r="G42" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="H42" s="52" t="b">
+      <c r="H42" s="43" t="b">
         <v>0</v>
       </c>
       <c r="I42" s="35" t="s">
@@ -6909,7 +6805,7 @@
       <c r="G43" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="H43" s="52" t="b">
+      <c r="H43" s="43" t="b">
         <v>0</v>
       </c>
       <c r="I43" s="35" t="s">
@@ -6968,7 +6864,7 @@
       <c r="G44" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="H44" s="52" t="b">
+      <c r="H44" s="43" t="b">
         <v>0</v>
       </c>
       <c r="I44" s="35" t="s">
@@ -7027,7 +6923,7 @@
       <c r="G45" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="H45" s="52" t="b">
+      <c r="H45" s="43" t="b">
         <v>0</v>
       </c>
       <c r="I45" s="35" t="s">
@@ -7086,7 +6982,7 @@
       <c r="G46" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="H46" s="52" t="b">
+      <c r="H46" s="43" t="b">
         <v>0</v>
       </c>
       <c r="I46" s="35" t="s">
@@ -7145,7 +7041,7 @@
       <c r="G47" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="H47" s="52" t="b">
+      <c r="H47" s="43" t="b">
         <v>0</v>
       </c>
       <c r="I47" s="35" t="s">
@@ -7204,7 +7100,7 @@
       <c r="G48" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="H48" s="52" t="b">
+      <c r="H48" s="43" t="b">
         <v>0</v>
       </c>
       <c r="I48" s="35" t="s">
@@ -7263,7 +7159,7 @@
       <c r="G49" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H49" s="52" t="b">
+      <c r="H49" s="43" t="b">
         <v>0</v>
       </c>
       <c r="I49" s="28" t="s">
@@ -7322,7 +7218,7 @@
       <c r="G50" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H50" s="52" t="b">
+      <c r="H50" s="43" t="b">
         <v>0</v>
       </c>
       <c r="I50" s="28" t="s">
@@ -7381,7 +7277,7 @@
       <c r="G51" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H51" s="52" t="b">
+      <c r="H51" s="43" t="b">
         <v>0</v>
       </c>
       <c r="I51" s="28" t="s">
@@ -7406,7 +7302,7 @@
         <v>142</v>
       </c>
       <c r="P51" s="26">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="Q51" s="29">
         <v>0.46800000000000003</v>
@@ -7440,7 +7336,7 @@
       <c r="G52" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H52" s="52" t="b">
+      <c r="H52" s="43" t="b">
         <v>0</v>
       </c>
       <c r="I52" s="28" t="s">
@@ -7465,7 +7361,7 @@
         <v>142</v>
       </c>
       <c r="P52" s="26">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="Q52" s="29">
         <v>0.46800000000000003</v>
@@ -7499,7 +7395,7 @@
       <c r="G53" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H53" s="52" t="b">
+      <c r="H53" s="43" t="b">
         <v>0</v>
       </c>
       <c r="I53" s="28" t="s">
@@ -7524,7 +7420,7 @@
         <v>142</v>
       </c>
       <c r="P53" s="26">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="Q53" s="29">
         <v>0.46800000000000003</v>
@@ -7558,7 +7454,7 @@
       <c r="G54" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H54" s="52" t="b">
+      <c r="H54" s="43" t="b">
         <v>0</v>
       </c>
       <c r="I54" s="28" t="s">
@@ -7583,7 +7479,7 @@
         <v>142</v>
       </c>
       <c r="P54" s="26">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="Q54" s="29">
         <v>0.46800000000000003</v>
@@ -7617,7 +7513,7 @@
       <c r="G55" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H55" s="52" t="b">
+      <c r="H55" s="43" t="b">
         <v>0</v>
       </c>
       <c r="I55" s="28" t="s">
@@ -7642,7 +7538,7 @@
         <v>142</v>
       </c>
       <c r="P55" s="26">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="Q55" s="29">
         <v>0.46800000000000003</v>
@@ -7676,7 +7572,7 @@
       <c r="G56" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H56" s="52" t="b">
+      <c r="H56" s="43" t="b">
         <v>0</v>
       </c>
       <c r="I56" s="28" t="s">
@@ -7701,7 +7597,7 @@
         <v>142</v>
       </c>
       <c r="P56" s="26">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="Q56" s="29">
         <v>0.46800000000000003</v>
@@ -7735,7 +7631,7 @@
       <c r="G57" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H57" s="52" t="b">
+      <c r="H57" s="43" t="b">
         <v>0</v>
       </c>
       <c r="I57" s="28" t="s">
@@ -7760,7 +7656,7 @@
         <v>142</v>
       </c>
       <c r="P57" s="26">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="Q57" s="29">
         <v>0.46800000000000003</v>
@@ -7794,7 +7690,7 @@
       <c r="G58" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H58" s="52" t="b">
+      <c r="H58" s="43" t="b">
         <v>0</v>
       </c>
       <c r="I58" s="28" t="s">
@@ -7819,7 +7715,7 @@
         <v>142</v>
       </c>
       <c r="P58" s="26">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="Q58" s="29">
         <v>0.46800000000000003</v>
@@ -7853,7 +7749,7 @@
       <c r="G59" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H59" s="52" t="b">
+      <c r="H59" s="43" t="b">
         <v>0</v>
       </c>
       <c r="I59" s="28" t="s">
@@ -7878,7 +7774,7 @@
         <v>142</v>
       </c>
       <c r="P59" s="26">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="Q59" s="29">
         <v>0.46800000000000003</v>
@@ -7912,7 +7808,7 @@
       <c r="G60" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H60" s="52" t="b">
+      <c r="H60" s="43" t="b">
         <v>0</v>
       </c>
       <c r="I60" s="28" t="s">
@@ -7937,7 +7833,7 @@
         <v>142</v>
       </c>
       <c r="P60" s="26">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="Q60" s="29">
         <v>0.46800000000000003</v>
@@ -7971,7 +7867,7 @@
       <c r="G61" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H61" s="52" t="b">
+      <c r="H61" s="43" t="b">
         <v>0</v>
       </c>
       <c r="I61" s="28" t="s">
@@ -7996,7 +7892,7 @@
         <v>142</v>
       </c>
       <c r="P61" s="26">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="Q61" s="29">
         <v>0.46800000000000003</v>
@@ -8030,7 +7926,7 @@
       <c r="G62" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H62" s="52" t="b">
+      <c r="H62" s="43" t="b">
         <v>0</v>
       </c>
       <c r="I62" s="28" t="s">
@@ -8055,7 +7951,7 @@
         <v>142</v>
       </c>
       <c r="P62" s="26">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="Q62" s="29">
         <v>0.46800000000000003</v>
@@ -8089,7 +7985,7 @@
       <c r="G63" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H63" s="52" t="b">
+      <c r="H63" s="43" t="b">
         <v>0</v>
       </c>
       <c r="I63" s="28" t="s">
@@ -8114,7 +8010,7 @@
         <v>142</v>
       </c>
       <c r="P63" s="26">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="Q63" s="29">
         <v>0.46800000000000003</v>
@@ -8148,7 +8044,7 @@
       <c r="G64" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H64" s="52" t="b">
+      <c r="H64" s="43" t="b">
         <v>0</v>
       </c>
       <c r="I64" s="28" t="s">
@@ -8173,7 +8069,7 @@
         <v>142</v>
       </c>
       <c r="P64" s="26">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="Q64" s="29">
         <v>0.46800000000000003</v>
@@ -8207,7 +8103,7 @@
       <c r="G65" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H65" s="52" t="b">
+      <c r="H65" s="43" t="b">
         <v>0</v>
       </c>
       <c r="I65" s="28" t="s">
@@ -8232,7 +8128,7 @@
         <v>142</v>
       </c>
       <c r="P65" s="26">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="Q65" s="29">
         <v>0.46800000000000003</v>
@@ -8283,34 +8179,34 @@
   <sheetData>
     <row r="1" spans="2:28" ht="58" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C2" s="47" t="s">
+      <c r="C2" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="H2" s="48" t="s">
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="H2" s="47" t="s">
         <v>123</v>
       </c>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
-      <c r="W2" s="48"/>
-      <c r="X2" s="48"/>
-      <c r="Y2" s="48"/>
-      <c r="Z2" s="48"/>
-      <c r="AA2" s="48"/>
-      <c r="AB2" s="48"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="47"/>
+      <c r="S2" s="47"/>
+      <c r="T2" s="47"/>
+      <c r="U2" s="47"/>
+      <c r="V2" s="47"/>
+      <c r="W2" s="47"/>
+      <c r="X2" s="47"/>
+      <c r="Y2" s="47"/>
+      <c r="Z2" s="47"/>
+      <c r="AA2" s="47"/>
+      <c r="AB2" s="47"/>
     </row>
     <row r="3" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B3" s="5" t="s">
@@ -9507,29 +9403,29 @@
       <c r="E19" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H19" s="48" t="s">
+      <c r="H19" s="47" t="s">
         <v>122</v>
       </c>
-      <c r="I19" s="48"/>
-      <c r="J19" s="48"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="48"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="48"/>
-      <c r="O19" s="48"/>
-      <c r="P19" s="48"/>
-      <c r="Q19" s="48"/>
-      <c r="R19" s="48"/>
-      <c r="S19" s="48"/>
-      <c r="T19" s="48"/>
-      <c r="U19" s="48"/>
-      <c r="V19" s="48"/>
-      <c r="W19" s="48"/>
-      <c r="X19" s="48"/>
-      <c r="Y19" s="48"/>
-      <c r="Z19" s="48"/>
-      <c r="AA19" s="48"/>
-      <c r="AB19" s="48"/>
+      <c r="I19" s="47"/>
+      <c r="J19" s="47"/>
+      <c r="K19" s="47"/>
+      <c r="L19" s="47"/>
+      <c r="M19" s="47"/>
+      <c r="N19" s="47"/>
+      <c r="O19" s="47"/>
+      <c r="P19" s="47"/>
+      <c r="Q19" s="47"/>
+      <c r="R19" s="47"/>
+      <c r="S19" s="47"/>
+      <c r="T19" s="47"/>
+      <c r="U19" s="47"/>
+      <c r="V19" s="47"/>
+      <c r="W19" s="47"/>
+      <c r="X19" s="47"/>
+      <c r="Y19" s="47"/>
+      <c r="Z19" s="47"/>
+      <c r="AA19" s="47"/>
+      <c r="AB19" s="47"/>
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
@@ -9646,19 +9542,19 @@
         <v>3343.9969999999998</v>
       </c>
       <c r="N21" s="19">
-        <v>494.03</v>
+        <v>493</v>
       </c>
       <c r="O21" s="19">
-        <v>35.307000000000002</v>
+        <v>35</v>
       </c>
       <c r="P21" s="19">
-        <v>193.845</v>
+        <v>193</v>
       </c>
       <c r="Q21" s="19">
         <v>988.83879999999999</v>
       </c>
       <c r="R21" s="19">
-        <v>448.18</v>
+        <v>448</v>
       </c>
       <c r="S21" s="19">
         <v>1797.05</v>
@@ -9673,7 +9569,7 @@
         <v>3799.9992000000002</v>
       </c>
       <c r="W21" s="2">
-        <v>39.375</v>
+        <v>39</v>
       </c>
       <c r="X21" s="19">
         <v>1283.51</v>
@@ -9685,7 +9581,7 @@
         <v>3324.047</v>
       </c>
       <c r="AA21" s="19">
-        <v>263.286</v>
+        <v>263</v>
       </c>
       <c r="AB21" s="2">
         <v>0</v>
@@ -9726,19 +9622,19 @@
         <v>3343.9969999999998</v>
       </c>
       <c r="N22" s="19">
-        <v>494.03</v>
+        <v>493</v>
       </c>
       <c r="O22" s="19">
-        <v>35.307000000000002</v>
+        <v>35</v>
       </c>
       <c r="P22" s="19">
-        <v>193.845</v>
+        <v>193</v>
       </c>
       <c r="Q22" s="19">
         <v>988.83879999999999</v>
       </c>
       <c r="R22" s="19">
-        <v>448.18</v>
+        <v>448</v>
       </c>
       <c r="S22" s="19">
         <v>1815.51</v>
@@ -9753,7 +9649,7 @@
         <v>3799.9992000000002</v>
       </c>
       <c r="W22" s="2">
-        <v>39.375</v>
+        <v>39</v>
       </c>
       <c r="X22" s="19">
         <v>1285.31</v>
@@ -9765,7 +9661,7 @@
         <v>3324.0574999999999</v>
       </c>
       <c r="AA22" s="19">
-        <v>263.286</v>
+        <v>263</v>
       </c>
       <c r="AB22" s="2">
         <v>0</v>
@@ -9806,19 +9702,19 @@
         <v>3358.0970000000002</v>
       </c>
       <c r="N23" s="19">
-        <v>494.03</v>
+        <v>493</v>
       </c>
       <c r="O23" s="19">
-        <v>35.307000000000002</v>
+        <v>35</v>
       </c>
       <c r="P23" s="19">
-        <v>193.845</v>
+        <v>193</v>
       </c>
       <c r="Q23" s="19">
         <v>988.83879999999999</v>
       </c>
       <c r="R23" s="19">
-        <v>448.18</v>
+        <v>448</v>
       </c>
       <c r="S23" s="19">
         <v>1815.51</v>
@@ -9833,7 +9729,7 @@
         <v>3799.9992000000002</v>
       </c>
       <c r="W23" s="2">
-        <v>39.375</v>
+        <v>39</v>
       </c>
       <c r="X23" s="19">
         <v>1285.31</v>
@@ -9845,7 +9741,7 @@
         <v>3325.8575000000001</v>
       </c>
       <c r="AA23" s="19">
-        <v>263.286</v>
+        <v>263</v>
       </c>
       <c r="AB23" s="2">
         <v>0</v>
@@ -9885,20 +9781,20 @@
       <c r="M24" s="2">
         <v>3360.4969999999998</v>
       </c>
-      <c r="N24" s="2">
-        <v>494.03</v>
-      </c>
-      <c r="O24" s="2">
-        <v>35.307000000000002</v>
-      </c>
-      <c r="P24" s="2">
-        <v>193.845</v>
+      <c r="N24" s="19">
+        <v>493</v>
+      </c>
+      <c r="O24" s="19">
+        <v>35</v>
+      </c>
+      <c r="P24" s="19">
+        <v>193</v>
       </c>
       <c r="Q24" s="2">
         <v>1017.8088</v>
       </c>
-      <c r="R24" s="2">
-        <v>448.18</v>
+      <c r="R24" s="19">
+        <v>448</v>
       </c>
       <c r="S24" s="2">
         <v>1815.51</v>
@@ -9913,7 +9809,7 @@
         <v>3799.9992000000002</v>
       </c>
       <c r="W24" s="2">
-        <v>39.375</v>
+        <v>39</v>
       </c>
       <c r="X24" s="2">
         <v>1285.31</v>
@@ -9924,8 +9820,8 @@
       <c r="Z24" s="2">
         <v>3325.8575000000001</v>
       </c>
-      <c r="AA24" s="2">
-        <v>263.286</v>
+      <c r="AA24" s="19">
+        <v>263</v>
       </c>
       <c r="AB24" s="2">
         <v>0</v>
@@ -9965,20 +9861,20 @@
       <c r="M25" s="2">
         <v>3384.1469999999999</v>
       </c>
-      <c r="N25" s="2">
-        <v>494.03</v>
-      </c>
-      <c r="O25" s="2">
-        <v>35.307000000000002</v>
-      </c>
-      <c r="P25" s="2">
-        <v>193.845</v>
+      <c r="N25" s="19">
+        <v>493</v>
+      </c>
+      <c r="O25" s="19">
+        <v>35</v>
+      </c>
+      <c r="P25" s="19">
+        <v>193</v>
       </c>
       <c r="Q25" s="2">
         <v>974.00879999999995</v>
       </c>
-      <c r="R25" s="2">
-        <v>448.18</v>
+      <c r="R25" s="19">
+        <v>448</v>
       </c>
       <c r="S25" s="2">
         <v>1818.51</v>
@@ -9993,7 +9889,7 @@
         <v>3800.2242000000001</v>
       </c>
       <c r="W25" s="2">
-        <v>39.375</v>
+        <v>39</v>
       </c>
       <c r="X25" s="2">
         <v>1285.31</v>
@@ -10004,8 +9900,8 @@
       <c r="Z25" s="2">
         <v>3325.8575000000001</v>
       </c>
-      <c r="AA25" s="2">
-        <v>263.286</v>
+      <c r="AA25" s="19">
+        <v>263</v>
       </c>
       <c r="AB25" s="2">
         <v>0</v>
@@ -10045,20 +9941,20 @@
       <c r="M26" s="2">
         <v>3397.4720000000002</v>
       </c>
-      <c r="N26" s="2">
-        <v>494.03</v>
-      </c>
-      <c r="O26" s="2">
-        <v>35.307000000000002</v>
-      </c>
-      <c r="P26" s="2">
-        <v>193.845</v>
+      <c r="N26" s="19">
+        <v>493</v>
+      </c>
+      <c r="O26" s="19">
+        <v>35</v>
+      </c>
+      <c r="P26" s="19">
+        <v>193</v>
       </c>
       <c r="Q26" s="2">
         <v>929.60879999999997</v>
       </c>
-      <c r="R26" s="2">
-        <v>448.18</v>
+      <c r="R26" s="19">
+        <v>448</v>
       </c>
       <c r="S26" s="2">
         <v>1815.85</v>
@@ -10073,7 +9969,7 @@
         <v>3809.2242000000001</v>
       </c>
       <c r="W26" s="2">
-        <v>39.375</v>
+        <v>39</v>
       </c>
       <c r="X26" s="2">
         <v>1287.6600000000001</v>
@@ -10084,8 +9980,8 @@
       <c r="Z26" s="2">
         <v>3325.8575000000001</v>
       </c>
-      <c r="AA26" s="2">
-        <v>263.286</v>
+      <c r="AA26" s="19">
+        <v>263</v>
       </c>
       <c r="AB26" s="2">
         <v>0</v>
@@ -10125,20 +10021,20 @@
       <c r="M27" s="2">
         <v>3652.6320000000001</v>
       </c>
-      <c r="N27" s="2">
-        <v>494.03</v>
-      </c>
-      <c r="O27" s="2">
-        <v>35.307000000000002</v>
-      </c>
-      <c r="P27" s="2">
-        <v>193.845</v>
+      <c r="N27" s="19">
+        <v>493</v>
+      </c>
+      <c r="O27" s="19">
+        <v>35</v>
+      </c>
+      <c r="P27" s="19">
+        <v>193</v>
       </c>
       <c r="Q27" s="2">
         <v>978.11879999999996</v>
       </c>
-      <c r="R27" s="2">
-        <v>448.18</v>
+      <c r="R27" s="19">
+        <v>448</v>
       </c>
       <c r="S27" s="2">
         <v>2143.62</v>
@@ -10153,7 +10049,7 @@
         <v>3812.2242000000001</v>
       </c>
       <c r="W27" s="2">
-        <v>39.375</v>
+        <v>39</v>
       </c>
       <c r="X27" s="2">
         <v>1287.6600000000001</v>
@@ -10164,8 +10060,8 @@
       <c r="Z27" s="2">
         <v>3407.0574999999999</v>
       </c>
-      <c r="AA27" s="2">
-        <v>263.286</v>
+      <c r="AA27" s="19">
+        <v>263</v>
       </c>
       <c r="AB27" s="2">
         <v>0</v>
@@ -10205,20 +10101,20 @@
       <c r="M28" s="2">
         <v>3838.0619999999999</v>
       </c>
-      <c r="N28" s="2">
-        <v>495.03</v>
-      </c>
-      <c r="O28" s="2">
-        <v>35.307000000000002</v>
-      </c>
-      <c r="P28" s="2">
-        <v>193.845</v>
+      <c r="N28" s="19">
+        <v>493</v>
+      </c>
+      <c r="O28" s="19">
+        <v>35</v>
+      </c>
+      <c r="P28" s="19">
+        <v>193</v>
       </c>
       <c r="Q28" s="2">
         <v>1180.0788</v>
       </c>
-      <c r="R28" s="2">
-        <v>448.18</v>
+      <c r="R28" s="19">
+        <v>448</v>
       </c>
       <c r="S28" s="2">
         <v>3668.05</v>
@@ -10233,7 +10129,7 @@
         <v>3877.2242000000001</v>
       </c>
       <c r="W28" s="2">
-        <v>39.375</v>
+        <v>39</v>
       </c>
       <c r="X28" s="2">
         <v>1287.6600000000001</v>
@@ -10244,8 +10140,8 @@
       <c r="Z28" s="2">
         <v>3473.2075</v>
       </c>
-      <c r="AA28" s="2">
-        <v>263.286</v>
+      <c r="AA28" s="19">
+        <v>263</v>
       </c>
       <c r="AB28" s="2">
         <v>0</v>
@@ -10286,19 +10182,19 @@
         <v>3878.8620000000001</v>
       </c>
       <c r="N29" s="2">
-        <v>623.65499999999997</v>
-      </c>
-      <c r="O29" s="2">
-        <v>35.307000000000002</v>
-      </c>
-      <c r="P29" s="2">
-        <v>193.845</v>
+        <v>623</v>
+      </c>
+      <c r="O29" s="19">
+        <v>35</v>
+      </c>
+      <c r="P29" s="19">
+        <v>193</v>
       </c>
       <c r="Q29" s="2">
         <v>1234.8438000000001</v>
       </c>
-      <c r="R29" s="2">
-        <v>448.18</v>
+      <c r="R29" s="19">
+        <v>448</v>
       </c>
       <c r="S29" s="2">
         <v>4409.0550000000003</v>
@@ -10313,7 +10209,7 @@
         <v>3945.9241999999999</v>
       </c>
       <c r="W29" s="2">
-        <v>39.375</v>
+        <v>39</v>
       </c>
       <c r="X29" s="2">
         <v>1292.1600000000001</v>
@@ -10324,8 +10220,8 @@
       <c r="Z29" s="2">
         <v>3473.2075</v>
       </c>
-      <c r="AA29" s="2">
-        <v>263.27999999999997</v>
+      <c r="AA29" s="19">
+        <v>263</v>
       </c>
       <c r="AB29" s="2">
         <v>0</v>
@@ -10366,19 +10262,19 @@
         <v>3907.0520000000001</v>
       </c>
       <c r="N30" s="2">
-        <v>673.65499999999997</v>
-      </c>
-      <c r="O30" s="2">
-        <v>35.307000000000002</v>
-      </c>
-      <c r="P30" s="2">
-        <v>193.845</v>
+        <v>673</v>
+      </c>
+      <c r="O30" s="19">
+        <v>35</v>
+      </c>
+      <c r="P30" s="19">
+        <v>193</v>
       </c>
       <c r="Q30" s="2">
         <v>1284.8388</v>
       </c>
-      <c r="R30" s="2">
-        <v>448.18</v>
+      <c r="R30" s="19">
+        <v>448</v>
       </c>
       <c r="S30" s="2">
         <v>4814.8249999999998</v>
@@ -10393,7 +10289,7 @@
         <v>4778.6242000000002</v>
       </c>
       <c r="W30" s="2">
-        <v>39.375</v>
+        <v>39</v>
       </c>
       <c r="X30" s="2">
         <v>1292.1600000000001</v>
@@ -10404,8 +10300,8 @@
       <c r="Z30" s="2">
         <v>3535.1075000000001</v>
       </c>
-      <c r="AA30" s="2">
-        <v>263.27999999999997</v>
+      <c r="AA30" s="19">
+        <v>263</v>
       </c>
       <c r="AB30" s="2">
         <v>0</v>
@@ -10446,19 +10342,19 @@
         <v>3915.002</v>
       </c>
       <c r="N31" s="2">
-        <v>674.33799999999997</v>
-      </c>
-      <c r="O31" s="2">
-        <v>35.307000000000002</v>
-      </c>
-      <c r="P31" s="2">
-        <v>193.845</v>
+        <v>674</v>
+      </c>
+      <c r="O31" s="19">
+        <v>35</v>
+      </c>
+      <c r="P31" s="19">
+        <v>193</v>
       </c>
       <c r="Q31" s="2">
         <v>1486.2467999999999</v>
       </c>
-      <c r="R31" s="2">
-        <v>448.18</v>
+      <c r="R31" s="19">
+        <v>448</v>
       </c>
       <c r="S31" s="2">
         <v>4966.6450000000004</v>
@@ -10473,7 +10369,7 @@
         <v>4875.7241999999997</v>
       </c>
       <c r="W31" s="2">
-        <v>88.875</v>
+        <v>88</v>
       </c>
       <c r="X31" s="2">
         <v>1339.86</v>
@@ -10484,8 +10380,8 @@
       <c r="Z31" s="2">
         <v>3609.6075000000001</v>
       </c>
-      <c r="AA31" s="2">
-        <v>263.27999999999997</v>
+      <c r="AA31" s="19">
+        <v>263</v>
       </c>
       <c r="AB31" s="2">
         <v>0</v>
@@ -10526,19 +10422,19 @@
         <v>3940.502</v>
       </c>
       <c r="N32" s="2">
-        <v>674.33799999999997</v>
-      </c>
-      <c r="O32" s="2">
-        <v>35.307000000000002</v>
-      </c>
-      <c r="P32" s="2">
-        <v>193.845</v>
+        <v>674</v>
+      </c>
+      <c r="O32" s="19">
+        <v>35</v>
+      </c>
+      <c r="P32" s="19">
+        <v>193</v>
       </c>
       <c r="Q32" s="2">
         <v>1486.2467999999999</v>
       </c>
-      <c r="R32" s="2">
-        <v>448.18</v>
+      <c r="R32" s="19">
+        <v>448</v>
       </c>
       <c r="S32" s="2">
         <v>5404.9449999999997</v>
@@ -10553,7 +10449,7 @@
         <v>4977.7241999999997</v>
       </c>
       <c r="W32" s="2">
-        <v>88.875</v>
+        <v>88</v>
       </c>
       <c r="X32" s="2">
         <v>1397.15</v>
@@ -10564,8 +10460,8 @@
       <c r="Z32" s="2">
         <v>3661.8074999999999</v>
       </c>
-      <c r="AA32" s="2">
-        <v>263.27999999999997</v>
+      <c r="AA32" s="19">
+        <v>263</v>
       </c>
       <c r="AB32" s="2">
         <v>0</v>
@@ -10606,19 +10502,19 @@
         <v>3963.8519999999999</v>
       </c>
       <c r="N33" s="2">
-        <v>674.33799999999997</v>
-      </c>
-      <c r="O33" s="2">
-        <v>35.307000000000002</v>
-      </c>
-      <c r="P33" s="2">
-        <v>193.845</v>
+        <v>674</v>
+      </c>
+      <c r="O33" s="19">
+        <v>35</v>
+      </c>
+      <c r="P33" s="19">
+        <v>193</v>
       </c>
       <c r="Q33" s="2">
         <v>1536.2467999999999</v>
       </c>
-      <c r="R33" s="2">
-        <v>448.18</v>
+      <c r="R33" s="19">
+        <v>448</v>
       </c>
       <c r="S33" s="2">
         <v>5708.9449999999997</v>
@@ -10633,7 +10529,7 @@
         <v>4977.7241999999997</v>
       </c>
       <c r="W33" s="2">
-        <v>88.875</v>
+        <v>88</v>
       </c>
       <c r="X33" s="2">
         <v>1427.15</v>
@@ -10644,8 +10540,8 @@
       <c r="Z33" s="2">
         <v>3699.0075000000002</v>
       </c>
-      <c r="AA33" s="2">
-        <v>263.27999999999997</v>
+      <c r="AA33" s="19">
+        <v>263</v>
       </c>
       <c r="AB33" s="2">
         <v>0</v>
@@ -11618,7 +11514,7 @@
   <sheetPr codeName="Sheet7">
     <tabColor theme="6" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="B1:P64"/>
+  <dimension ref="B1:Q106"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.5" customWidth="1"/>
@@ -11639,7 +11535,7 @@
     <col min="16" max="16" width="2.5" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:17" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1"/>
       <c r="C1"/>
       <c r="D1"/>
@@ -11654,25 +11550,25 @@
       <c r="M1"/>
       <c r="N1"/>
     </row>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B2"/>
-      <c r="C2" s="47" t="s">
+      <c r="C2" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
-      <c r="M2" s="47"/>
-      <c r="N2" s="47"/>
-      <c r="O2" s="45"/>
-    </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="42"/>
+    </row>
+    <row r="3" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B3" s="22" t="s">
         <v>36</v>
       </c>
@@ -11713,11 +11609,9 @@
         <v>138</v>
       </c>
       <c r="O3" s="7"/>
-      <c r="P3" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P3" s="1"/>
+    </row>
+    <row r="4" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>66</v>
       </c>
@@ -11728,10 +11622,10 @@
         <v>3226.0089686098654</v>
       </c>
       <c r="E4" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="F4" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="G4" s="25">
         <v>0.5</v>
@@ -11740,7 +11634,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1"/>
-      <c r="J4" s="25"/>
+      <c r="J4" s="12"/>
       <c r="K4" s="1" t="s">
         <v>146</v>
       </c>
@@ -11749,11 +11643,11 @@
       <c r="N4" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="P4" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O4" s="46"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="46"/>
+    </row>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>68</v>
       </c>
@@ -11764,10 +11658,10 @@
         <v>3693.8435940099826</v>
       </c>
       <c r="E5" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="F5" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="G5" s="25">
         <v>0.5</v>
@@ -11776,7 +11670,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1"/>
-      <c r="J5" s="25"/>
+      <c r="J5" s="12"/>
       <c r="K5" s="1" t="s">
         <v>146</v>
       </c>
@@ -11785,8 +11679,10 @@
       <c r="N5" s="2" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O5" s="46"/>
+      <c r="Q5" s="46"/>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>71</v>
       </c>
@@ -11797,10 +11693,10 @@
         <v>3005155.6027648887</v>
       </c>
       <c r="E6" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="F6" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="G6" s="25">
         <v>0.5</v>
@@ -11809,7 +11705,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1"/>
-      <c r="J6" s="25"/>
+      <c r="J6" s="12"/>
       <c r="K6" s="1" t="s">
         <v>146</v>
       </c>
@@ -11818,8 +11714,10 @@
       <c r="N6" s="2" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O6" s="46"/>
+      <c r="Q6" s="46"/>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>74</v>
       </c>
@@ -11830,10 +11728,10 @@
         <v>1123</v>
       </c>
       <c r="E7" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="F7" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="G7" s="25">
         <v>0.5</v>
@@ -11848,8 +11746,10 @@
       <c r="N7" s="2" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O7" s="46"/>
+      <c r="Q7" s="46"/>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>76</v>
       </c>
@@ -11860,10 +11760,10 @@
         <v>738</v>
       </c>
       <c r="E8" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="F8" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="G8" s="25">
         <v>0.5</v>
@@ -11878,8 +11778,10 @@
       <c r="N8" s="2" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O8" s="46"/>
+      <c r="Q8" s="46"/>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>77</v>
       </c>
@@ -11890,10 +11792,10 @@
         <v>2790</v>
       </c>
       <c r="E9" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="F9" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="G9" s="25">
         <v>0.5</v>
@@ -11908,8 +11810,10 @@
       <c r="N9" s="2" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O9" s="46"/>
+      <c r="Q9" s="46"/>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>80</v>
       </c>
@@ -11920,10 +11824,10 @@
         <v>1320</v>
       </c>
       <c r="E10" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="F10" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="G10" s="25">
         <v>0.5</v>
@@ -11938,8 +11842,10 @@
       <c r="N10" s="2" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O10" s="46"/>
+      <c r="Q10" s="46"/>
+    </row>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>83</v>
       </c>
@@ -11950,10 +11856,10 @@
         <v>3570</v>
       </c>
       <c r="E11" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="F11" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="G11" s="25">
         <v>0.5</v>
@@ -11968,8 +11874,10 @@
       <c r="N11" s="2" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O11" s="46"/>
+      <c r="Q11" s="46"/>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>87</v>
       </c>
@@ -11980,10 +11888,10 @@
         <v>24503.876684511721</v>
       </c>
       <c r="E12" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="F12" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="G12" s="25">
         <v>0.5</v>
@@ -11998,8 +11906,10 @@
       <c r="N12" s="2" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O12" s="46"/>
+      <c r="Q12" s="46"/>
+    </row>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>91</v>
       </c>
@@ -12010,10 +11920,10 @@
         <v>26755.65610859729</v>
       </c>
       <c r="E13" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="F13" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="G13" s="25">
         <v>0.5</v>
@@ -12028,8 +11938,10 @@
       <c r="N13" s="2" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O13" s="46"/>
+      <c r="Q13" s="46"/>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>92</v>
       </c>
@@ -12040,10 +11952,10 @@
         <v>1452</v>
       </c>
       <c r="E14" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="F14" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="G14" s="25">
         <v>0.5</v>
@@ -12058,8 +11970,10 @@
       <c r="N14" s="2" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O14" s="46"/>
+      <c r="Q14" s="46"/>
+    </row>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>94</v>
       </c>
@@ -12070,10 +11984,10 @@
         <v>669376.51821862359</v>
       </c>
       <c r="E15" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="F15" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="G15" s="25">
         <v>0.5</v>
@@ -12088,8 +12002,10 @@
       <c r="N15" s="2" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O15" s="46"/>
+      <c r="Q15" s="46"/>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>101</v>
       </c>
@@ -12100,10 +12016,10 @@
         <v>1047.2222222222222</v>
       </c>
       <c r="E16" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="F16" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="G16" s="25">
         <v>0.5</v>
@@ -12118,8 +12034,10 @@
       <c r="N16" s="2" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="46"/>
+      <c r="Q16" s="46"/>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>107</v>
       </c>
@@ -12130,10 +12048,10 @@
         <v>1653690.7936507936</v>
       </c>
       <c r="E17" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="F17" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="G17" s="25">
         <v>0.5</v>
@@ -12148,8 +12066,10 @@
       <c r="N17" s="2" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="46"/>
+      <c r="Q17" s="46"/>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>111</v>
       </c>
@@ -12160,10 +12080,10 @@
         <v>5811.2840466926045</v>
       </c>
       <c r="E18" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="F18" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="G18" s="25">
         <v>0.5</v>
@@ -12178,8 +12098,10 @@
       <c r="N18" s="2" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="46"/>
+      <c r="Q18" s="46"/>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>112</v>
       </c>
@@ -12190,10 +12112,10 @@
         <v>39200.000000000015</v>
       </c>
       <c r="E19" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="F19" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="G19" s="25">
         <v>0.5</v>
@@ -12208,8 +12130,10 @@
       <c r="N19" s="2" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="46"/>
+      <c r="Q19" s="46"/>
+    </row>
+    <row r="20" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>113</v>
       </c>
@@ -12220,10 +12144,10 @@
         <v>2752.3809523809527</v>
       </c>
       <c r="E20" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="F20" s="2">
-        <v>0.8660254037844386</v>
+        <v>0.85</v>
       </c>
       <c r="G20" s="25">
         <v>0.5</v>
@@ -12238,8 +12162,10 @@
       <c r="N20" s="2" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="46"/>
+      <c r="Q20" s="46"/>
+    </row>
+    <row r="21" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
         <v>65</v>
       </c>
@@ -12253,7 +12179,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G21" s="12"/>
       <c r="H21" s="1">
@@ -12267,7 +12193,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
         <v>66</v>
       </c>
@@ -12281,7 +12207,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G22" s="12"/>
       <c r="H22" s="1">
@@ -12295,7 +12221,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>68</v>
       </c>
@@ -12309,7 +12235,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G23" s="12"/>
       <c r="H23" s="1">
@@ -12323,7 +12249,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
         <v>71</v>
       </c>
@@ -12337,7 +12263,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G24" s="12"/>
       <c r="H24" s="1">
@@ -12351,7 +12277,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>72</v>
       </c>
@@ -12365,7 +12291,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="1">
@@ -12379,7 +12305,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>74</v>
       </c>
@@ -12393,7 +12319,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G26" s="12"/>
       <c r="H26" s="1">
@@ -12407,7 +12333,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>75</v>
       </c>
@@ -12421,7 +12347,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G27" s="12"/>
       <c r="H27" s="1">
@@ -12435,7 +12361,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>76</v>
       </c>
@@ -12449,7 +12375,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G28" s="12"/>
       <c r="H28" s="1">
@@ -12463,7 +12389,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
         <v>77</v>
       </c>
@@ -12477,7 +12403,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G29" s="12"/>
       <c r="H29" s="1">
@@ -12491,7 +12417,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>78</v>
       </c>
@@ -12505,7 +12431,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G30" s="12"/>
       <c r="H30" s="1">
@@ -12519,7 +12445,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
         <v>80</v>
       </c>
@@ -12533,7 +12459,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G31" s="12"/>
       <c r="H31" s="1">
@@ -12547,7 +12473,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
         <v>82</v>
       </c>
@@ -12561,7 +12487,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G32" s="12"/>
       <c r="H32" s="1">
@@ -12589,7 +12515,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G33" s="12"/>
       <c r="H33" s="1">
@@ -12617,7 +12543,7 @@
         <v>0</v>
       </c>
       <c r="F34" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G34" s="12"/>
       <c r="H34" s="1">
@@ -12645,7 +12571,7 @@
         <v>0</v>
       </c>
       <c r="F35" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G35" s="12"/>
       <c r="H35" s="1">
@@ -12673,7 +12599,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G36" s="12"/>
       <c r="H36" s="1">
@@ -12701,7 +12627,7 @@
         <v>0</v>
       </c>
       <c r="F37" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G37" s="12"/>
       <c r="H37" s="1">
@@ -12729,7 +12655,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G38" s="12"/>
       <c r="H38" s="1">
@@ -12757,7 +12683,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G39" s="12"/>
       <c r="H39" s="1">
@@ -12785,7 +12711,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G40" s="12"/>
       <c r="H40" s="1">
@@ -12813,7 +12739,7 @@
         <v>0</v>
       </c>
       <c r="F41" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G41" s="12"/>
       <c r="H41" s="1">
@@ -12841,7 +12767,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G42" s="12"/>
       <c r="H42" s="1">
@@ -12869,7 +12795,7 @@
         <v>0</v>
       </c>
       <c r="F43" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G43" s="12"/>
       <c r="H43" s="1">
@@ -12897,7 +12823,7 @@
         <v>0</v>
       </c>
       <c r="F44" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G44" s="12"/>
       <c r="H44" s="1">
@@ -12925,7 +12851,7 @@
         <v>0</v>
       </c>
       <c r="F45" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G45" s="12"/>
       <c r="H45" s="1">
@@ -12953,7 +12879,7 @@
         <v>0</v>
       </c>
       <c r="F46" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G46" s="12"/>
       <c r="H46" s="1">
@@ -12981,7 +12907,7 @@
         <v>0</v>
       </c>
       <c r="F47" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G47" s="12"/>
       <c r="H47" s="1">
@@ -13009,7 +12935,7 @@
         <v>0</v>
       </c>
       <c r="F48" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G48" s="12"/>
       <c r="H48" s="1">
@@ -13023,7 +12949,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="49" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B49" s="2" t="s">
         <v>107</v>
       </c>
@@ -13037,7 +12963,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G49" s="12"/>
       <c r="H49" s="1">
@@ -13051,7 +12977,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="50" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B50" s="2" t="s">
         <v>108</v>
       </c>
@@ -13065,7 +12991,7 @@
         <v>0</v>
       </c>
       <c r="F50" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G50" s="12"/>
       <c r="H50" s="1">
@@ -13079,7 +13005,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="51" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B51" s="2" t="s">
         <v>109</v>
       </c>
@@ -13093,7 +13019,7 @@
         <v>0</v>
       </c>
       <c r="F51" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G51" s="12"/>
       <c r="H51" s="1">
@@ -13107,7 +13033,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="52" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B52" s="2" t="s">
         <v>110</v>
       </c>
@@ -13121,7 +13047,7 @@
         <v>0</v>
       </c>
       <c r="F52" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G52" s="12"/>
       <c r="H52" s="1">
@@ -13135,7 +13061,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="53" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B53" s="2" t="s">
         <v>111</v>
       </c>
@@ -13149,7 +13075,7 @@
         <v>0</v>
       </c>
       <c r="F53" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G53" s="12"/>
       <c r="H53" s="1">
@@ -13163,7 +13089,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="54" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B54" s="2" t="s">
         <v>112</v>
       </c>
@@ -13177,7 +13103,7 @@
         <v>0</v>
       </c>
       <c r="F54" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G54" s="12"/>
       <c r="H54" s="1">
@@ -13191,7 +13117,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="55" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B55" s="2" t="s">
         <v>113</v>
       </c>
@@ -13205,7 +13131,7 @@
         <v>0</v>
       </c>
       <c r="F55" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G55" s="12"/>
       <c r="H55" s="1">
@@ -13219,2066 +13145,1000 @@
         <v>145</v>
       </c>
     </row>
-    <row r="56" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B56" s="42"/>
-      <c r="C56" s="42"/>
-      <c r="E56" s="42"/>
-      <c r="F56" s="42"/>
-      <c r="G56" s="43"/>
-      <c r="H56" s="44"/>
-      <c r="I56" s="42"/>
-      <c r="J56" s="43"/>
-      <c r="K56" s="44"/>
-      <c r="L56" s="42"/>
-      <c r="M56" s="42"/>
-      <c r="N56" s="42"/>
-    </row>
-    <row r="57" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B57" s="2"/>
-      <c r="E57" s="42"/>
-      <c r="F57" s="42"/>
-      <c r="G57" s="43"/>
-      <c r="H57" s="44"/>
-      <c r="I57" s="42"/>
-      <c r="J57" s="43"/>
-      <c r="K57" s="44"/>
-      <c r="L57" s="42"/>
-      <c r="M57" s="42"/>
-      <c r="N57" s="42"/>
-    </row>
-    <row r="58" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B58" s="2"/>
-      <c r="E58" s="42"/>
-      <c r="F58" s="42"/>
-      <c r="G58" s="43"/>
-      <c r="H58" s="44"/>
-      <c r="I58" s="42"/>
-      <c r="J58" s="43"/>
-      <c r="K58" s="44"/>
-      <c r="L58" s="42"/>
-      <c r="M58" s="42"/>
-      <c r="N58" s="42"/>
-    </row>
-    <row r="59" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B59" s="2"/>
-      <c r="E59" s="42"/>
-      <c r="F59" s="42"/>
-      <c r="G59" s="43"/>
-      <c r="H59" s="44"/>
-      <c r="I59" s="42"/>
-      <c r="J59" s="43"/>
-      <c r="K59" s="44"/>
-      <c r="L59" s="42"/>
-      <c r="M59" s="42"/>
-      <c r="N59" s="42"/>
-    </row>
-    <row r="60" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B60" s="2"/>
-      <c r="E60" s="42"/>
-      <c r="F60" s="42"/>
-      <c r="G60" s="43"/>
-      <c r="H60" s="44"/>
-      <c r="I60" s="42"/>
-      <c r="J60" s="43"/>
-      <c r="K60" s="44"/>
-      <c r="L60" s="42"/>
-      <c r="M60" s="42"/>
-      <c r="N60" s="42"/>
-    </row>
-    <row r="61" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B61" s="2"/>
-      <c r="D61" s="42"/>
-      <c r="E61" s="42"/>
-      <c r="F61" s="42"/>
-      <c r="G61" s="43"/>
-      <c r="H61" s="44"/>
-      <c r="I61" s="42"/>
-      <c r="J61" s="43"/>
-      <c r="K61" s="44"/>
-      <c r="L61" s="42"/>
-      <c r="M61" s="42"/>
-      <c r="N61" s="42"/>
-    </row>
-    <row r="62" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B62" s="2"/>
-      <c r="D62" s="42"/>
-      <c r="E62" s="42"/>
-      <c r="F62" s="42"/>
-      <c r="G62" s="43"/>
-      <c r="H62" s="44"/>
-      <c r="I62" s="42"/>
-      <c r="J62" s="43"/>
-      <c r="K62" s="44"/>
-      <c r="L62" s="42"/>
-      <c r="M62" s="42"/>
-      <c r="N62" s="42"/>
-    </row>
-    <row r="63" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B63" s="2"/>
-      <c r="E63" s="42"/>
-      <c r="F63" s="42"/>
-      <c r="G63" s="43"/>
-      <c r="H63" s="44"/>
-      <c r="I63" s="42"/>
-      <c r="J63" s="43"/>
-      <c r="K63" s="44"/>
-      <c r="L63" s="42"/>
-      <c r="M63" s="42"/>
-      <c r="N63" s="42"/>
-    </row>
-    <row r="64" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B64" s="2"/>
-      <c r="C64" s="42"/>
-      <c r="D64" s="42"/>
-      <c r="E64" s="42"/>
-      <c r="F64" s="42"/>
-      <c r="G64" s="43"/>
-      <c r="H64" s="44"/>
-      <c r="I64" s="42"/>
-      <c r="J64" s="43"/>
-      <c r="K64" s="44"/>
-      <c r="L64" s="42"/>
-      <c r="M64" s="42"/>
-      <c r="N64" s="42"/>
+    <row r="56" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B56" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="C56" s="52">
+        <v>1289.2729999999999</v>
+      </c>
+      <c r="D56" s="52">
+        <v>8573.6669999999995</v>
+      </c>
+      <c r="E56" s="52">
+        <v>0.95</v>
+      </c>
+      <c r="F56" s="52">
+        <v>0.95</v>
+      </c>
+      <c r="G56" s="54">
+        <v>0.5</v>
+      </c>
+      <c r="H56" s="53">
+        <v>0</v>
+      </c>
+      <c r="I56" s="52"/>
+      <c r="J56" s="55"/>
+      <c r="K56" s="53" t="s">
+        <v>146</v>
+      </c>
+      <c r="L56" s="52"/>
+      <c r="M56" s="52"/>
+      <c r="N56" s="52" t="s">
+        <v>149</v>
+      </c>
+      <c r="O56" s="56"/>
+    </row>
+    <row r="57" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B57" s="52" t="s">
+        <v>85</v>
+      </c>
+      <c r="C57" s="52">
+        <v>264.78899999999999</v>
+      </c>
+      <c r="D57" s="52">
+        <v>1455.076</v>
+      </c>
+      <c r="E57" s="52">
+        <v>0.95</v>
+      </c>
+      <c r="F57" s="52">
+        <v>0.95</v>
+      </c>
+      <c r="G57" s="54">
+        <v>0.5</v>
+      </c>
+      <c r="H57" s="53">
+        <v>0</v>
+      </c>
+      <c r="I57" s="52"/>
+      <c r="J57" s="55"/>
+      <c r="K57" s="53" t="s">
+        <v>146</v>
+      </c>
+      <c r="L57" s="52"/>
+      <c r="M57" s="52"/>
+      <c r="N57" s="52" t="s">
+        <v>149</v>
+      </c>
+      <c r="O57" s="56"/>
+    </row>
+    <row r="58" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B58" s="52" t="s">
+        <v>86</v>
+      </c>
+      <c r="C58" s="52">
+        <v>306.851</v>
+      </c>
+      <c r="D58" s="52">
+        <v>1749.0530000000001</v>
+      </c>
+      <c r="E58" s="52">
+        <v>0.95</v>
+      </c>
+      <c r="F58" s="52">
+        <v>0.95</v>
+      </c>
+      <c r="G58" s="54">
+        <v>0.5</v>
+      </c>
+      <c r="H58" s="53">
+        <v>0</v>
+      </c>
+      <c r="I58" s="52"/>
+      <c r="J58" s="55"/>
+      <c r="K58" s="53" t="s">
+        <v>146</v>
+      </c>
+      <c r="L58" s="52"/>
+      <c r="M58" s="52"/>
+      <c r="N58" s="52" t="s">
+        <v>149</v>
+      </c>
+      <c r="O58" s="56"/>
+    </row>
+    <row r="59" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B59" s="52" t="s">
+        <v>88</v>
+      </c>
+      <c r="C59" s="52">
+        <v>791.27499999999998</v>
+      </c>
+      <c r="D59" s="52">
+        <v>3758.5549999999998</v>
+      </c>
+      <c r="E59" s="52">
+        <v>0.95</v>
+      </c>
+      <c r="F59" s="52">
+        <v>0.95</v>
+      </c>
+      <c r="G59" s="54">
+        <v>0.5</v>
+      </c>
+      <c r="H59" s="53">
+        <v>0</v>
+      </c>
+      <c r="I59" s="52"/>
+      <c r="J59" s="55"/>
+      <c r="K59" s="53" t="s">
+        <v>146</v>
+      </c>
+      <c r="L59" s="52"/>
+      <c r="M59" s="52"/>
+      <c r="N59" s="52" t="s">
+        <v>149</v>
+      </c>
+      <c r="O59" s="56"/>
+    </row>
+    <row r="60" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B60" s="52" t="s">
+        <v>93</v>
+      </c>
+      <c r="C60" s="52">
+        <v>287.91699999999997</v>
+      </c>
+      <c r="D60" s="52">
+        <v>1641.1289999999999</v>
+      </c>
+      <c r="E60" s="52">
+        <v>0.95</v>
+      </c>
+      <c r="F60" s="52">
+        <v>0.95</v>
+      </c>
+      <c r="G60" s="54">
+        <v>0.5</v>
+      </c>
+      <c r="H60" s="53">
+        <v>0</v>
+      </c>
+      <c r="I60" s="52"/>
+      <c r="J60" s="55"/>
+      <c r="K60" s="53" t="s">
+        <v>146</v>
+      </c>
+      <c r="L60" s="52"/>
+      <c r="M60" s="52"/>
+      <c r="N60" s="52" t="s">
+        <v>149</v>
+      </c>
+      <c r="O60" s="56"/>
+    </row>
+    <row r="61" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B61" s="52" t="s">
+        <v>94</v>
+      </c>
+      <c r="C61" s="52">
+        <v>1264.807</v>
+      </c>
+      <c r="D61" s="52">
+        <v>7209.402</v>
+      </c>
+      <c r="E61" s="52">
+        <v>0.95</v>
+      </c>
+      <c r="F61" s="52">
+        <v>0.95</v>
+      </c>
+      <c r="G61" s="54">
+        <v>0.5</v>
+      </c>
+      <c r="H61" s="53">
+        <v>0</v>
+      </c>
+      <c r="I61" s="52"/>
+      <c r="J61" s="55"/>
+      <c r="K61" s="53" t="s">
+        <v>146</v>
+      </c>
+      <c r="L61" s="52"/>
+      <c r="M61" s="52"/>
+      <c r="N61" s="52" t="s">
+        <v>149</v>
+      </c>
+      <c r="O61" s="56"/>
+    </row>
+    <row r="62" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B62" s="52" t="s">
+        <v>97</v>
+      </c>
+      <c r="C62" s="52">
+        <v>520.65099999999995</v>
+      </c>
+      <c r="D62" s="52">
+        <v>2967.13</v>
+      </c>
+      <c r="E62" s="52">
+        <v>0.95</v>
+      </c>
+      <c r="F62" s="52">
+        <v>0.95</v>
+      </c>
+      <c r="G62" s="54">
+        <v>0.5</v>
+      </c>
+      <c r="H62" s="53">
+        <v>0</v>
+      </c>
+      <c r="I62" s="52"/>
+      <c r="J62" s="55"/>
+      <c r="K62" s="53" t="s">
+        <v>146</v>
+      </c>
+      <c r="L62" s="52"/>
+      <c r="M62" s="52"/>
+      <c r="N62" s="52" t="s">
+        <v>149</v>
+      </c>
+      <c r="O62" s="56"/>
+    </row>
+    <row r="63" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B63" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="C63" s="52">
+        <v>1316.9939999999999</v>
+      </c>
+      <c r="D63" s="52">
+        <v>7129.8549999999996</v>
+      </c>
+      <c r="E63" s="52">
+        <v>0.95</v>
+      </c>
+      <c r="F63" s="52">
+        <v>0.95</v>
+      </c>
+      <c r="G63" s="54">
+        <v>0.5</v>
+      </c>
+      <c r="H63" s="53">
+        <v>0</v>
+      </c>
+      <c r="I63" s="52"/>
+      <c r="J63" s="55"/>
+      <c r="K63" s="53" t="s">
+        <v>146</v>
+      </c>
+      <c r="L63" s="52"/>
+      <c r="M63" s="52"/>
+      <c r="N63" s="52" t="s">
+        <v>149</v>
+      </c>
+      <c r="O63" s="56"/>
+    </row>
+    <row r="64" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B64" s="52" t="s">
+        <v>102</v>
+      </c>
+      <c r="C64" s="52">
+        <v>2727.4580000000001</v>
+      </c>
+      <c r="D64" s="52">
+        <v>15795.677</v>
+      </c>
+      <c r="E64" s="52">
+        <v>0.95</v>
+      </c>
+      <c r="F64" s="52">
+        <v>0.95</v>
+      </c>
+      <c r="G64" s="54">
+        <v>0.5</v>
+      </c>
+      <c r="H64" s="53">
+        <v>0</v>
+      </c>
+      <c r="I64" s="52"/>
+      <c r="J64" s="55"/>
+      <c r="K64" s="53" t="s">
+        <v>146</v>
+      </c>
+      <c r="L64" s="52"/>
+      <c r="M64" s="52"/>
+      <c r="N64" s="52" t="s">
+        <v>149</v>
+      </c>
+      <c r="O64" s="56"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B65" s="57"/>
+      <c r="C65" s="52"/>
+      <c r="D65" s="52"/>
+      <c r="E65" s="52"/>
+      <c r="F65" s="52"/>
+      <c r="G65" s="54"/>
+      <c r="H65" s="53"/>
+      <c r="I65" s="52"/>
+      <c r="J65" s="55"/>
+      <c r="K65" s="53"/>
+      <c r="L65" s="52"/>
+      <c r="M65" s="52"/>
+      <c r="N65" s="52"/>
+      <c r="O65" s="56"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B66" s="57"/>
+      <c r="C66" s="52"/>
+      <c r="D66" s="52"/>
+      <c r="E66" s="52"/>
+      <c r="F66" s="52"/>
+      <c r="G66" s="54"/>
+      <c r="H66" s="53"/>
+      <c r="I66" s="52"/>
+      <c r="J66" s="55"/>
+      <c r="K66" s="53"/>
+      <c r="L66" s="52"/>
+      <c r="M66" s="52"/>
+      <c r="N66" s="52"/>
+      <c r="O66" s="56"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B67" s="57"/>
+      <c r="C67" s="52"/>
+      <c r="D67" s="52"/>
+      <c r="E67" s="52"/>
+      <c r="F67" s="52"/>
+      <c r="G67" s="54"/>
+      <c r="H67" s="53"/>
+      <c r="I67" s="52"/>
+      <c r="J67" s="55"/>
+      <c r="K67" s="53"/>
+      <c r="L67" s="52"/>
+      <c r="M67" s="52"/>
+      <c r="N67" s="52"/>
+      <c r="O67" s="56"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B68" s="57"/>
+      <c r="C68" s="52"/>
+      <c r="D68" s="52"/>
+      <c r="E68" s="52"/>
+      <c r="F68" s="52"/>
+      <c r="G68" s="54"/>
+      <c r="H68" s="53"/>
+      <c r="I68" s="52"/>
+      <c r="J68" s="55"/>
+      <c r="K68" s="53"/>
+      <c r="L68" s="52"/>
+      <c r="M68" s="52"/>
+      <c r="N68" s="52"/>
+      <c r="O68" s="56"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B69" s="57"/>
+      <c r="C69" s="52"/>
+      <c r="D69" s="52"/>
+      <c r="E69" s="52"/>
+      <c r="F69" s="52"/>
+      <c r="G69" s="54"/>
+      <c r="H69" s="53"/>
+      <c r="I69" s="52"/>
+      <c r="J69" s="55"/>
+      <c r="K69" s="53"/>
+      <c r="L69" s="52"/>
+      <c r="M69" s="52"/>
+      <c r="N69" s="52"/>
+      <c r="O69" s="56"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B70" s="57"/>
+      <c r="C70" s="52"/>
+      <c r="D70" s="52"/>
+      <c r="E70" s="52"/>
+      <c r="F70" s="52"/>
+      <c r="G70" s="54"/>
+      <c r="H70" s="53"/>
+      <c r="I70" s="52"/>
+      <c r="J70" s="55"/>
+      <c r="K70" s="53"/>
+      <c r="L70" s="52"/>
+      <c r="M70" s="52"/>
+      <c r="N70" s="52"/>
+      <c r="O70" s="56"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B71" s="57"/>
+      <c r="C71" s="52"/>
+      <c r="D71" s="52"/>
+      <c r="E71" s="52"/>
+      <c r="F71" s="52"/>
+      <c r="G71" s="54"/>
+      <c r="H71" s="53"/>
+      <c r="I71" s="52"/>
+      <c r="J71" s="55"/>
+      <c r="K71" s="53"/>
+      <c r="L71" s="52"/>
+      <c r="M71" s="52"/>
+      <c r="N71" s="52"/>
+      <c r="O71" s="56"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B72" s="57"/>
+      <c r="C72" s="52"/>
+      <c r="D72" s="52"/>
+      <c r="E72" s="52"/>
+      <c r="F72" s="52"/>
+      <c r="G72" s="54"/>
+      <c r="H72" s="53"/>
+      <c r="I72" s="52"/>
+      <c r="J72" s="55"/>
+      <c r="K72" s="53"/>
+      <c r="L72" s="52"/>
+      <c r="M72" s="52"/>
+      <c r="N72" s="52"/>
+      <c r="O72" s="56"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B73" s="57"/>
+      <c r="C73" s="52"/>
+      <c r="D73" s="52"/>
+      <c r="E73" s="52"/>
+      <c r="F73" s="52"/>
+      <c r="G73" s="54"/>
+      <c r="H73" s="53"/>
+      <c r="I73" s="52"/>
+      <c r="J73" s="55"/>
+      <c r="K73" s="53"/>
+      <c r="L73" s="52"/>
+      <c r="M73" s="52"/>
+      <c r="N73" s="52"/>
+      <c r="O73" s="56"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B74" s="57"/>
+      <c r="C74" s="52"/>
+      <c r="D74" s="52"/>
+      <c r="E74" s="52"/>
+      <c r="F74" s="52"/>
+      <c r="G74" s="54"/>
+      <c r="H74" s="53"/>
+      <c r="I74" s="52"/>
+      <c r="J74" s="55"/>
+      <c r="K74" s="53"/>
+      <c r="L74" s="52"/>
+      <c r="M74" s="52"/>
+      <c r="N74" s="52"/>
+      <c r="O74" s="56"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B75" s="57"/>
+      <c r="C75" s="52"/>
+      <c r="D75" s="52"/>
+      <c r="E75" s="52"/>
+      <c r="F75" s="52"/>
+      <c r="G75" s="54"/>
+      <c r="H75" s="53"/>
+      <c r="I75" s="52"/>
+      <c r="J75" s="55"/>
+      <c r="K75" s="53"/>
+      <c r="L75" s="52"/>
+      <c r="M75" s="52"/>
+      <c r="N75" s="52"/>
+      <c r="O75" s="56"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B76" s="57"/>
+      <c r="C76" s="52"/>
+      <c r="D76" s="52"/>
+      <c r="E76" s="52"/>
+      <c r="F76" s="52"/>
+      <c r="G76" s="54"/>
+      <c r="H76" s="53"/>
+      <c r="I76" s="52"/>
+      <c r="J76" s="55"/>
+      <c r="K76" s="53"/>
+      <c r="L76" s="52"/>
+      <c r="M76" s="52"/>
+      <c r="N76" s="52"/>
+      <c r="O76" s="56"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B77" s="57"/>
+      <c r="C77" s="52"/>
+      <c r="D77" s="52"/>
+      <c r="E77" s="52"/>
+      <c r="F77" s="52"/>
+      <c r="G77" s="54"/>
+      <c r="H77" s="53"/>
+      <c r="I77" s="52"/>
+      <c r="J77" s="55"/>
+      <c r="K77" s="53"/>
+      <c r="L77" s="52"/>
+      <c r="M77" s="52"/>
+      <c r="N77" s="52"/>
+      <c r="O77" s="56"/>
+    </row>
+    <row r="78" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B78" s="57"/>
+      <c r="C78" s="52"/>
+      <c r="D78" s="52"/>
+      <c r="E78" s="52"/>
+      <c r="F78" s="52"/>
+      <c r="G78" s="54"/>
+      <c r="H78" s="53"/>
+      <c r="I78" s="52"/>
+      <c r="J78" s="55"/>
+      <c r="K78" s="53"/>
+      <c r="L78" s="52"/>
+      <c r="M78" s="52"/>
+      <c r="N78" s="52"/>
+      <c r="O78" s="56"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B79" s="57"/>
+      <c r="C79" s="52"/>
+      <c r="D79" s="52"/>
+      <c r="E79" s="52"/>
+      <c r="F79" s="52"/>
+      <c r="G79" s="54"/>
+      <c r="H79" s="53"/>
+      <c r="I79" s="52"/>
+      <c r="J79" s="55"/>
+      <c r="K79" s="53"/>
+      <c r="L79" s="52"/>
+      <c r="M79" s="52"/>
+      <c r="N79" s="52"/>
+      <c r="O79" s="56"/>
+    </row>
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B80" s="57"/>
+      <c r="C80" s="52"/>
+      <c r="D80" s="52"/>
+      <c r="E80" s="52"/>
+      <c r="F80" s="52"/>
+      <c r="G80" s="54"/>
+      <c r="H80" s="53"/>
+      <c r="I80" s="52"/>
+      <c r="J80" s="55"/>
+      <c r="K80" s="53"/>
+      <c r="L80" s="52"/>
+      <c r="M80" s="52"/>
+      <c r="N80" s="52"/>
+      <c r="O80" s="56"/>
+    </row>
+    <row r="81" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B81" s="57"/>
+      <c r="C81" s="52"/>
+      <c r="D81" s="52"/>
+      <c r="E81" s="52"/>
+      <c r="F81" s="52"/>
+      <c r="G81" s="54"/>
+      <c r="H81" s="53"/>
+      <c r="I81" s="52"/>
+      <c r="J81" s="55"/>
+      <c r="K81" s="53"/>
+      <c r="L81" s="52"/>
+      <c r="M81" s="52"/>
+      <c r="N81" s="52"/>
+      <c r="O81" s="56"/>
+    </row>
+    <row r="82" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B82" s="57"/>
+      <c r="C82" s="52"/>
+      <c r="D82" s="52"/>
+      <c r="E82" s="52"/>
+      <c r="F82" s="52"/>
+      <c r="G82" s="54"/>
+      <c r="H82" s="53"/>
+      <c r="I82" s="52"/>
+      <c r="J82" s="55"/>
+      <c r="K82" s="53"/>
+      <c r="L82" s="52"/>
+      <c r="M82" s="52"/>
+      <c r="N82" s="52"/>
+      <c r="O82" s="56"/>
+    </row>
+    <row r="83" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B83" s="57"/>
+      <c r="C83" s="52"/>
+      <c r="D83" s="52"/>
+      <c r="E83" s="52"/>
+      <c r="F83" s="52"/>
+      <c r="G83" s="54"/>
+      <c r="H83" s="53"/>
+      <c r="I83" s="52"/>
+      <c r="J83" s="55"/>
+      <c r="K83" s="53"/>
+      <c r="L83" s="52"/>
+      <c r="M83" s="52"/>
+      <c r="N83" s="52"/>
+      <c r="O83" s="56"/>
+    </row>
+    <row r="84" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B84" s="57"/>
+      <c r="C84" s="52"/>
+      <c r="D84" s="52"/>
+      <c r="E84" s="52"/>
+      <c r="F84" s="52"/>
+      <c r="G84" s="54"/>
+      <c r="H84" s="53"/>
+      <c r="I84" s="52"/>
+      <c r="J84" s="55"/>
+      <c r="K84" s="53"/>
+      <c r="L84" s="52"/>
+      <c r="M84" s="52"/>
+      <c r="N84" s="52"/>
+      <c r="O84" s="56"/>
+    </row>
+    <row r="85" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B85" s="57"/>
+      <c r="C85" s="52"/>
+      <c r="D85" s="52"/>
+      <c r="E85" s="52"/>
+      <c r="F85" s="52"/>
+      <c r="G85" s="54"/>
+      <c r="H85" s="53"/>
+      <c r="I85" s="52"/>
+      <c r="J85" s="55"/>
+      <c r="K85" s="53"/>
+      <c r="L85" s="52"/>
+      <c r="M85" s="52"/>
+      <c r="N85" s="52"/>
+      <c r="O85" s="56"/>
+    </row>
+    <row r="86" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B86" s="57"/>
+      <c r="C86" s="52"/>
+      <c r="D86" s="52"/>
+      <c r="E86" s="52"/>
+      <c r="F86" s="52"/>
+      <c r="G86" s="54"/>
+      <c r="H86" s="53"/>
+      <c r="I86" s="52"/>
+      <c r="J86" s="55"/>
+      <c r="K86" s="53"/>
+      <c r="L86" s="52"/>
+      <c r="M86" s="52"/>
+      <c r="N86" s="52"/>
+      <c r="O86" s="56"/>
+    </row>
+    <row r="87" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B87" s="57"/>
+      <c r="C87" s="52"/>
+      <c r="D87" s="52"/>
+      <c r="E87" s="52"/>
+      <c r="F87" s="52"/>
+      <c r="G87" s="54"/>
+      <c r="H87" s="53"/>
+      <c r="I87" s="52"/>
+      <c r="J87" s="55"/>
+      <c r="K87" s="53"/>
+      <c r="L87" s="52"/>
+      <c r="M87" s="52"/>
+      <c r="N87" s="52"/>
+      <c r="O87" s="56"/>
+    </row>
+    <row r="88" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B88" s="57"/>
+      <c r="C88" s="52"/>
+      <c r="D88" s="52"/>
+      <c r="E88" s="52"/>
+      <c r="F88" s="52"/>
+      <c r="G88" s="54"/>
+      <c r="H88" s="53"/>
+      <c r="I88" s="52"/>
+      <c r="J88" s="55"/>
+      <c r="K88" s="53"/>
+      <c r="L88" s="52"/>
+      <c r="M88" s="52"/>
+      <c r="N88" s="52"/>
+      <c r="O88" s="56"/>
+    </row>
+    <row r="89" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B89" s="57"/>
+      <c r="C89" s="52"/>
+      <c r="D89" s="52"/>
+      <c r="E89" s="52"/>
+      <c r="F89" s="52"/>
+      <c r="G89" s="54"/>
+      <c r="H89" s="53"/>
+      <c r="I89" s="52"/>
+      <c r="J89" s="55"/>
+      <c r="K89" s="53"/>
+      <c r="L89" s="52"/>
+      <c r="M89" s="52"/>
+      <c r="N89" s="52"/>
+      <c r="O89" s="56"/>
+    </row>
+    <row r="90" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B90" s="57"/>
+      <c r="C90" s="52"/>
+      <c r="D90" s="52"/>
+      <c r="E90" s="52"/>
+      <c r="F90" s="52"/>
+      <c r="G90" s="54"/>
+      <c r="H90" s="53"/>
+      <c r="I90" s="52"/>
+      <c r="J90" s="55"/>
+      <c r="K90" s="53"/>
+      <c r="L90" s="52"/>
+      <c r="M90" s="52"/>
+      <c r="N90" s="52"/>
+      <c r="O90" s="56"/>
+    </row>
+    <row r="91" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B91" s="57"/>
+      <c r="C91" s="52"/>
+      <c r="D91" s="52"/>
+      <c r="E91" s="52"/>
+      <c r="F91" s="52"/>
+      <c r="G91" s="54"/>
+      <c r="H91" s="53"/>
+      <c r="I91" s="52"/>
+      <c r="J91" s="55"/>
+      <c r="K91" s="53"/>
+      <c r="L91" s="52"/>
+      <c r="M91" s="52"/>
+      <c r="N91" s="52"/>
+      <c r="O91" s="56"/>
+    </row>
+    <row r="92" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B92" s="57"/>
+      <c r="C92" s="52"/>
+      <c r="D92" s="52"/>
+      <c r="E92" s="52"/>
+      <c r="F92" s="52"/>
+      <c r="G92" s="54"/>
+      <c r="H92" s="53"/>
+      <c r="I92" s="52"/>
+      <c r="J92" s="55"/>
+      <c r="K92" s="53"/>
+      <c r="L92" s="52"/>
+      <c r="M92" s="52"/>
+      <c r="N92" s="52"/>
+      <c r="O92" s="56"/>
+    </row>
+    <row r="93" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B93" s="57"/>
+      <c r="C93" s="52"/>
+      <c r="D93" s="52"/>
+      <c r="E93" s="52"/>
+      <c r="F93" s="52"/>
+      <c r="G93" s="54"/>
+      <c r="H93" s="53"/>
+      <c r="I93" s="52"/>
+      <c r="J93" s="55"/>
+      <c r="K93" s="53"/>
+      <c r="L93" s="52"/>
+      <c r="M93" s="52"/>
+      <c r="N93" s="52"/>
+      <c r="O93" s="56"/>
+    </row>
+    <row r="94" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B94" s="57"/>
+      <c r="C94" s="52"/>
+      <c r="D94" s="52"/>
+      <c r="E94" s="52"/>
+      <c r="F94" s="52"/>
+      <c r="G94" s="54"/>
+      <c r="H94" s="53"/>
+      <c r="I94" s="52"/>
+      <c r="J94" s="55"/>
+      <c r="K94" s="53"/>
+      <c r="L94" s="52"/>
+      <c r="M94" s="52"/>
+      <c r="N94" s="52"/>
+      <c r="O94" s="56"/>
+    </row>
+    <row r="95" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B95" s="57"/>
+      <c r="C95" s="52"/>
+      <c r="D95" s="52"/>
+      <c r="E95" s="52"/>
+      <c r="F95" s="52"/>
+      <c r="G95" s="54"/>
+      <c r="H95" s="53"/>
+      <c r="I95" s="52"/>
+      <c r="J95" s="55"/>
+      <c r="K95" s="53"/>
+      <c r="L95" s="52"/>
+      <c r="M95" s="52"/>
+      <c r="N95" s="52"/>
+      <c r="O95" s="56"/>
+    </row>
+    <row r="96" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B96" s="57"/>
+      <c r="C96" s="52"/>
+      <c r="D96" s="52"/>
+      <c r="E96" s="52"/>
+      <c r="F96" s="52"/>
+      <c r="G96" s="54"/>
+      <c r="H96" s="53"/>
+      <c r="I96" s="52"/>
+      <c r="J96" s="55"/>
+      <c r="K96" s="53"/>
+      <c r="L96" s="52"/>
+      <c r="M96" s="52"/>
+      <c r="N96" s="52"/>
+      <c r="O96" s="56"/>
+    </row>
+    <row r="97" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B97" s="57"/>
+      <c r="C97" s="52"/>
+      <c r="D97" s="52"/>
+      <c r="E97" s="52"/>
+      <c r="F97" s="52"/>
+      <c r="G97" s="54"/>
+      <c r="H97" s="53"/>
+      <c r="I97" s="52"/>
+      <c r="J97" s="55"/>
+      <c r="K97" s="53"/>
+      <c r="L97" s="52"/>
+      <c r="M97" s="52"/>
+      <c r="N97" s="52"/>
+      <c r="O97" s="56"/>
+    </row>
+    <row r="98" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B98" s="57"/>
+      <c r="C98" s="52"/>
+      <c r="D98" s="52"/>
+      <c r="E98" s="52"/>
+      <c r="F98" s="52"/>
+      <c r="G98" s="54"/>
+      <c r="H98" s="53"/>
+      <c r="I98" s="52"/>
+      <c r="J98" s="55"/>
+      <c r="K98" s="53"/>
+      <c r="L98" s="52"/>
+      <c r="M98" s="52"/>
+      <c r="N98" s="52"/>
+      <c r="O98" s="56"/>
+    </row>
+    <row r="99" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B99" s="57"/>
+      <c r="C99" s="52"/>
+      <c r="D99" s="52"/>
+      <c r="E99" s="52"/>
+      <c r="F99" s="52"/>
+      <c r="G99" s="54"/>
+      <c r="H99" s="53"/>
+      <c r="I99" s="52"/>
+      <c r="J99" s="55"/>
+      <c r="K99" s="53"/>
+      <c r="L99" s="52"/>
+      <c r="M99" s="52"/>
+      <c r="N99" s="52"/>
+      <c r="O99" s="56"/>
+    </row>
+    <row r="100" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B100" s="57"/>
+      <c r="C100" s="52"/>
+      <c r="D100" s="52"/>
+      <c r="E100" s="52"/>
+      <c r="F100" s="52"/>
+      <c r="G100" s="54"/>
+      <c r="H100" s="53"/>
+      <c r="I100" s="52"/>
+      <c r="J100" s="55"/>
+      <c r="K100" s="53"/>
+      <c r="L100" s="52"/>
+      <c r="M100" s="52"/>
+      <c r="N100" s="52"/>
+      <c r="O100" s="56"/>
+    </row>
+    <row r="101" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B101" s="57"/>
+      <c r="C101" s="52"/>
+      <c r="D101" s="52"/>
+      <c r="E101" s="52"/>
+      <c r="F101" s="52"/>
+      <c r="G101" s="54"/>
+      <c r="H101" s="53"/>
+      <c r="I101" s="52"/>
+      <c r="J101" s="55"/>
+      <c r="K101" s="53"/>
+      <c r="L101" s="52"/>
+      <c r="M101" s="52"/>
+      <c r="N101" s="52"/>
+      <c r="O101" s="56"/>
+    </row>
+    <row r="102" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B102" s="57"/>
+      <c r="C102" s="52"/>
+      <c r="D102" s="52"/>
+      <c r="E102" s="52"/>
+      <c r="F102" s="52"/>
+      <c r="G102" s="54"/>
+      <c r="H102" s="53"/>
+      <c r="I102" s="52"/>
+      <c r="J102" s="55"/>
+      <c r="K102" s="53"/>
+      <c r="L102" s="52"/>
+      <c r="M102" s="52"/>
+      <c r="N102" s="52"/>
+      <c r="O102" s="56"/>
+    </row>
+    <row r="103" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B103" s="57"/>
+      <c r="C103" s="52"/>
+      <c r="D103" s="52"/>
+      <c r="E103" s="52"/>
+      <c r="F103" s="52"/>
+      <c r="G103" s="54"/>
+      <c r="H103" s="53"/>
+      <c r="I103" s="52"/>
+      <c r="J103" s="55"/>
+      <c r="K103" s="53"/>
+      <c r="L103" s="52"/>
+      <c r="M103" s="52"/>
+      <c r="N103" s="52"/>
+      <c r="O103" s="56"/>
+    </row>
+    <row r="104" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B104" s="57"/>
+      <c r="C104" s="52"/>
+      <c r="D104" s="52"/>
+      <c r="E104" s="52"/>
+      <c r="F104" s="52"/>
+      <c r="G104" s="54"/>
+      <c r="H104" s="53"/>
+      <c r="I104" s="52"/>
+      <c r="J104" s="55"/>
+      <c r="K104" s="53"/>
+      <c r="L104" s="52"/>
+      <c r="M104" s="52"/>
+      <c r="N104" s="52"/>
+      <c r="O104" s="56"/>
+    </row>
+    <row r="105" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B105" s="58"/>
+      <c r="C105" s="52"/>
+      <c r="D105" s="52"/>
+      <c r="E105" s="52"/>
+      <c r="F105" s="52"/>
+      <c r="G105" s="52"/>
+      <c r="H105" s="52"/>
+      <c r="I105" s="52"/>
+      <c r="J105" s="52"/>
+      <c r="K105" s="52"/>
+      <c r="L105" s="52"/>
+      <c r="M105" s="52"/>
+      <c r="N105" s="52"/>
+      <c r="O105" s="56"/>
+    </row>
+    <row r="106" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B106" s="58"/>
+      <c r="C106" s="52"/>
+      <c r="D106" s="52"/>
+      <c r="E106" s="52"/>
+      <c r="F106" s="52"/>
+      <c r="G106" s="52"/>
+      <c r="H106" s="52"/>
+      <c r="I106" s="52"/>
+      <c r="J106" s="52"/>
+      <c r="K106" s="52"/>
+      <c r="L106" s="52"/>
+      <c r="M106" s="52"/>
+      <c r="N106" s="52"/>
+      <c r="O106" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="C2:N2"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:H1110" xr:uid="{FFB9847E-AD12-0647-9B64-7D7CB1648887}">
-      <formula1>IF($B4&lt;&gt;"",$P$3:$P$4)</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K1048576" xr:uid="{2CC8A806-C616-DC45-A40B-9EC7FA2E4D5E}">
       <formula1>"Fixed, Optimize MWh, Optimize MW, Optimize both"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N4:N1048576" xr:uid="{55579949-45F9-134A-ACAC-707D11CD8872}">
       <formula1>"PHS, hydro, BatteryStore"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:H1110" xr:uid="{FFB9847E-AD12-0647-9B64-7D7CB1648887}">
+      <formula1>IF($B4&lt;&gt;"",$P$3:$P$4)</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7B60DB5-92C9-F245-B244-7CC76E316208}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="3" max="3" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="39.1640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87ED3F32-2AFE-4D4A-9596-D39A8243454D}">
-  <dimension ref="A1:W36"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="46" t="s">
-        <v>149</v>
-      </c>
-      <c r="B1" s="46" t="s">
-        <v>150</v>
-      </c>
-      <c r="C1" s="46" t="s">
-        <v>151</v>
-      </c>
-      <c r="D1" s="46" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C3" t="s">
-        <v>155</v>
-      </c>
-      <c r="D3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C4" t="s">
-        <v>161</v>
-      </c>
-      <c r="D4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>162</v>
-      </c>
-      <c r="B5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C5" t="s">
-        <v>155</v>
-      </c>
-      <c r="D5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>164</v>
-      </c>
-      <c r="B6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C6" t="s">
-        <v>155</v>
-      </c>
-      <c r="D6" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>166</v>
-      </c>
-      <c r="B7" t="s">
-        <v>158</v>
-      </c>
-      <c r="C7" t="s">
-        <v>155</v>
-      </c>
-      <c r="D7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>167</v>
-      </c>
-      <c r="B8" t="s">
-        <v>168</v>
-      </c>
-      <c r="C8" t="s">
-        <v>169</v>
-      </c>
-      <c r="D8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>170</v>
-      </c>
-      <c r="B9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C9" t="s">
-        <v>171</v>
-      </c>
-      <c r="D9" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>172</v>
-      </c>
-      <c r="B10" t="s">
-        <v>154</v>
-      </c>
-      <c r="C10" t="s">
-        <v>173</v>
-      </c>
-      <c r="D10" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>174</v>
-      </c>
-      <c r="B11" t="s">
-        <v>154</v>
-      </c>
-      <c r="C11" t="s">
-        <v>175</v>
-      </c>
-      <c r="D11" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>177</v>
-      </c>
-      <c r="B12" t="s">
-        <v>178</v>
-      </c>
-      <c r="C12" t="s">
-        <v>179</v>
-      </c>
-      <c r="D12" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>180</v>
-      </c>
-      <c r="B13" t="s">
-        <v>178</v>
-      </c>
-      <c r="C13" t="s">
-        <v>181</v>
-      </c>
-      <c r="D13" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>182</v>
-      </c>
-      <c r="B14" t="s">
-        <v>178</v>
-      </c>
-      <c r="C14" t="s">
-        <v>183</v>
-      </c>
-      <c r="D14" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B16" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="17" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B17" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="18" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="19" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B19" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="24" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="C24" s="48" t="s">
-        <v>123</v>
-      </c>
-      <c r="D24" s="48"/>
-      <c r="E24" s="48"/>
-      <c r="F24" s="48"/>
-      <c r="G24" s="48"/>
-      <c r="H24" s="48"/>
-      <c r="I24" s="48"/>
-      <c r="J24" s="48"/>
-      <c r="K24" s="48"/>
-      <c r="L24" s="48"/>
-      <c r="M24" s="48"/>
-      <c r="N24" s="48"/>
-      <c r="O24" s="48"/>
-      <c r="P24" s="48"/>
-      <c r="Q24" s="48"/>
-      <c r="R24" s="48"/>
-      <c r="S24" s="48"/>
-      <c r="T24" s="48"/>
-      <c r="U24" s="48"/>
-      <c r="V24" s="48"/>
-      <c r="W24" s="48"/>
-    </row>
-    <row r="25" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B25" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="D25" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="E25" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="F25" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="G25" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="H25" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="I25" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J25" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="K25" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="L25" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="M25" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="N25" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="O25" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="P25" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q25" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="R25" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="S25" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="T25" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="U25" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="V25" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="W25" s="19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="26" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B26" s="2">
-        <v>2015</v>
-      </c>
-      <c r="C26" s="2">
-        <v>48</v>
-      </c>
-      <c r="D26" s="2">
-        <v>66</v>
-      </c>
-      <c r="E26" s="2">
-        <v>91</v>
-      </c>
-      <c r="F26" s="2">
-        <v>156</v>
-      </c>
-      <c r="G26" s="2">
-        <v>50</v>
-      </c>
-      <c r="H26" s="19">
-        <v>16.083600000000001</v>
-      </c>
-      <c r="I26" s="19">
-        <v>0.76319999999999999</v>
-      </c>
-      <c r="J26" s="19">
-        <v>2.0488</v>
-      </c>
-      <c r="K26" s="19">
-        <v>25.8901</v>
-      </c>
-      <c r="L26" s="19">
-        <v>161.17490000000001</v>
-      </c>
-      <c r="M26" s="19">
-        <v>85.712400000000002</v>
-      </c>
-      <c r="N26" s="19">
-        <v>167.51240000000001</v>
-      </c>
-      <c r="O26" s="19">
-        <v>65.737099999999998</v>
-      </c>
-      <c r="P26" s="19">
-        <v>493.36219999999997</v>
-      </c>
-      <c r="Q26" s="19">
-        <v>923.55949999999996</v>
-      </c>
-      <c r="R26" s="19">
-        <v>560.58230000000003</v>
-      </c>
-      <c r="S26" s="19">
-        <v>263.7106</v>
-      </c>
-      <c r="T26" s="19">
-        <v>348.24430000000001</v>
-      </c>
-      <c r="U26" s="19">
-        <v>867.77689999999996</v>
-      </c>
-      <c r="V26" s="19">
-        <v>438.03469999999999</v>
-      </c>
-      <c r="W26" s="19">
-        <v>5.79E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B27" s="2">
-        <v>2016</v>
-      </c>
-      <c r="C27" s="20">
-        <v>70</v>
-      </c>
-      <c r="D27" s="20">
-        <v>87</v>
-      </c>
-      <c r="E27" s="20">
-        <v>100</v>
-      </c>
-      <c r="F27" s="20">
-        <v>177</v>
-      </c>
-      <c r="G27" s="20">
-        <v>57</v>
-      </c>
-      <c r="H27" s="2">
-        <v>16.083600000000001</v>
-      </c>
-      <c r="I27" s="2">
-        <v>0.7732</v>
-      </c>
-      <c r="J27" s="2">
-        <v>2.0488</v>
-      </c>
-      <c r="K27" s="2">
-        <v>26.026</v>
-      </c>
-      <c r="L27" s="2">
-        <v>161.18289999999999</v>
-      </c>
-      <c r="M27" s="2">
-        <v>85.712400000000002</v>
-      </c>
-      <c r="N27" s="2">
-        <v>167.51240000000001</v>
-      </c>
-      <c r="O27" s="2">
-        <v>65.737099999999998</v>
-      </c>
-      <c r="P27" s="2">
-        <v>493.36869999999999</v>
-      </c>
-      <c r="Q27" s="2">
-        <v>923.55949999999996</v>
-      </c>
-      <c r="R27" s="2">
-        <v>561.08230000000003</v>
-      </c>
-      <c r="S27" s="2">
-        <v>265.233</v>
-      </c>
-      <c r="T27" s="2">
-        <v>348.33929999999998</v>
-      </c>
-      <c r="U27" s="2">
-        <v>871.71040000000005</v>
-      </c>
-      <c r="V27" s="2">
-        <v>438.03469999999999</v>
-      </c>
-      <c r="W27" s="2">
-        <v>5.79E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B28" s="2">
-        <v>2017</v>
-      </c>
-      <c r="C28" s="20">
-        <v>88</v>
-      </c>
-      <c r="D28" s="20">
-        <v>102</v>
-      </c>
-      <c r="E28" s="20">
-        <v>106</v>
-      </c>
-      <c r="F28" s="20">
-        <v>197</v>
-      </c>
-      <c r="G28" s="20">
-        <v>61</v>
-      </c>
-      <c r="H28" s="2">
-        <v>16.2136</v>
-      </c>
-      <c r="I28" s="2">
-        <v>0.7732</v>
-      </c>
-      <c r="J28" s="2">
-        <v>2.0488</v>
-      </c>
-      <c r="K28" s="2">
-        <v>26.026</v>
-      </c>
-      <c r="L28" s="2">
-        <v>161.18889999999999</v>
-      </c>
-      <c r="M28" s="2">
-        <v>85.712400000000002</v>
-      </c>
-      <c r="N28" s="2">
-        <v>167.59440000000001</v>
-      </c>
-      <c r="O28" s="2">
-        <v>66.237099999999998</v>
-      </c>
-      <c r="P28" s="2">
-        <v>493.61829999999998</v>
-      </c>
-      <c r="Q28" s="2">
-        <v>924.60550000000001</v>
-      </c>
-      <c r="R28" s="2">
-        <v>561.23230000000001</v>
-      </c>
-      <c r="S28" s="2">
-        <v>265.6748</v>
-      </c>
-      <c r="T28" s="2">
-        <v>348.38830000000002</v>
-      </c>
-      <c r="U28" s="2">
-        <v>872.44929999999999</v>
-      </c>
-      <c r="V28" s="2">
-        <v>438.03469999999999</v>
-      </c>
-      <c r="W28" s="2">
-        <v>5.79E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B29" s="2">
-        <v>2018</v>
-      </c>
-      <c r="C29" s="20">
-        <v>104</v>
-      </c>
-      <c r="D29" s="20">
-        <v>116</v>
-      </c>
-      <c r="E29" s="20">
-        <v>112</v>
-      </c>
-      <c r="F29" s="20">
-        <v>248</v>
-      </c>
-      <c r="G29" s="20">
-        <v>66</v>
-      </c>
-      <c r="H29" s="2">
-        <v>16.2136</v>
-      </c>
-      <c r="I29" s="2">
-        <v>0.7732</v>
-      </c>
-      <c r="J29" s="2">
-        <v>2.0488</v>
-      </c>
-      <c r="K29" s="2">
-        <v>26.026</v>
-      </c>
-      <c r="L29" s="2">
-        <v>162.33269999999999</v>
-      </c>
-      <c r="M29" s="2">
-        <v>85.712400000000002</v>
-      </c>
-      <c r="N29" s="2">
-        <v>167.59440000000001</v>
-      </c>
-      <c r="O29" s="2">
-        <v>66.237099999999998</v>
-      </c>
-      <c r="P29" s="2">
-        <v>533.87070000000006</v>
-      </c>
-      <c r="Q29" s="2">
-        <v>924.60550000000001</v>
-      </c>
-      <c r="R29" s="2">
-        <v>561.24220000000003</v>
-      </c>
-      <c r="S29" s="2">
-        <v>268.02179999999998</v>
-      </c>
-      <c r="T29" s="2">
-        <v>360.38830000000002</v>
-      </c>
-      <c r="U29" s="2">
-        <v>875.58929999999998</v>
-      </c>
-      <c r="V29" s="2">
-        <v>441.37970000000001</v>
-      </c>
-      <c r="W29" s="2">
-        <v>5.79E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B30" s="2">
-        <v>2019</v>
-      </c>
-      <c r="C30" s="20">
-        <v>137</v>
-      </c>
-      <c r="D30" s="20">
-        <v>156</v>
-      </c>
-      <c r="E30" s="20">
-        <v>126</v>
-      </c>
-      <c r="F30" s="20">
-        <v>403</v>
-      </c>
-      <c r="G30" s="20">
-        <v>69</v>
-      </c>
-      <c r="H30" s="2">
-        <v>17.7136</v>
-      </c>
-      <c r="I30" s="2">
-        <v>0.7732</v>
-      </c>
-      <c r="J30" s="2">
-        <v>2.0488</v>
-      </c>
-      <c r="K30" s="2">
-        <v>26.105799999999999</v>
-      </c>
-      <c r="L30" s="2">
-        <v>162.33269999999999</v>
-      </c>
-      <c r="M30" s="2">
-        <v>98.909400000000005</v>
-      </c>
-      <c r="N30" s="2">
-        <v>753.23509999999999</v>
-      </c>
-      <c r="O30" s="2">
-        <v>66.237099999999998</v>
-      </c>
-      <c r="P30" s="2">
-        <v>712.34559999999999</v>
-      </c>
-      <c r="Q30" s="2">
-        <v>1729.8141000000001</v>
-      </c>
-      <c r="R30" s="2">
-        <v>1072.3669</v>
-      </c>
-      <c r="S30" s="2">
-        <v>269.98910000000001</v>
-      </c>
-      <c r="T30" s="2">
-        <v>360.38830000000002</v>
-      </c>
-      <c r="U30" s="2">
-        <v>1469.12</v>
-      </c>
-      <c r="V30" s="2">
-        <v>1103.5744999999999</v>
-      </c>
-      <c r="W30" s="2">
-        <v>5.79E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B31" s="2">
-        <v>2020</v>
-      </c>
-      <c r="C31" s="20">
-        <v>162</v>
-      </c>
-      <c r="D31" s="20">
-        <v>188</v>
-      </c>
-      <c r="E31" s="20">
-        <v>136</v>
-      </c>
-      <c r="F31" s="20">
-        <v>524</v>
-      </c>
-      <c r="G31" s="20">
-        <v>73</v>
-      </c>
-      <c r="H31" s="2">
-        <v>17.7136</v>
-      </c>
-      <c r="I31" s="2">
-        <v>0.7732</v>
-      </c>
-      <c r="J31" s="2">
-        <v>2.0488</v>
-      </c>
-      <c r="K31" s="2">
-        <v>50.105800000000002</v>
-      </c>
-      <c r="L31" s="2">
-        <v>162.93270000000001</v>
-      </c>
-      <c r="M31" s="2">
-        <v>98.909400000000005</v>
-      </c>
-      <c r="N31" s="2">
-        <v>1099.1387999999999</v>
-      </c>
-      <c r="O31" s="2">
-        <v>66.737099999999998</v>
-      </c>
-      <c r="P31" s="2">
-        <v>840.77179999999998</v>
-      </c>
-      <c r="Q31" s="2">
-        <v>1925.1898000000001</v>
-      </c>
-      <c r="R31" s="2">
-        <v>2328.7757999999999</v>
-      </c>
-      <c r="S31" s="2">
-        <v>276.38810000000001</v>
-      </c>
-      <c r="T31" s="2">
-        <v>364.29910000000001</v>
-      </c>
-      <c r="U31" s="2">
-        <v>2089.4504999999999</v>
-      </c>
-      <c r="V31" s="2">
-        <v>1218.7228</v>
-      </c>
-      <c r="W31" s="2">
-        <v>5.79E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B32" s="2">
-        <v>2021</v>
-      </c>
-      <c r="C32" s="20">
-        <v>297</v>
-      </c>
-      <c r="D32" s="20">
-        <v>284</v>
-      </c>
-      <c r="E32" s="20">
-        <v>172</v>
-      </c>
-      <c r="F32" s="20">
-        <v>721</v>
-      </c>
-      <c r="G32" s="20">
-        <v>327</v>
-      </c>
-      <c r="H32" s="2">
-        <v>17.683499999999999</v>
-      </c>
-      <c r="I32" s="2">
-        <v>0.73709999999999998</v>
-      </c>
-      <c r="J32" s="2">
-        <v>3.5488</v>
-      </c>
-      <c r="K32" s="2">
-        <v>50.525500000000001</v>
-      </c>
-      <c r="L32" s="2">
-        <v>163.55269999999999</v>
-      </c>
-      <c r="M32" s="2">
-        <v>99.759100000000004</v>
-      </c>
-      <c r="N32" s="2">
-        <v>1503.5422000000001</v>
-      </c>
-      <c r="O32" s="2">
-        <v>66.436300000000003</v>
-      </c>
-      <c r="P32" s="2">
-        <v>1030.7711999999999</v>
-      </c>
-      <c r="Q32" s="2">
-        <v>2824.7231999999999</v>
-      </c>
-      <c r="R32" s="2">
-        <v>3365.6097</v>
-      </c>
-      <c r="S32" s="2">
-        <v>279.33749999999998</v>
-      </c>
-      <c r="T32" s="2">
-        <v>404.96940000000001</v>
-      </c>
-      <c r="U32" s="2">
-        <v>2968.2550999999999</v>
-      </c>
-      <c r="V32" s="2">
-        <v>1302.9530999999999</v>
-      </c>
-      <c r="W32" s="2">
-        <v>5.79E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B33" s="2">
-        <v>2022</v>
-      </c>
-      <c r="C33" s="20">
-        <v>482</v>
-      </c>
-      <c r="D33" s="20">
-        <v>461</v>
-      </c>
-      <c r="E33" s="20">
-        <v>315</v>
-      </c>
-      <c r="F33" s="20">
-        <v>877</v>
-      </c>
-      <c r="G33" s="20">
-        <v>524</v>
-      </c>
-      <c r="H33" s="2">
-        <v>17.782699999999998</v>
-      </c>
-      <c r="I33" s="2">
-        <v>0.79710000000000003</v>
-      </c>
-      <c r="J33" s="2">
-        <v>3.6738</v>
-      </c>
-      <c r="K33" s="2">
-        <v>50.685499999999998</v>
-      </c>
-      <c r="L33" s="2">
-        <v>163.55269999999999</v>
-      </c>
-      <c r="M33" s="2">
-        <v>99.859099999999998</v>
-      </c>
-      <c r="N33" s="2">
-        <v>1810.9880000000001</v>
-      </c>
-      <c r="O33" s="2">
-        <v>66.436300000000003</v>
-      </c>
-      <c r="P33" s="2">
-        <v>1396.5757000000001</v>
-      </c>
-      <c r="Q33" s="2">
-        <v>3893.9758000000002</v>
-      </c>
-      <c r="R33" s="2">
-        <v>5319.424</v>
-      </c>
-      <c r="S33" s="2">
-        <v>284.7353</v>
-      </c>
-      <c r="T33" s="2">
-        <v>410.04539999999997</v>
-      </c>
-      <c r="U33" s="2">
-        <v>3917.9250999999999</v>
-      </c>
-      <c r="V33" s="2">
-        <v>1404.2308</v>
-      </c>
-      <c r="W33" s="2">
-        <v>5.79E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B34" s="2">
-        <v>2023</v>
-      </c>
-      <c r="C34" s="20">
-        <v>752</v>
-      </c>
-      <c r="D34" s="20">
-        <v>1025</v>
-      </c>
-      <c r="E34" s="20">
-        <v>474</v>
-      </c>
-      <c r="F34" s="20">
-        <v>1066</v>
-      </c>
-      <c r="G34" s="20">
-        <v>553</v>
-      </c>
-      <c r="H34" s="2">
-        <v>19.332699999999999</v>
-      </c>
-      <c r="I34" s="2">
-        <v>0.87619999999999998</v>
-      </c>
-      <c r="J34" s="2">
-        <v>3.9238</v>
-      </c>
-      <c r="K34" s="2">
-        <v>57.3155</v>
-      </c>
-      <c r="L34" s="2">
-        <v>172.2927</v>
-      </c>
-      <c r="M34" s="2">
-        <v>103.6181</v>
-      </c>
-      <c r="N34" s="2">
-        <v>2259.2469000000001</v>
-      </c>
-      <c r="O34" s="2">
-        <v>152.04130000000001</v>
-      </c>
-      <c r="P34" s="2">
-        <v>1909.9184</v>
-      </c>
-      <c r="Q34" s="2">
-        <v>5764.7286999999997</v>
-      </c>
-      <c r="R34" s="2">
-        <v>6014.6284999999998</v>
-      </c>
-      <c r="S34" s="2">
-        <v>293.39640000000003</v>
-      </c>
-      <c r="T34" s="2">
-        <v>443.1404</v>
-      </c>
-      <c r="U34" s="2">
-        <v>4957.8874999999998</v>
-      </c>
-      <c r="V34" s="2">
-        <v>1553.2028</v>
-      </c>
-      <c r="W34" s="2">
-        <v>5.79E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B35" s="2">
-        <v>2024</v>
-      </c>
-      <c r="C35" s="20">
-        <v>946</v>
-      </c>
-      <c r="D35" s="20">
-        <v>1601</v>
-      </c>
-      <c r="E35" s="20">
-        <v>595</v>
-      </c>
-      <c r="F35" s="20">
-        <v>1878</v>
-      </c>
-      <c r="G35" s="20">
-        <v>621</v>
-      </c>
-      <c r="H35" s="2">
-        <v>19.4649</v>
-      </c>
-      <c r="I35" s="2">
-        <v>0.93620000000000003</v>
-      </c>
-      <c r="J35" s="2">
-        <v>7.5818000000000003</v>
-      </c>
-      <c r="K35" s="2">
-        <v>59.515500000000003</v>
-      </c>
-      <c r="L35" s="2">
-        <v>234.41380000000001</v>
-      </c>
-      <c r="M35" s="2">
-        <v>105.11409999999999</v>
-      </c>
-      <c r="N35" s="2">
-        <v>2781.4018999999998</v>
-      </c>
-      <c r="O35" s="2">
-        <v>152.05860000000001</v>
-      </c>
-      <c r="P35" s="2">
-        <v>2402.6529</v>
-      </c>
-      <c r="Q35" s="2">
-        <v>6752.4339</v>
-      </c>
-      <c r="R35" s="2">
-        <v>6715.3987999999999</v>
-      </c>
-      <c r="S35" s="2">
-        <v>308.52460000000002</v>
-      </c>
-      <c r="T35" s="2">
-        <v>477.52710000000002</v>
-      </c>
-      <c r="U35" s="2">
-        <v>6559.0370000000003</v>
-      </c>
-      <c r="V35" s="2">
-        <v>1690.5808</v>
-      </c>
-      <c r="W35" s="2">
-        <v>5.79E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B36" s="2">
-        <v>2025</v>
-      </c>
-      <c r="C36" s="20">
-        <v>1326</v>
-      </c>
-      <c r="D36" s="20">
-        <v>1927</v>
-      </c>
-      <c r="E36" s="20">
-        <v>677</v>
-      </c>
-      <c r="F36" s="20">
-        <v>2192</v>
-      </c>
-      <c r="G36" s="20">
-        <v>691</v>
-      </c>
-      <c r="H36" s="2">
-        <v>19.4649</v>
-      </c>
-      <c r="I36" s="2">
-        <v>0.93620000000000003</v>
-      </c>
-      <c r="J36" s="2">
-        <v>7.5818000000000003</v>
-      </c>
-      <c r="K36" s="2">
-        <v>62.514499999999998</v>
-      </c>
-      <c r="L36" s="2">
-        <v>279.63279999999997</v>
-      </c>
-      <c r="M36" s="2">
-        <v>105.11409999999999</v>
-      </c>
-      <c r="N36" s="2">
-        <v>3122.9047999999998</v>
-      </c>
-      <c r="O36" s="2">
-        <v>152.05860000000001</v>
-      </c>
-      <c r="P36" s="2">
-        <v>3964.9854</v>
-      </c>
-      <c r="Q36" s="2">
-        <v>7744.6749</v>
-      </c>
-      <c r="R36" s="2">
-        <v>7094.5673999999999</v>
-      </c>
-      <c r="S36" s="2">
-        <v>414.77620000000002</v>
-      </c>
-      <c r="T36" s="2">
-        <v>572.47410000000002</v>
-      </c>
-      <c r="U36" s="2">
-        <v>8186.1710000000003</v>
-      </c>
-      <c r="V36" s="2">
-        <v>1796.0708</v>
-      </c>
-      <c r="W36" s="2">
-        <v>5.79E-2</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="C24:W24"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57FD5248-C7A5-664D-AD0D-5AECEF6931A7}">
-  <dimension ref="C5:W17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="10.1640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="5" spans="3:23" x14ac:dyDescent="0.2">
-      <c r="D5" s="48" t="s">
-        <v>123</v>
-      </c>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
-      <c r="K5" s="48"/>
-      <c r="L5" s="48"/>
-      <c r="M5" s="48"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
-      <c r="W5" s="48"/>
-    </row>
-    <row r="6" spans="3:23" x14ac:dyDescent="0.2">
-      <c r="C6" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="H6" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="I6" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="J6" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="K6" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="L6" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="M6" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="N6" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="O6" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="P6" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q6" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="R6" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="S6" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="T6" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="U6" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="V6" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="W6" s="19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="3:23" x14ac:dyDescent="0.2">
-      <c r="C7" s="2">
-        <v>2015</v>
-      </c>
-      <c r="D7" s="2">
-        <v>48</v>
-      </c>
-      <c r="E7" s="2">
-        <v>66</v>
-      </c>
-      <c r="F7" s="2">
-        <v>91</v>
-      </c>
-      <c r="G7" s="2">
-        <v>156</v>
-      </c>
-      <c r="H7" s="2">
-        <v>50</v>
-      </c>
-      <c r="I7" s="19">
-        <v>16.083600000000001</v>
-      </c>
-      <c r="J7" s="19">
-        <v>0.76319999999999999</v>
-      </c>
-      <c r="K7" s="19">
-        <v>2.0488</v>
-      </c>
-      <c r="L7" s="19">
-        <v>25.8901</v>
-      </c>
-      <c r="M7" s="19">
-        <v>161.17490000000001</v>
-      </c>
-      <c r="N7" s="19">
-        <v>85.712400000000002</v>
-      </c>
-      <c r="O7" s="19">
-        <v>167.51240000000001</v>
-      </c>
-      <c r="P7" s="19">
-        <v>65.737099999999998</v>
-      </c>
-      <c r="Q7" s="19">
-        <v>493.36219999999997</v>
-      </c>
-      <c r="R7" s="19">
-        <v>923.55949999999996</v>
-      </c>
-      <c r="S7" s="19">
-        <v>560.58230000000003</v>
-      </c>
-      <c r="T7" s="19">
-        <v>263.7106</v>
-      </c>
-      <c r="U7" s="19">
-        <v>348.24430000000001</v>
-      </c>
-      <c r="V7" s="19">
-        <v>867.77689999999996</v>
-      </c>
-      <c r="W7" s="19">
-        <v>438.03469999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="3:23" x14ac:dyDescent="0.2">
-      <c r="C8" s="2">
-        <v>2016</v>
-      </c>
-      <c r="D8" s="20">
-        <v>70</v>
-      </c>
-      <c r="E8" s="20">
-        <v>87</v>
-      </c>
-      <c r="F8" s="20">
-        <v>100</v>
-      </c>
-      <c r="G8" s="20">
-        <v>177</v>
-      </c>
-      <c r="H8" s="20">
-        <v>57</v>
-      </c>
-      <c r="I8" s="2">
-        <v>16.083600000000001</v>
-      </c>
-      <c r="J8" s="2">
-        <v>0.7732</v>
-      </c>
-      <c r="K8" s="2">
-        <v>2.0488</v>
-      </c>
-      <c r="L8" s="2">
-        <v>26.026</v>
-      </c>
-      <c r="M8" s="2">
-        <v>161.18289999999999</v>
-      </c>
-      <c r="N8" s="2">
-        <v>85.712400000000002</v>
-      </c>
-      <c r="O8" s="2">
-        <v>167.51240000000001</v>
-      </c>
-      <c r="P8" s="2">
-        <v>65.737099999999998</v>
-      </c>
-      <c r="Q8" s="2">
-        <v>493.36869999999999</v>
-      </c>
-      <c r="R8" s="2">
-        <v>923.55949999999996</v>
-      </c>
-      <c r="S8" s="2">
-        <v>561.08230000000003</v>
-      </c>
-      <c r="T8" s="2">
-        <v>265.233</v>
-      </c>
-      <c r="U8" s="2">
-        <v>348.33929999999998</v>
-      </c>
-      <c r="V8" s="2">
-        <v>871.71040000000005</v>
-      </c>
-      <c r="W8" s="2">
-        <v>438.03469999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="3:23" x14ac:dyDescent="0.2">
-      <c r="C9" s="2">
-        <v>2017</v>
-      </c>
-      <c r="D9" s="20">
-        <v>88</v>
-      </c>
-      <c r="E9" s="20">
-        <v>102</v>
-      </c>
-      <c r="F9" s="20">
-        <v>106</v>
-      </c>
-      <c r="G9" s="20">
-        <v>197</v>
-      </c>
-      <c r="H9" s="20">
-        <v>61</v>
-      </c>
-      <c r="I9" s="2">
-        <v>16.2136</v>
-      </c>
-      <c r="J9" s="2">
-        <v>0.7732</v>
-      </c>
-      <c r="K9" s="2">
-        <v>2.0488</v>
-      </c>
-      <c r="L9" s="2">
-        <v>26.026</v>
-      </c>
-      <c r="M9" s="2">
-        <v>161.18889999999999</v>
-      </c>
-      <c r="N9" s="2">
-        <v>85.712400000000002</v>
-      </c>
-      <c r="O9" s="2">
-        <v>167.59440000000001</v>
-      </c>
-      <c r="P9" s="2">
-        <v>66.237099999999998</v>
-      </c>
-      <c r="Q9" s="2">
-        <v>493.61829999999998</v>
-      </c>
-      <c r="R9" s="2">
-        <v>924.60550000000001</v>
-      </c>
-      <c r="S9" s="2">
-        <v>561.23230000000001</v>
-      </c>
-      <c r="T9" s="2">
-        <v>265.6748</v>
-      </c>
-      <c r="U9" s="2">
-        <v>348.38830000000002</v>
-      </c>
-      <c r="V9" s="2">
-        <v>872.44929999999999</v>
-      </c>
-      <c r="W9" s="2">
-        <v>438.03469999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="3:23" x14ac:dyDescent="0.2">
-      <c r="C10" s="2">
-        <v>2018</v>
-      </c>
-      <c r="D10" s="20">
-        <v>104</v>
-      </c>
-      <c r="E10" s="20">
-        <v>116</v>
-      </c>
-      <c r="F10" s="20">
-        <v>112</v>
-      </c>
-      <c r="G10" s="20">
-        <v>248</v>
-      </c>
-      <c r="H10" s="20">
-        <v>66</v>
-      </c>
-      <c r="I10" s="2">
-        <v>16.2136</v>
-      </c>
-      <c r="J10" s="2">
-        <v>0.7732</v>
-      </c>
-      <c r="K10" s="2">
-        <v>2.0488</v>
-      </c>
-      <c r="L10" s="2">
-        <v>26.026</v>
-      </c>
-      <c r="M10" s="2">
-        <v>162.33269999999999</v>
-      </c>
-      <c r="N10" s="2">
-        <v>85.712400000000002</v>
-      </c>
-      <c r="O10" s="2">
-        <v>167.59440000000001</v>
-      </c>
-      <c r="P10" s="2">
-        <v>66.237099999999998</v>
-      </c>
-      <c r="Q10" s="2">
-        <v>533.87070000000006</v>
-      </c>
-      <c r="R10" s="2">
-        <v>924.60550000000001</v>
-      </c>
-      <c r="S10" s="2">
-        <v>561.24220000000003</v>
-      </c>
-      <c r="T10" s="2">
-        <v>268.02179999999998</v>
-      </c>
-      <c r="U10" s="2">
-        <v>360.38830000000002</v>
-      </c>
-      <c r="V10" s="2">
-        <v>875.58929999999998</v>
-      </c>
-      <c r="W10" s="2">
-        <v>441.37970000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="3:23" x14ac:dyDescent="0.2">
-      <c r="C11" s="2">
-        <v>2019</v>
-      </c>
-      <c r="D11" s="20">
-        <v>137</v>
-      </c>
-      <c r="E11" s="20">
-        <v>156</v>
-      </c>
-      <c r="F11" s="20">
-        <v>126</v>
-      </c>
-      <c r="G11" s="20">
-        <v>403</v>
-      </c>
-      <c r="H11" s="20">
-        <v>69</v>
-      </c>
-      <c r="I11" s="2">
-        <v>17.7136</v>
-      </c>
-      <c r="J11" s="2">
-        <v>0.7732</v>
-      </c>
-      <c r="K11" s="2">
-        <v>2.0488</v>
-      </c>
-      <c r="L11" s="2">
-        <v>26.105799999999999</v>
-      </c>
-      <c r="M11" s="2">
-        <v>162.33269999999999</v>
-      </c>
-      <c r="N11" s="2">
-        <v>98.909400000000005</v>
-      </c>
-      <c r="O11" s="2">
-        <v>753.23509999999999</v>
-      </c>
-      <c r="P11" s="2">
-        <v>66.237099999999998</v>
-      </c>
-      <c r="Q11" s="2">
-        <v>712.34559999999999</v>
-      </c>
-      <c r="R11" s="2">
-        <v>1729.8141000000001</v>
-      </c>
-      <c r="S11" s="2">
-        <v>1072.3669</v>
-      </c>
-      <c r="T11" s="2">
-        <v>269.98910000000001</v>
-      </c>
-      <c r="U11" s="2">
-        <v>360.38830000000002</v>
-      </c>
-      <c r="V11" s="2">
-        <v>1469.12</v>
-      </c>
-      <c r="W11" s="2">
-        <v>1103.5744999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="3:23" x14ac:dyDescent="0.2">
-      <c r="C12" s="2">
-        <v>2020</v>
-      </c>
-      <c r="D12" s="20">
-        <v>162</v>
-      </c>
-      <c r="E12" s="20">
-        <v>188</v>
-      </c>
-      <c r="F12" s="20">
-        <v>136</v>
-      </c>
-      <c r="G12" s="20">
-        <v>524</v>
-      </c>
-      <c r="H12" s="20">
-        <v>73</v>
-      </c>
-      <c r="I12" s="2">
-        <v>17.7136</v>
-      </c>
-      <c r="J12" s="2">
-        <v>0.7732</v>
-      </c>
-      <c r="K12" s="2">
-        <v>2.0488</v>
-      </c>
-      <c r="L12" s="2">
-        <v>50.105800000000002</v>
-      </c>
-      <c r="M12" s="2">
-        <v>162.93270000000001</v>
-      </c>
-      <c r="N12" s="2">
-        <v>98.909400000000005</v>
-      </c>
-      <c r="O12" s="2">
-        <v>1099.1387999999999</v>
-      </c>
-      <c r="P12" s="2">
-        <v>66.737099999999998</v>
-      </c>
-      <c r="Q12" s="2">
-        <v>840.77179999999998</v>
-      </c>
-      <c r="R12" s="2">
-        <v>1925.1898000000001</v>
-      </c>
-      <c r="S12" s="2">
-        <v>2328.7757999999999</v>
-      </c>
-      <c r="T12" s="2">
-        <v>276.38810000000001</v>
-      </c>
-      <c r="U12" s="2">
-        <v>364.29910000000001</v>
-      </c>
-      <c r="V12" s="2">
-        <v>2089.4504999999999</v>
-      </c>
-      <c r="W12" s="2">
-        <v>1218.7228</v>
-      </c>
-    </row>
-    <row r="13" spans="3:23" x14ac:dyDescent="0.2">
-      <c r="C13" s="2">
-        <v>2021</v>
-      </c>
-      <c r="D13" s="20">
-        <v>297</v>
-      </c>
-      <c r="E13" s="20">
-        <v>284</v>
-      </c>
-      <c r="F13" s="20">
-        <v>172</v>
-      </c>
-      <c r="G13" s="20">
-        <v>721</v>
-      </c>
-      <c r="H13" s="20">
-        <v>327</v>
-      </c>
-      <c r="I13" s="2">
-        <v>17.683499999999999</v>
-      </c>
-      <c r="J13" s="2">
-        <v>0.73709999999999998</v>
-      </c>
-      <c r="K13" s="2">
-        <v>3.5488</v>
-      </c>
-      <c r="L13" s="2">
-        <v>50.525500000000001</v>
-      </c>
-      <c r="M13" s="2">
-        <v>163.55269999999999</v>
-      </c>
-      <c r="N13" s="2">
-        <v>99.759100000000004</v>
-      </c>
-      <c r="O13" s="2">
-        <v>1503.5422000000001</v>
-      </c>
-      <c r="P13" s="2">
-        <v>66.436300000000003</v>
-      </c>
-      <c r="Q13" s="2">
-        <v>1030.7711999999999</v>
-      </c>
-      <c r="R13" s="2">
-        <v>2824.7231999999999</v>
-      </c>
-      <c r="S13" s="2">
-        <v>3365.6097</v>
-      </c>
-      <c r="T13" s="2">
-        <v>279.33749999999998</v>
-      </c>
-      <c r="U13" s="2">
-        <v>404.96940000000001</v>
-      </c>
-      <c r="V13" s="2">
-        <v>2968.2550999999999</v>
-      </c>
-      <c r="W13" s="2">
-        <v>1302.9530999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="3:23" x14ac:dyDescent="0.2">
-      <c r="C14" s="2">
-        <v>2022</v>
-      </c>
-      <c r="D14" s="20">
-        <v>482</v>
-      </c>
-      <c r="E14" s="20">
-        <v>461</v>
-      </c>
-      <c r="F14" s="20">
-        <v>315</v>
-      </c>
-      <c r="G14" s="20">
-        <v>877</v>
-      </c>
-      <c r="H14" s="20">
-        <v>524</v>
-      </c>
-      <c r="I14" s="2">
-        <v>17.782699999999998</v>
-      </c>
-      <c r="J14" s="2">
-        <v>0.79710000000000003</v>
-      </c>
-      <c r="K14" s="2">
-        <v>3.6738</v>
-      </c>
-      <c r="L14" s="2">
-        <v>50.685499999999998</v>
-      </c>
-      <c r="M14" s="2">
-        <v>163.55269999999999</v>
-      </c>
-      <c r="N14" s="2">
-        <v>99.859099999999998</v>
-      </c>
-      <c r="O14" s="2">
-        <v>1810.9880000000001</v>
-      </c>
-      <c r="P14" s="2">
-        <v>66.436300000000003</v>
-      </c>
-      <c r="Q14" s="2">
-        <v>1396.5757000000001</v>
-      </c>
-      <c r="R14" s="2">
-        <v>3893.9758000000002</v>
-      </c>
-      <c r="S14" s="2">
-        <v>5319.424</v>
-      </c>
-      <c r="T14" s="2">
-        <v>284.7353</v>
-      </c>
-      <c r="U14" s="2">
-        <v>410.04539999999997</v>
-      </c>
-      <c r="V14" s="2">
-        <v>3917.9250999999999</v>
-      </c>
-      <c r="W14" s="2">
-        <v>1404.2308</v>
-      </c>
-    </row>
-    <row r="15" spans="3:23" x14ac:dyDescent="0.2">
-      <c r="C15" s="2">
-        <v>2023</v>
-      </c>
-      <c r="D15" s="20">
-        <v>752</v>
-      </c>
-      <c r="E15" s="20">
-        <v>1025</v>
-      </c>
-      <c r="F15" s="20">
-        <v>474</v>
-      </c>
-      <c r="G15" s="20">
-        <v>1066</v>
-      </c>
-      <c r="H15" s="20">
-        <v>553</v>
-      </c>
-      <c r="I15" s="2">
-        <v>19.332699999999999</v>
-      </c>
-      <c r="J15" s="2">
-        <v>0.87619999999999998</v>
-      </c>
-      <c r="K15" s="2">
-        <v>3.9238</v>
-      </c>
-      <c r="L15" s="2">
-        <v>57.3155</v>
-      </c>
-      <c r="M15" s="2">
-        <v>172.2927</v>
-      </c>
-      <c r="N15" s="2">
-        <v>103.6181</v>
-      </c>
-      <c r="O15" s="2">
-        <v>2259.2469000000001</v>
-      </c>
-      <c r="P15" s="2">
-        <v>152.04130000000001</v>
-      </c>
-      <c r="Q15" s="2">
-        <v>1909.9184</v>
-      </c>
-      <c r="R15" s="2">
-        <v>5764.7286999999997</v>
-      </c>
-      <c r="S15" s="2">
-        <v>6014.6284999999998</v>
-      </c>
-      <c r="T15" s="2">
-        <v>293.39640000000003</v>
-      </c>
-      <c r="U15" s="2">
-        <v>443.1404</v>
-      </c>
-      <c r="V15" s="2">
-        <v>4957.8874999999998</v>
-      </c>
-      <c r="W15" s="2">
-        <v>1553.2028</v>
-      </c>
-    </row>
-    <row r="16" spans="3:23" x14ac:dyDescent="0.2">
-      <c r="C16" s="2">
-        <v>2024</v>
-      </c>
-      <c r="D16" s="20">
-        <v>946</v>
-      </c>
-      <c r="E16" s="20">
-        <v>1601</v>
-      </c>
-      <c r="F16" s="20">
-        <v>595</v>
-      </c>
-      <c r="G16" s="20">
-        <v>1878</v>
-      </c>
-      <c r="H16" s="20">
-        <v>621</v>
-      </c>
-      <c r="I16" s="2">
-        <v>19.4649</v>
-      </c>
-      <c r="J16" s="2">
-        <v>0.93620000000000003</v>
-      </c>
-      <c r="K16" s="2">
-        <v>7.5818000000000003</v>
-      </c>
-      <c r="L16" s="2">
-        <v>59.515500000000003</v>
-      </c>
-      <c r="M16" s="2">
-        <v>234.41380000000001</v>
-      </c>
-      <c r="N16" s="2">
-        <v>105.11409999999999</v>
-      </c>
-      <c r="O16" s="2">
-        <v>2781.4018999999998</v>
-      </c>
-      <c r="P16" s="2">
-        <v>152.05860000000001</v>
-      </c>
-      <c r="Q16" s="2">
-        <v>2402.6529</v>
-      </c>
-      <c r="R16" s="2">
-        <v>6752.4339</v>
-      </c>
-      <c r="S16" s="2">
-        <v>6715.3987999999999</v>
-      </c>
-      <c r="T16" s="2">
-        <v>308.52460000000002</v>
-      </c>
-      <c r="U16" s="2">
-        <v>477.52710000000002</v>
-      </c>
-      <c r="V16" s="2">
-        <v>6559.0370000000003</v>
-      </c>
-      <c r="W16" s="2">
-        <v>1690.5808</v>
-      </c>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
-      <c r="C17" s="2">
-        <v>2025</v>
-      </c>
-      <c r="D17" s="20">
-        <v>1326</v>
-      </c>
-      <c r="E17" s="20">
-        <v>1927</v>
-      </c>
-      <c r="F17" s="20">
-        <v>677</v>
-      </c>
-      <c r="G17" s="20">
-        <v>2192</v>
-      </c>
-      <c r="H17" s="20">
-        <v>691</v>
-      </c>
-      <c r="I17" s="2">
-        <v>19.4649</v>
-      </c>
-      <c r="J17" s="2">
-        <v>0.93620000000000003</v>
-      </c>
-      <c r="K17" s="2">
-        <v>7.5818000000000003</v>
-      </c>
-      <c r="L17" s="2">
-        <v>62.514499999999998</v>
-      </c>
-      <c r="M17" s="2">
-        <v>279.63279999999997</v>
-      </c>
-      <c r="N17" s="2">
-        <v>105.11409999999999</v>
-      </c>
-      <c r="O17" s="2">
-        <v>3122.9047999999998</v>
-      </c>
-      <c r="P17" s="2">
-        <v>152.05860000000001</v>
-      </c>
-      <c r="Q17" s="2">
-        <v>3964.9854</v>
-      </c>
-      <c r="R17" s="2">
-        <v>7744.6749</v>
-      </c>
-      <c r="S17" s="2">
-        <v>7094.5673999999999</v>
-      </c>
-      <c r="T17" s="2">
-        <v>414.77620000000002</v>
-      </c>
-      <c r="U17" s="2">
-        <v>572.47410000000002</v>
-      </c>
-      <c r="V17" s="2">
-        <v>8186.1710000000003</v>
-      </c>
-      <c r="W17" s="2">
-        <v>1796.0708</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="D5:W5"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>